--- a/research/traditional_assets/database/data/ireland/ireland_heathcare_information_and_technology.xlsx
+++ b/research/traditional_assets/database/data/ireland/ireland_heathcare_information_and_technology.xlsx
@@ -353,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -581,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.247</v>
+        <v>0.482</v>
       </c>
       <c r="E2">
         <v>0.155</v>
@@ -599,31 +599,31 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="G2">
-        <v>0.1964294313092888</v>
+        <v>0.1954221172408005</v>
       </c>
       <c r="H2">
-        <v>0.1964294313092888</v>
+        <v>0.1939473147803983</v>
       </c>
       <c r="I2">
-        <v>0.1391383691478609</v>
+        <v>0.1374593355999869</v>
       </c>
       <c r="J2">
-        <v>0.1289806473545924</v>
+        <v>0.1341142873158855</v>
       </c>
       <c r="K2">
-        <v>747.9</v>
+        <v>740.86</v>
       </c>
       <c r="L2">
-        <v>0.09003467039052343</v>
+        <v>0.08883106917183249</v>
       </c>
       <c r="M2">
         <v>100</v>
       </c>
       <c r="N2">
-        <v>0.005775839662690963</v>
+        <v>0.005598007109469029</v>
       </c>
       <c r="O2">
-        <v>0.1337077149351518</v>
+        <v>0.1349782684987717</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -641,73 +641,73 @@
         <v>1</v>
       </c>
       <c r="U2">
-        <v>695.5</v>
+        <v>757.3</v>
       </c>
       <c r="V2">
-        <v>0.04017096485401565</v>
+        <v>0.04239370784000895</v>
       </c>
       <c r="W2">
-        <v>0.08348029914052907</v>
+        <v>-0.01123809523809524</v>
       </c>
       <c r="X2">
-        <v>0.11694939095233</v>
+        <v>0.1090424174320601</v>
       </c>
       <c r="Y2">
-        <v>-0.03346909181180094</v>
+        <v>-0.1202805126701554</v>
       </c>
       <c r="Z2">
-        <v>2.158884986439396</v>
+        <v>2.118046953345302</v>
       </c>
       <c r="AA2">
-        <v>0.2784543831150637</v>
+        <v>-0.04702549575070822</v>
       </c>
       <c r="AB2">
-        <v>0.1067778624427352</v>
+        <v>0.1060467875084202</v>
       </c>
       <c r="AC2">
-        <v>0.1716765206723285</v>
+        <v>-0.1530586232232634</v>
       </c>
       <c r="AD2">
-        <v>3432.1</v>
+        <v>3453.9</v>
       </c>
       <c r="AE2">
         <v>143.0269758127467</v>
       </c>
       <c r="AF2">
-        <v>3575.126975812746</v>
+        <v>3596.926975812747</v>
       </c>
       <c r="AG2">
-        <v>2879.626975812746</v>
+        <v>2839.626975812746</v>
       </c>
       <c r="AH2">
-        <v>0.1711518416194822</v>
+        <v>0.1676074283082396</v>
       </c>
       <c r="AI2">
-        <v>0.2678072565091346</v>
+        <v>0.2660266549954157</v>
       </c>
       <c r="AJ2">
-        <v>0.1426043118166866</v>
+        <v>0.1371593276286357</v>
       </c>
       <c r="AK2">
-        <v>0.2275642548329807</v>
+        <v>0.2224780606009467</v>
       </c>
       <c r="AL2">
-        <v>266.8</v>
+        <v>270.174</v>
       </c>
       <c r="AM2">
-        <v>259.48</v>
+        <v>262.5720000000001</v>
       </c>
       <c r="AN2">
-        <v>1.988470451911935</v>
+        <v>2.011847761507007</v>
       </c>
       <c r="AO2">
-        <v>4.285982008995502</v>
+        <v>4.197776247899502</v>
       </c>
       <c r="AP2">
-        <v>1.668381793634268</v>
+        <v>1.654042437477572</v>
       </c>
       <c r="AQ2">
-        <v>4.406890704485894</v>
+        <v>4.319310512925978</v>
       </c>
     </row>
     <row r="3">
@@ -787,10 +787,10 @@
         <v>0.08348029914052907</v>
       </c>
       <c r="X3">
-        <v>0.11694939095233</v>
+        <v>0.1169161634852974</v>
       </c>
       <c r="Y3">
-        <v>-0.03346909181180094</v>
+        <v>-0.03343586434476836</v>
       </c>
       <c r="Z3">
         <v>2.158884986439396</v>
@@ -799,10 +799,10 @@
         <v>0.2784543831150637</v>
       </c>
       <c r="AB3">
-        <v>0.1067778624427352</v>
+        <v>0.1067503219178776</v>
       </c>
       <c r="AC3">
-        <v>0.1716765206723285</v>
+        <v>0.1717040611971861</v>
       </c>
       <c r="AD3">
         <v>3432.1</v>
@@ -845,6 +845,244 @@
       </c>
       <c r="AQ3">
         <v>4.406890704485894</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Malin Corporation plc (ISE:MLC)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Heathcare Information and Technology</t>
+        </is>
+      </c>
+      <c r="K4">
+        <v>-1.18</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>38.3</v>
+      </c>
+      <c r="V4">
+        <v>0.227705112960761</v>
+      </c>
+      <c r="W4">
+        <v>-0.01123809523809524</v>
+      </c>
+      <c r="X4">
+        <v>0.1060331274725552</v>
+      </c>
+      <c r="Y4">
+        <v>-0.1172712227106504</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>-0.04702549575070822</v>
+      </c>
+      <c r="AB4">
+        <v>0.1060331274725552</v>
+      </c>
+      <c r="AC4">
+        <v>-0.1530586232232634</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>-38.3</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>-0.2948421862971517</v>
+      </c>
+      <c r="AK4">
+        <v>-0.4337485843714609</v>
+      </c>
+      <c r="AL4">
+        <v>0.964</v>
+      </c>
+      <c r="AM4">
+        <v>0.964</v>
+      </c>
+      <c r="AN4">
+        <v>-0</v>
+      </c>
+      <c r="AO4">
+        <v>-3.443983402489626</v>
+      </c>
+      <c r="AP4">
+        <v>11.93146417445483</v>
+      </c>
+      <c r="AQ4">
+        <v>-3.443983402489626</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>kneat.com, inc. (TSX:KSI)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Heathcare Information and Technology</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>0.7170000000000001</v>
+      </c>
+      <c r="G5">
+        <v>0.07027027027027027</v>
+      </c>
+      <c r="H5">
+        <v>-0.2990990990990992</v>
+      </c>
+      <c r="I5">
+        <v>-0.1816816816816817</v>
+      </c>
+      <c r="J5">
+        <v>-0.1816816816816817</v>
+      </c>
+      <c r="K5">
+        <v>-5.86</v>
+      </c>
+      <c r="L5">
+        <v>-0.175975975975976</v>
+      </c>
+      <c r="M5">
+        <v>-0</v>
+      </c>
+      <c r="N5">
+        <v>-0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>-0</v>
+      </c>
+      <c r="Q5">
+        <v>-0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>23.5</v>
+      </c>
+      <c r="V5">
+        <v>0.06155055002619172</v>
+      </c>
+      <c r="W5">
+        <v>-0.4614173228346457</v>
+      </c>
+      <c r="X5">
+        <v>0.1090424174320601</v>
+      </c>
+      <c r="Y5">
+        <v>-0.5704597402667059</v>
+      </c>
+      <c r="Z5">
+        <v>1.724495080269291</v>
+      </c>
+      <c r="AA5">
+        <v>-0.3133091662351114</v>
+      </c>
+      <c r="AB5">
+        <v>0.1060467875084202</v>
+      </c>
+      <c r="AC5">
+        <v>-0.4193559537435316</v>
+      </c>
+      <c r="AD5">
+        <v>21.8</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>21.8</v>
+      </c>
+      <c r="AG5">
+        <v>-1.699999999999999</v>
+      </c>
+      <c r="AH5">
+        <v>0.05401387512388503</v>
+      </c>
+      <c r="AI5">
+        <v>0.4876957494407159</v>
+      </c>
+      <c r="AJ5">
+        <v>-0.004472507234938172</v>
+      </c>
+      <c r="AK5">
+        <v>-0.08018867924528299</v>
+      </c>
+      <c r="AL5">
+        <v>2.41</v>
+      </c>
+      <c r="AM5">
+        <v>2.128</v>
+      </c>
+      <c r="AN5">
+        <v>-3.627287853577371</v>
+      </c>
+      <c r="AO5">
+        <v>-2.510373443983402</v>
+      </c>
+      <c r="AP5">
+        <v>0.2828618968386022</v>
+      </c>
+      <c r="AQ5">
+        <v>-2.843045112781954</v>
       </c>
     </row>
   </sheetData>
@@ -1139,7 +1377,7 @@
         <v>4.43928035982009</v>
       </c>
       <c r="F2">
-        <v>8.94329053915078</v>
+        <v>9.16593207589089</v>
       </c>
       <c r="G2">
         <v>2.07133660244076</v>
@@ -1157,13 +1395,13 @@
         <v>17313.5</v>
       </c>
       <c r="L2">
-        <v>18916.2898049813</v>
+        <v>18959.4802048652</v>
       </c>
       <c r="M2">
         <v>20193.1269758127</v>
       </c>
       <c r="N2">
-        <v>20518.5387723207</v>
+        <v>20561.7291722046</v>
       </c>
       <c r="O2">
         <v>3575.12697581275</v>
@@ -1172,16 +1410,16 @@
         <v>2297.7489673394</v>
       </c>
       <c r="Q2">
-        <v>0.106777862442735</v>
+        <v>0.106750321917878</v>
       </c>
       <c r="R2">
-        <v>0.105742201969967</v>
+        <v>0.105579696323576</v>
       </c>
       <c r="S2">
         <v>0.0575195395797173</v>
       </c>
       <c r="T2">
-        <v>0.0504320395797173</v>
+        <v>0.0492070395797173</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1194,10 +1432,10 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.11694939095233</v>
+        <v>0.116916163485297</v>
       </c>
       <c r="X2">
-        <v>0.112578289456402</v>
+        <v>0.112547103336862</v>
       </c>
       <c r="Y2">
         <v>1.38618639477393</v>
@@ -1236,7 +1474,7 @@
         <v>17313.5</v>
       </c>
       <c r="AK2">
-        <v>0.05132743418963756</v>
+        <v>0.05130346377183671</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1424,13 +1662,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.1060612700797949</v>
+        <v>0.1060331274725552</v>
       </c>
       <c r="C2">
-        <v>21112.67300238701</v>
+        <v>21112.86897858459</v>
       </c>
       <c r="D2">
-        <v>20417.17300238701</v>
+        <v>20417.36897858459</v>
       </c>
       <c r="E2">
         <v>-3575.126975812746</v>
@@ -1475,19 +1713,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.1060612700797949</v>
+        <v>0.1060331274725552</v>
       </c>
       <c r="T2">
         <v>1.174055766301309</v>
       </c>
       <c r="U2">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V2">
         <v>0.125</v>
       </c>
       <c r="W2">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1506,13 +1744,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.1060322638879924</v>
+        <v>0.1059919064590117</v>
       </c>
       <c r="C3">
-        <v>20912.96039827611</v>
+        <v>20917.02254674257</v>
       </c>
       <c r="D3">
-        <v>20426.34666803424</v>
+        <v>20430.4088165007</v>
       </c>
       <c r="E3">
         <v>-3366.240706054618</v>
@@ -1539,37 +1777,37 @@
         <v>1184.4</v>
       </c>
       <c r="M3">
-        <v>12.03949785611588</v>
+        <v>11.7470570784545</v>
       </c>
       <c r="N3">
-        <v>1172.360502143884</v>
+        <v>1172.652942921546</v>
       </c>
       <c r="O3">
-        <v>146.5450627679855</v>
+        <v>146.5816178651932</v>
       </c>
       <c r="P3">
-        <v>1025.815439375899</v>
+        <v>1026.071325056352</v>
       </c>
       <c r="Q3">
-        <v>1567.415439375899</v>
+        <v>1567.671325056353</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.1065938823153487</v>
+        <v>0.106565490972944</v>
       </c>
       <c r="T3">
         <v>1.184432521811548</v>
       </c>
       <c r="U3">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V3">
         <v>0.125</v>
       </c>
       <c r="W3">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1577,7 +1815,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>98.37619593065858</v>
+        <v>100.8252528347998</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1588,13 +1826,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.1060032576961898</v>
+        <v>0.1059506854454682</v>
       </c>
       <c r="C4">
-        <v>20713.25604153333</v>
+        <v>20721.19278169433</v>
       </c>
       <c r="D4">
-        <v>20435.52858104958</v>
+        <v>20443.46532121058</v>
       </c>
       <c r="E4">
         <v>-3157.354436296491</v>
@@ -1621,37 +1859,37 @@
         <v>1184.4</v>
       </c>
       <c r="M4">
-        <v>24.07899571223177</v>
+        <v>23.49411415690901</v>
       </c>
       <c r="N4">
-        <v>1160.321004287768</v>
+        <v>1160.905885843091</v>
       </c>
       <c r="O4">
-        <v>145.040125535971</v>
+        <v>145.1132357303864</v>
       </c>
       <c r="P4">
-        <v>1015.280878751797</v>
+        <v>1015.792650112705</v>
       </c>
       <c r="Q4">
-        <v>1556.880878751797</v>
+        <v>1557.392650112705</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.1071373641883627</v>
+        <v>0.1071087190345651</v>
       </c>
       <c r="T4">
         <v>1.195021047842404</v>
       </c>
       <c r="U4">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V4">
         <v>0.125</v>
       </c>
       <c r="W4">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1659,7 +1897,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>49.18809796532929</v>
+        <v>50.4126264173999</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1670,13 +1908,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.1059742515043872</v>
+        <v>0.1059094644319246</v>
       </c>
       <c r="C5">
-        <v>20513.55994328555</v>
+        <v>20525.37971541413</v>
       </c>
       <c r="D5">
-        <v>20444.71875255993</v>
+        <v>20456.53852468851</v>
       </c>
       <c r="E5">
         <v>-2948.468166538364</v>
@@ -1703,37 +1941,37 @@
         <v>1184.4</v>
       </c>
       <c r="M5">
-        <v>36.11849356834764</v>
+        <v>35.2411712353635</v>
       </c>
       <c r="N5">
-        <v>1148.281506431652</v>
+        <v>1149.158828764637</v>
       </c>
       <c r="O5">
-        <v>143.5351883039565</v>
+        <v>143.6448535955796</v>
       </c>
       <c r="P5">
-        <v>1004.746318127696</v>
+        <v>1005.513975169057</v>
       </c>
       <c r="Q5">
-        <v>1546.346318127696</v>
+        <v>1547.113975169057</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.1076920518731914</v>
+        <v>0.1076631476747764</v>
       </c>
       <c r="T5">
         <v>1.205827893997607</v>
       </c>
       <c r="U5">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V5">
         <v>0.125</v>
       </c>
       <c r="W5">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1741,7 +1979,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>32.79206531021953</v>
+        <v>33.60841761159995</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1752,13 +1990,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.1059452453125846</v>
+        <v>0.1058682434183811</v>
       </c>
       <c r="C6">
-        <v>20313.87211467971</v>
+        <v>20329.58337995811</v>
       </c>
       <c r="D6">
-        <v>20453.91719371222</v>
+        <v>20469.62845899062</v>
       </c>
       <c r="E6">
         <v>-2739.581896780236</v>
@@ -1785,37 +2023,37 @@
         <v>1184.4</v>
       </c>
       <c r="M6">
-        <v>48.15799142446353</v>
+        <v>46.98822831381802</v>
       </c>
       <c r="N6">
-        <v>1136.242008575537</v>
+        <v>1137.411771686182</v>
       </c>
       <c r="O6">
-        <v>142.0302510719421</v>
+        <v>142.1764714607727</v>
       </c>
       <c r="P6">
-        <v>994.2117575035945</v>
+        <v>995.2353002254092</v>
       </c>
       <c r="Q6">
-        <v>1535.811757503594</v>
+        <v>1536.835300225409</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.1082582955514541</v>
+        <v>0.1082291269116588</v>
       </c>
       <c r="T6">
         <v>1.216859882781044</v>
       </c>
       <c r="U6">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V6">
         <v>0.125</v>
       </c>
       <c r="W6">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1823,7 +2061,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>24.59404898266465</v>
+        <v>25.20631320869995</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1834,13 +2072,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.1059162391207821</v>
+        <v>0.1058270224048376</v>
       </c>
       <c r="C7">
-        <v>20114.1925668828</v>
+        <v>20133.80380746448</v>
       </c>
       <c r="D7">
-        <v>20463.12391567344</v>
+        <v>20482.73515625512</v>
       </c>
       <c r="E7">
         <v>-2530.695627022109</v>
@@ -1867,37 +2105,37 @@
         <v>1184.4</v>
       </c>
       <c r="M7">
-        <v>60.1974892805794</v>
+        <v>58.73528539227252</v>
       </c>
       <c r="N7">
-        <v>1124.202510719421</v>
+        <v>1125.664714607728</v>
       </c>
       <c r="O7">
-        <v>140.5253138399276</v>
+        <v>140.7080893259659</v>
       </c>
       <c r="P7">
-        <v>983.6771968794931</v>
+        <v>984.9566252817616</v>
       </c>
       <c r="Q7">
-        <v>1525.277196879493</v>
+        <v>1526.556625281762</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.1088364601492592</v>
+        <v>0.1088070215008966</v>
       </c>
       <c r="T7">
         <v>1.228124123959922</v>
       </c>
       <c r="U7">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V7">
         <v>0.125</v>
       </c>
       <c r="W7">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1905,7 +2143,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>19.67523918613172</v>
+        <v>20.16505056695996</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1916,13 +2154,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.1058872329289795</v>
+        <v>0.1057858013912941</v>
       </c>
       <c r="C8">
-        <v>19914.52131108195</v>
+        <v>19938.04103015386</v>
       </c>
       <c r="D8">
-        <v>20472.33892963072</v>
+        <v>20495.85864870262</v>
       </c>
       <c r="E8">
         <v>-2321.809357263981</v>
@@ -1949,37 +2187,37 @@
         <v>1184.4</v>
       </c>
       <c r="M8">
-        <v>72.23698713669528</v>
+        <v>70.482342470727</v>
       </c>
       <c r="N8">
-        <v>1112.163012863305</v>
+        <v>1113.917657529273</v>
       </c>
       <c r="O8">
-        <v>139.0203766079131</v>
+        <v>139.2397071911591</v>
       </c>
       <c r="P8">
-        <v>973.1426362553917</v>
+        <v>974.677950338114</v>
       </c>
       <c r="Q8">
-        <v>1514.742636255392</v>
+        <v>1516.277950338114</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.1094269261214856</v>
+        <v>0.1093972117196926</v>
       </c>
       <c r="T8">
         <v>1.239628029844734</v>
       </c>
       <c r="U8">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V8">
         <v>0.125</v>
       </c>
       <c r="W8">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1987,7 +2225,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>16.39603265510977</v>
+        <v>16.80420880579997</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1998,13 +2236,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.1058582267371769</v>
+        <v>0.1057445803777506</v>
       </c>
       <c r="C9">
-        <v>19714.85835848443</v>
+        <v>19742.29508032943</v>
       </c>
       <c r="D9">
-        <v>20481.56224679133</v>
+        <v>20508.99896863633</v>
       </c>
       <c r="E9">
         <v>-2112.923087505854</v>
@@ -2031,37 +2269,37 @@
         <v>1184.4</v>
       </c>
       <c r="M9">
-        <v>84.27648499281118</v>
+        <v>82.22939954918154</v>
       </c>
       <c r="N9">
-        <v>1100.123515007189</v>
+        <v>1102.170600450818</v>
       </c>
       <c r="O9">
-        <v>137.5154393758986</v>
+        <v>137.7713250563523</v>
       </c>
       <c r="P9">
-        <v>962.6080756312903</v>
+        <v>964.3992753944661</v>
       </c>
       <c r="Q9">
-        <v>1504.20807563129</v>
+        <v>1505.999275394466</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.1100300902866632</v>
+        <v>0.1100000942012584</v>
       </c>
       <c r="T9">
         <v>1.251379331555025</v>
       </c>
       <c r="U9">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V9">
         <v>0.125</v>
       </c>
       <c r="W9">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2069,7 +2307,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>14.05374227580837</v>
+        <v>14.40360754782854</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2080,13 +2318,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.1058292205453744</v>
+        <v>0.1057033593642071</v>
       </c>
       <c r="C10">
-        <v>19515.20372031771</v>
+        <v>19546.56599037734</v>
       </c>
       <c r="D10">
-        <v>20490.79387838273</v>
+        <v>20522.15614844236</v>
       </c>
       <c r="E10">
         <v>-1904.036817747726</v>
@@ -2113,37 +2351,37 @@
         <v>1184.4</v>
       </c>
       <c r="M10">
-        <v>96.31598284892706</v>
+        <v>93.97645662763604</v>
       </c>
       <c r="N10">
-        <v>1088.084017151073</v>
+        <v>1090.423543372364</v>
       </c>
       <c r="O10">
-        <v>136.0105021438841</v>
+        <v>136.3029429215455</v>
       </c>
       <c r="P10">
-        <v>952.0735150071889</v>
+        <v>954.1206004508185</v>
       </c>
       <c r="Q10">
-        <v>1493.673515007189</v>
+        <v>1495.720600450818</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.1106463667163011</v>
+        <v>0.1106160828237279</v>
       </c>
       <c r="T10">
         <v>1.263386096345974</v>
       </c>
       <c r="U10">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V10">
         <v>0.125</v>
       </c>
       <c r="W10">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2151,7 +2389,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>12.29702449133232</v>
+        <v>12.60315660434997</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2162,13 +2400,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.1058002143535718</v>
+        <v>0.1056621383506635</v>
       </c>
       <c r="C11">
-        <v>19315.55740782955</v>
+        <v>19350.85379276686</v>
       </c>
       <c r="D11">
-        <v>20500.0338356527</v>
+        <v>20535.33022059001</v>
       </c>
       <c r="E11">
         <v>-1695.150547989599</v>
@@ -2195,37 +2433,37 @@
         <v>1184.4</v>
       </c>
       <c r="M11">
-        <v>108.3554807050429</v>
+        <v>105.7235137060905</v>
       </c>
       <c r="N11">
-        <v>1076.044519294957</v>
+        <v>1078.67648629391</v>
       </c>
       <c r="O11">
-        <v>134.5055649118696</v>
+        <v>134.8345607867387</v>
       </c>
       <c r="P11">
-        <v>941.5389543830875</v>
+        <v>943.8419255071709</v>
       </c>
       <c r="Q11">
-        <v>1483.138954383087</v>
+        <v>1485.441925507171</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.1112761876828541</v>
+        <v>0.1112456096576802</v>
       </c>
       <c r="T11">
         <v>1.275656746077384</v>
       </c>
       <c r="U11">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V11">
         <v>0.125</v>
       </c>
       <c r="W11">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2233,7 +2471,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>10.93068843673984</v>
+        <v>11.20280587053331</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2244,13 +2482,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.1057712081617692</v>
+        <v>0.10562091733712</v>
       </c>
       <c r="C12">
-        <v>19115.91943228795</v>
+        <v>19155.15852005067</v>
       </c>
       <c r="D12">
-        <v>20509.28212986923</v>
+        <v>20548.52121763194</v>
       </c>
       <c r="E12">
         <v>-1486.264278231472</v>
@@ -2277,37 +2515,37 @@
         <v>1184.4</v>
       </c>
       <c r="M12">
-        <v>120.3949785611588</v>
+        <v>117.470570784545</v>
       </c>
       <c r="N12">
-        <v>1064.005021438841</v>
+        <v>1066.929429215455</v>
       </c>
       <c r="O12">
-        <v>133.0006276798552</v>
+        <v>133.3661786519319</v>
       </c>
       <c r="P12">
-        <v>931.0043937589862</v>
+        <v>933.5632505635231</v>
       </c>
       <c r="Q12">
-        <v>1472.604393758986</v>
+        <v>1475.163250563523</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.1119200046708861</v>
+        <v>0.1118891259768314</v>
       </c>
       <c r="T12">
         <v>1.288200076913937</v>
       </c>
       <c r="U12">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V12">
         <v>0.125</v>
       </c>
       <c r="W12">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2315,7 +2553,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>9.837619593065861</v>
+        <v>10.08252528347998</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2326,13 +2564,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.1057422019699667</v>
+        <v>0.1055796963235765</v>
       </c>
       <c r="C13">
-        <v>18916.28980498129</v>
+        <v>18959.48020486518</v>
       </c>
       <c r="D13">
-        <v>20518.53877232069</v>
+        <v>20561.72917220458</v>
       </c>
       <c r="E13">
         <v>-1277.378008473344</v>
@@ -2359,37 +2597,37 @@
         <v>1184.4</v>
       </c>
       <c r="M13">
-        <v>132.4344764172747</v>
+        <v>129.2176278629995</v>
       </c>
       <c r="N13">
-        <v>1051.965523582725</v>
+        <v>1055.182372137001</v>
       </c>
       <c r="O13">
-        <v>131.4956904478407</v>
+        <v>131.8977965171251</v>
       </c>
       <c r="P13">
-        <v>920.4698331348848</v>
+        <v>923.2845756198756</v>
       </c>
       <c r="Q13">
-        <v>1462.069833134885</v>
+        <v>1464.884575619876</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.112578289456402</v>
+        <v>0.1125471033368624</v>
       </c>
       <c r="T13">
         <v>1.301025280353558</v>
       </c>
       <c r="U13">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V13">
         <v>0.125</v>
       </c>
       <c r="W13">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2397,7 +2635,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>8.94329053915078</v>
+        <v>9.165932075890892</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2408,13 +2646,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.1058286957781641</v>
+        <v>0.105695975310033</v>
       </c>
       <c r="C14">
-        <v>18679.82573252726</v>
+        <v>18713.37958281746</v>
       </c>
       <c r="D14">
-        <v>20490.96096962479</v>
+        <v>20524.51481991499</v>
       </c>
       <c r="E14">
         <v>-1068.491738715217</v>
@@ -2441,37 +2679,37 @@
         <v>1184.4</v>
       </c>
       <c r="M14">
-        <v>147.2312730341978</v>
+        <v>144.7246377971003</v>
       </c>
       <c r="N14">
-        <v>1037.168726965802</v>
+        <v>1039.6753622029</v>
       </c>
       <c r="O14">
-        <v>129.6460908707253</v>
+        <v>129.9594202753625</v>
       </c>
       <c r="P14">
-        <v>907.522636095077</v>
+        <v>909.7159419275373</v>
       </c>
       <c r="Q14">
-        <v>1449.122636095077</v>
+        <v>1451.315941927537</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.1132515352597705</v>
+        <v>0.1132200347278033</v>
       </c>
       <c r="T14">
         <v>1.314141965689534</v>
       </c>
       <c r="U14">
-        <v>0.0587366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V14">
         <v>0.125</v>
       </c>
       <c r="W14">
-        <v>0.05139453957971733</v>
+        <v>0.05051953957971733</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2479,7 +2717,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>8.044486579457178</v>
+        <v>8.183817337725827</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2490,13 +2728,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.1058093145863615</v>
+        <v>0.1056678792964894</v>
       </c>
       <c r="C15">
-        <v>18477.11254173991</v>
+        <v>18513.47291655999</v>
       </c>
       <c r="D15">
-        <v>20497.13404859557</v>
+        <v>20533.49442341565</v>
       </c>
       <c r="E15">
         <v>-859.6054689570888</v>
@@ -2523,37 +2761,37 @@
         <v>1184.4</v>
       </c>
       <c r="M15">
-        <v>159.5005457870477</v>
+        <v>156.785024280192</v>
       </c>
       <c r="N15">
-        <v>1024.899454212952</v>
+        <v>1027.614975719808</v>
       </c>
       <c r="O15">
-        <v>128.112431776619</v>
+        <v>128.451871964976</v>
       </c>
       <c r="P15">
-        <v>896.7870224363334</v>
+        <v>899.1631037548322</v>
       </c>
       <c r="Q15">
-        <v>1438.387022436333</v>
+        <v>1440.763103754832</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.1139402579781589</v>
+        <v>0.1139084358058922</v>
       </c>
       <c r="T15">
         <v>1.327560184021739</v>
       </c>
       <c r="U15">
-        <v>0.0587366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V15">
         <v>0.125</v>
       </c>
       <c r="W15">
-        <v>0.05139453957971733</v>
+        <v>0.05051953957971733</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2561,7 +2799,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>7.425679919498933</v>
+        <v>7.554292927131532</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2572,13 +2810,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.105789933394559</v>
+        <v>0.1056397832829459</v>
       </c>
       <c r="C16">
-        <v>18274.4030714601</v>
+        <v>18313.57411100692</v>
       </c>
       <c r="D16">
-        <v>20503.31084807389</v>
+        <v>20542.4818876207</v>
       </c>
       <c r="E16">
         <v>-650.7191991989612</v>
@@ -2605,37 +2843,37 @@
         <v>1184.4</v>
       </c>
       <c r="M16">
-        <v>171.7698185398975</v>
+        <v>168.8454107632837</v>
       </c>
       <c r="N16">
-        <v>1012.630181460103</v>
+        <v>1015.554589236716</v>
       </c>
       <c r="O16">
-        <v>126.5787726825128</v>
+        <v>126.9443236545895</v>
       </c>
       <c r="P16">
-        <v>886.0514087775897</v>
+        <v>888.6102655821268</v>
       </c>
       <c r="Q16">
-        <v>1427.65140877759</v>
+        <v>1430.210265582127</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.1146449975039518</v>
+        <v>0.1146128462113785</v>
       </c>
       <c r="T16">
         <v>1.341290453943065</v>
       </c>
       <c r="U16">
-        <v>0.0587366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V16">
         <v>0.125</v>
       </c>
       <c r="W16">
-        <v>0.05139453957971733</v>
+        <v>0.05051953957971733</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2643,7 +2881,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>6.895274210963294</v>
+        <v>7.014700575193564</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2654,13 +2892,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.1060593022027564</v>
+        <v>0.1058348122694024</v>
       </c>
       <c r="C17">
-        <v>17980.00106760812</v>
+        <v>18042.46294640996</v>
       </c>
       <c r="D17">
-        <v>20417.79511398004</v>
+        <v>20480.25699278187</v>
       </c>
       <c r="E17">
         <v>-441.8329294408341</v>
@@ -2687,37 +2925,37 @@
         <v>1184.4</v>
       </c>
       <c r="M17">
-        <v>190.9323381947655</v>
+        <v>186.2323971252077</v>
       </c>
       <c r="N17">
-        <v>993.4676618052346</v>
+        <v>998.1676028747925</v>
       </c>
       <c r="O17">
-        <v>124.1834577256543</v>
+        <v>124.7709503593491</v>
       </c>
       <c r="P17">
-        <v>869.2842040795803</v>
+        <v>873.3966525154434</v>
       </c>
       <c r="Q17">
-        <v>1410.88420407958</v>
+        <v>1414.996652515443</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.1153663191362339</v>
+        <v>0.1153338309793468</v>
       </c>
       <c r="T17">
         <v>1.355343789039011</v>
       </c>
       <c r="U17">
-        <v>0.0609366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V17">
         <v>0.125</v>
       </c>
       <c r="W17">
-        <v>0.05331953957971734</v>
+        <v>0.05200703957971733</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2725,7 +2963,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>6.203244621619947</v>
+        <v>6.359795708389583</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2736,13 +2974,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.1060591710109538</v>
+        <v>0.1058215912558589</v>
       </c>
       <c r="C18">
-        <v>17771.15627330416</v>
+        <v>17837.78298818478</v>
       </c>
       <c r="D18">
-        <v>20417.8365894342</v>
+        <v>20484.46330431482</v>
       </c>
       <c r="E18">
         <v>-232.9466596827065</v>
@@ -2769,37 +3007,37 @@
         <v>1184.4</v>
       </c>
       <c r="M18">
-        <v>203.6611607410833</v>
+        <v>198.6478902668882</v>
       </c>
       <c r="N18">
-        <v>980.7388392589169</v>
+        <v>985.7521097331119</v>
       </c>
       <c r="O18">
-        <v>122.5923549073646</v>
+        <v>123.219013716639</v>
       </c>
       <c r="P18">
-        <v>858.1464843515523</v>
+        <v>862.5330960164729</v>
       </c>
       <c r="Q18">
-        <v>1399.746484351552</v>
+        <v>1404.133096016473</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.1161048150930941</v>
+        <v>0.1160719820513144</v>
       </c>
       <c r="T18">
         <v>1.369731727351527</v>
       </c>
       <c r="U18">
-        <v>0.0609366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V18">
         <v>0.125</v>
       </c>
       <c r="W18">
-        <v>0.05331953957971734</v>
+        <v>0.05200703957971733</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2807,7 +3045,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>5.8155418327687</v>
+        <v>5.962308476615234</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2818,13 +3056,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.1062821648191512</v>
+        <v>0.1058083702423154</v>
       </c>
       <c r="C19">
-        <v>17492.01436283323</v>
+        <v>17633.10475813042</v>
       </c>
       <c r="D19">
-        <v>20347.5809487214</v>
+        <v>20488.67134401859</v>
       </c>
       <c r="E19">
         <v>-24.06038992457889</v>
@@ -2851,45 +3089,45 @@
         <v>1184.4</v>
       </c>
       <c r="M19">
-        <v>221.7165831662332</v>
+        <v>211.0633834085687</v>
       </c>
       <c r="N19">
-        <v>962.6834168337668</v>
+        <v>973.3366165914314</v>
       </c>
       <c r="O19">
-        <v>120.3354271042209</v>
+        <v>121.6670770739289</v>
       </c>
       <c r="P19">
-        <v>842.347989729546</v>
+        <v>851.6695395175025</v>
       </c>
       <c r="Q19">
-        <v>1383.947989729546</v>
+        <v>1393.269539517502</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.1168611061332522</v>
+        <v>0.1168279198961005</v>
       </c>
       <c r="T19">
         <v>1.384466362972779</v>
       </c>
       <c r="U19">
-        <v>0.0624366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V19">
         <v>0.125</v>
       </c>
       <c r="W19">
-        <v>0.05463203957971734</v>
+        <v>0.05200703957971733</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y19">
-        <v>5.341954954772101</v>
+        <v>5.611584448579043</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2900,13 +3138,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.1062951586273487</v>
+        <v>0.1059211492287718</v>
       </c>
       <c r="C20">
-        <v>17279.04921390687</v>
+        <v>17388.37814960157</v>
       </c>
       <c r="D20">
-        <v>20343.50206955317</v>
+        <v>20452.83100524786</v>
       </c>
       <c r="E20">
         <v>184.8258798335482</v>
@@ -2933,37 +3171,37 @@
         <v>1184.4</v>
       </c>
       <c r="M20">
-        <v>234.7587351171881</v>
+        <v>226.4868388347662</v>
       </c>
       <c r="N20">
-        <v>949.641264882812</v>
+        <v>957.9131611652339</v>
       </c>
       <c r="O20">
-        <v>118.7051581103515</v>
+        <v>119.7391451456542</v>
       </c>
       <c r="P20">
-        <v>830.9361067724606</v>
+        <v>838.1740160195797</v>
       </c>
       <c r="Q20">
-        <v>1372.536106772461</v>
+        <v>1379.77401601958</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.1176358432963409</v>
+        <v>0.117602295249296</v>
       </c>
       <c r="T20">
         <v>1.399560379950646</v>
       </c>
       <c r="U20">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V20">
         <v>0.125</v>
       </c>
       <c r="W20">
-        <v>0.05463203957971734</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2971,7 +3209,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.045179679506985</v>
+        <v>5.229442938466198</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2982,13 +3220,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.1063081524355461</v>
+        <v>0.1059149282152283</v>
       </c>
       <c r="C21">
-        <v>17066.08569995825</v>
+        <v>17181.46560468606</v>
       </c>
       <c r="D21">
-        <v>20339.42482536267</v>
+        <v>20454.80473009048</v>
       </c>
       <c r="E21">
         <v>393.7121495916758</v>
@@ -3015,37 +3253,37 @@
         <v>1184.4</v>
       </c>
       <c r="M21">
-        <v>247.800887068143</v>
+        <v>239.0694409922532</v>
       </c>
       <c r="N21">
-        <v>936.5991129318571</v>
+        <v>945.3305590077468</v>
       </c>
       <c r="O21">
-        <v>117.0748891164821</v>
+        <v>118.1663198759684</v>
       </c>
       <c r="P21">
-        <v>819.524223815375</v>
+        <v>827.1642391317785</v>
       </c>
       <c r="Q21">
-        <v>1361.124223815375</v>
+        <v>1368.764239131779</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.1184297097720985</v>
+        <v>0.1183957909815827</v>
       </c>
       <c r="T21">
         <v>1.415027088705744</v>
       </c>
       <c r="U21">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V21">
         <v>0.125</v>
       </c>
       <c r="W21">
-        <v>0.05463203957971734</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3053,7 +3291,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>4.779643906901354</v>
+        <v>4.954209099599556</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3064,13 +3302,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.1063211462437435</v>
+        <v>0.1059087072016848</v>
       </c>
       <c r="C22">
-        <v>16853.12382000449</v>
+        <v>16974.55344074135</v>
       </c>
       <c r="D22">
-        <v>20335.34921516704</v>
+        <v>20456.7788359039</v>
       </c>
       <c r="E22">
         <v>602.598419349803</v>
@@ -3097,37 +3335,37 @@
         <v>1184.4</v>
       </c>
       <c r="M22">
-        <v>260.8430390190978</v>
+        <v>251.6520431497403</v>
       </c>
       <c r="N22">
-        <v>923.5569609809022</v>
+        <v>932.7479568502598</v>
       </c>
       <c r="O22">
-        <v>115.4446201226128</v>
+        <v>116.5934946062825</v>
       </c>
       <c r="P22">
-        <v>808.1123408582894</v>
+        <v>816.1544622439774</v>
       </c>
       <c r="Q22">
-        <v>1349.712340858289</v>
+        <v>1357.754462243977</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.1192434229097501</v>
+        <v>0.1192091241071767</v>
       </c>
       <c r="T22">
         <v>1.43088046517972</v>
       </c>
       <c r="U22">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V22">
         <v>0.125</v>
       </c>
       <c r="W22">
-        <v>0.05463203957971734</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3135,7 +3373,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>4.540661711556287</v>
+        <v>4.706498644619578</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3146,13 +3384,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.106334140051941</v>
+        <v>0.1059024861881413</v>
       </c>
       <c r="C23">
-        <v>16640.16357306355</v>
+        <v>16767.64165787776</v>
       </c>
       <c r="D23">
-        <v>20331.27523798423</v>
+        <v>20458.75332279844</v>
       </c>
       <c r="E23">
         <v>811.4846891079301</v>
@@ -3179,37 +3417,37 @@
         <v>1184.4</v>
       </c>
       <c r="M23">
-        <v>273.8851909700527</v>
+        <v>264.2346453072273</v>
       </c>
       <c r="N23">
-        <v>910.5148090299474</v>
+        <v>920.1653546927728</v>
       </c>
       <c r="O23">
-        <v>113.8143511287434</v>
+        <v>115.0206693365966</v>
       </c>
       <c r="P23">
-        <v>796.700457901204</v>
+        <v>805.1446853561762</v>
       </c>
       <c r="Q23">
-        <v>1338.300457901204</v>
+        <v>1346.744685356176</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.1200777363800004</v>
+        <v>0.1200430479448109</v>
       </c>
       <c r="T23">
         <v>1.447135192956835</v>
       </c>
       <c r="U23">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V23">
         <v>0.125</v>
       </c>
       <c r="W23">
-        <v>0.05463203957971734</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3217,7 +3455,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>4.324439725291702</v>
+        <v>4.482379661542455</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3228,13 +3466,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.1066166338601384</v>
+        <v>0.1058962651745978</v>
       </c>
       <c r="C24">
-        <v>16343.10816624026</v>
+        <v>16560.73025620564</v>
       </c>
       <c r="D24">
-        <v>20243.10610091906</v>
+        <v>20460.72819088444</v>
       </c>
       <c r="E24">
         <v>1020.370958866058</v>
@@ -3261,45 +3499,45 @@
         <v>1184.4</v>
       </c>
       <c r="M24">
-        <v>293.361040029558</v>
+        <v>276.8172474647143</v>
       </c>
       <c r="N24">
-        <v>891.0389599704422</v>
+        <v>907.5827525352859</v>
       </c>
       <c r="O24">
-        <v>111.3798699963053</v>
+        <v>113.4478440669107</v>
       </c>
       <c r="P24">
-        <v>779.6590899741369</v>
+        <v>794.1349084683751</v>
       </c>
       <c r="Q24">
-        <v>1321.259089974137</v>
+        <v>1335.734908468375</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.1209334425033341</v>
+        <v>0.1208983544449486</v>
       </c>
       <c r="T24">
         <v>1.463806708625671</v>
       </c>
       <c r="U24">
-        <v>0.0638366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V24">
         <v>0.125</v>
       </c>
       <c r="W24">
-        <v>0.05585703957971733</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y24">
-        <v>4.037345926646102</v>
+        <v>4.278635131472344</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3310,13 +3548,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.1066418776683358</v>
+        <v>0.1060912941610542</v>
       </c>
       <c r="C25">
-        <v>16126.38025840925</v>
+        <v>16290.11263946518</v>
       </c>
       <c r="D25">
-        <v>20235.26446284618</v>
+        <v>20398.99684390211</v>
       </c>
       <c r="E25">
         <v>1229.257228624186</v>
@@ -3343,37 +3581,37 @@
         <v>1184.4</v>
       </c>
       <c r="M25">
-        <v>306.6956327581743</v>
+        <v>294.2042338266382</v>
       </c>
       <c r="N25">
-        <v>877.7043672418258</v>
+        <v>890.1957661733618</v>
       </c>
       <c r="O25">
-        <v>109.7130459052282</v>
+        <v>111.2744707716702</v>
       </c>
       <c r="P25">
-        <v>767.9913213365976</v>
+        <v>778.9212954016916</v>
       </c>
       <c r="Q25">
-        <v>1309.591321336598</v>
+        <v>1320.521295401692</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.1218113747597414</v>
+        <v>0.1217758766983367</v>
       </c>
       <c r="T25">
         <v>1.480911250675515</v>
       </c>
       <c r="U25">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V25">
         <v>0.125</v>
       </c>
       <c r="W25">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3381,7 +3619,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>3.861809147226706</v>
+        <v>4.025774831975788</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3392,13 +3630,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.1066671214765333</v>
+        <v>0.1060938231475107</v>
       </c>
       <c r="C26">
-        <v>15909.65842350762</v>
+        <v>16080.42833123704</v>
       </c>
       <c r="D26">
-        <v>20227.42889770268</v>
+        <v>20398.1988054321</v>
       </c>
       <c r="E26">
         <v>1438.143498382312</v>
@@ -3425,37 +3663,37 @@
         <v>1184.4</v>
       </c>
       <c r="M26">
-        <v>320.0302254867905</v>
+        <v>306.9957222538833</v>
       </c>
       <c r="N26">
-        <v>864.3697745132097</v>
+        <v>877.4042777461168</v>
       </c>
       <c r="O26">
-        <v>108.0462218141512</v>
+        <v>109.6755347182646</v>
       </c>
       <c r="P26">
-        <v>756.3235526990585</v>
+        <v>767.7287430278523</v>
       </c>
       <c r="Q26">
-        <v>1297.923552699059</v>
+        <v>1309.328743027852</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.1227124104965804</v>
+        <v>0.1226764916426033</v>
       </c>
       <c r="T26">
         <v>1.498465912252986</v>
       </c>
       <c r="U26">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V26">
         <v>0.125</v>
       </c>
       <c r="W26">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3463,7 +3701,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>3.700900432758928</v>
+        <v>3.858034213976798</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3474,13 +3712,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.1066923652847307</v>
+        <v>0.1060963521339672</v>
       </c>
       <c r="C27">
-        <v>15692.94265448336</v>
+        <v>15870.74408544731</v>
       </c>
       <c r="D27">
-        <v>20219.59939843655</v>
+        <v>20397.40082940049</v>
       </c>
       <c r="E27">
         <v>1647.02976814044</v>
@@ -3507,37 +3745,37 @@
         <v>1184.4</v>
       </c>
       <c r="M27">
-        <v>333.3648182154068</v>
+        <v>319.7872106811285</v>
       </c>
       <c r="N27">
-        <v>851.0351817845933</v>
+        <v>864.6127893188716</v>
       </c>
       <c r="O27">
-        <v>106.3793977230742</v>
+        <v>108.0765986648589</v>
       </c>
       <c r="P27">
-        <v>744.6557840615192</v>
+        <v>756.5361906540127</v>
       </c>
       <c r="Q27">
-        <v>1286.255784061519</v>
+        <v>1298.136190654013</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.1236374738530684</v>
+        <v>0.1236011229853838</v>
       </c>
       <c r="T27">
         <v>1.516488698139191</v>
       </c>
       <c r="U27">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V27">
         <v>0.125</v>
       </c>
       <c r="W27">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3545,7 +3783,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>3.55286441544857</v>
+        <v>3.703712845417725</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3556,13 +3794,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.1067176090929281</v>
+        <v>0.1060988811204237</v>
       </c>
       <c r="C28">
-        <v>15476.23294429536</v>
+        <v>15661.05990208865</v>
       </c>
       <c r="D28">
-        <v>20211.77595800667</v>
+        <v>20396.60291579997</v>
       </c>
       <c r="E28">
         <v>1855.916037898568</v>
@@ -3589,37 +3827,37 @@
         <v>1184.4</v>
       </c>
       <c r="M28">
-        <v>346.6994109440231</v>
+        <v>332.5786991083737</v>
       </c>
       <c r="N28">
-        <v>837.7005890559769</v>
+        <v>851.8213008916264</v>
       </c>
       <c r="O28">
-        <v>104.7125736319971</v>
+        <v>106.4776626114533</v>
       </c>
       <c r="P28">
-        <v>732.9880154239798</v>
+        <v>745.3436382801731</v>
       </c>
       <c r="Q28">
-        <v>1274.58801542398</v>
+        <v>1286.943638280173</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.1245875389218941</v>
+        <v>0.1245507443644556</v>
       </c>
       <c r="T28">
         <v>1.534998586346644</v>
       </c>
       <c r="U28">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V28">
         <v>0.125</v>
       </c>
       <c r="W28">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3627,7 +3865,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>3.416215784085163</v>
+        <v>3.561262351363197</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3638,13 +3876,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.1067428529011255</v>
+        <v>0.1061014101068802</v>
       </c>
       <c r="C29">
-        <v>15259.52928591343</v>
+        <v>15451.37578115376</v>
       </c>
       <c r="D29">
-        <v>20203.95856938287</v>
+        <v>20395.8050646232</v>
       </c>
       <c r="E29">
         <v>2064.802307656696</v>
@@ -3671,37 +3909,37 @@
         <v>1184.4</v>
       </c>
       <c r="M29">
-        <v>360.0340036726394</v>
+        <v>345.3701875356188</v>
       </c>
       <c r="N29">
-        <v>824.3659963273608</v>
+        <v>839.0298124643813</v>
       </c>
       <c r="O29">
-        <v>103.0457495409201</v>
+        <v>104.8787265580477</v>
       </c>
       <c r="P29">
-        <v>721.3202467864407</v>
+        <v>734.1510859063336</v>
       </c>
       <c r="Q29">
-        <v>1262.920246786441</v>
+        <v>1275.751085906334</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.1255636331706875</v>
+        <v>0.1255263827676116</v>
       </c>
       <c r="T29">
         <v>1.554015594778959</v>
       </c>
       <c r="U29">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V29">
         <v>0.125</v>
       </c>
       <c r="W29">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3709,7 +3947,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.289689273563491</v>
+        <v>3.429363745757153</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3720,13 +3958,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.106768096709323</v>
+        <v>0.1061039390933366</v>
       </c>
       <c r="C30">
-        <v>15042.83167231824</v>
+        <v>15241.6917226353</v>
       </c>
       <c r="D30">
-        <v>20196.14722554581</v>
+        <v>20395.00727586287</v>
       </c>
       <c r="E30">
         <v>2273.688577414824</v>
@@ -3753,37 +3991,37 @@
         <v>1184.4</v>
       </c>
       <c r="M30">
-        <v>373.3685964012557</v>
+        <v>358.161675962864</v>
       </c>
       <c r="N30">
-        <v>811.0314035987444</v>
+        <v>826.2383240371362</v>
       </c>
       <c r="O30">
-        <v>101.3789254498431</v>
+        <v>103.279790504642</v>
       </c>
       <c r="P30">
-        <v>709.6524781489013</v>
+        <v>722.9585335324941</v>
       </c>
       <c r="Q30">
-        <v>1251.252478148901</v>
+        <v>1264.558533532494</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.1265668411486141</v>
+        <v>0.1265291222375219</v>
       </c>
       <c r="T30">
         <v>1.573560853445505</v>
       </c>
       <c r="U30">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V30">
         <v>0.125</v>
       </c>
       <c r="W30">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3791,7 +4029,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.172200370936223</v>
+        <v>3.306886469122969</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3802,13 +4040,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.1067933405175204</v>
+        <v>0.1061064680797931</v>
       </c>
       <c r="C31">
-        <v>14826.14009650133</v>
+        <v>15032.00772652597</v>
       </c>
       <c r="D31">
-        <v>20188.34191948703</v>
+        <v>20394.20954951166</v>
       </c>
       <c r="E31">
         <v>2482.57484717295</v>
@@ -3835,37 +4073,37 @@
         <v>1184.4</v>
       </c>
       <c r="M31">
-        <v>386.7031891298718</v>
+        <v>370.9531643901091</v>
       </c>
       <c r="N31">
-        <v>797.6968108701283</v>
+        <v>813.446835609891</v>
       </c>
       <c r="O31">
-        <v>99.71210135876603</v>
+        <v>101.6808544512364</v>
       </c>
       <c r="P31">
-        <v>697.9847095113622</v>
+        <v>711.7659811586545</v>
       </c>
       <c r="Q31">
-        <v>1239.584709511362</v>
+        <v>1253.365981158654</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.1275983085062005</v>
+        <v>0.1275601078896832</v>
       </c>
       <c r="T31">
         <v>1.593656682778714</v>
       </c>
       <c r="U31">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V31">
         <v>0.125</v>
       </c>
       <c r="W31">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3873,7 +4111,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.062814151248768</v>
+        <v>3.192855901222177</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3884,13 +4122,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.1075010843257178</v>
+        <v>0.1061089970662496</v>
       </c>
       <c r="C32">
-        <v>14400.85103966397</v>
+        <v>14822.3237928184</v>
       </c>
       <c r="D32">
-        <v>19971.9391324078</v>
+        <v>20393.41188556223</v>
       </c>
       <c r="E32">
         <v>2691.461116931078</v>
@@ -3917,45 +4155,45 @@
         <v>1184.4</v>
       </c>
       <c r="M32">
-        <v>416.330910899622</v>
+        <v>383.7446528173542</v>
       </c>
       <c r="N32">
-        <v>768.0690891003781</v>
+        <v>800.6553471826459</v>
       </c>
       <c r="O32">
-        <v>96.00863613754726</v>
+        <v>100.0819183978307</v>
       </c>
       <c r="P32">
-        <v>672.0604529628308</v>
+        <v>700.5734287848152</v>
       </c>
       <c r="Q32">
-        <v>1213.660452962831</v>
+        <v>1242.173428784815</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.128659246359718</v>
+        <v>0.1286205502747634</v>
       </c>
       <c r="T32">
         <v>1.6143266786643</v>
       </c>
       <c r="U32">
-        <v>0.06643661666253409</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V32">
         <v>0.125</v>
       </c>
       <c r="W32">
-        <v>0.05813203957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y32">
-        <v>2.844852421456548</v>
+        <v>3.086427371181438</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3966,13 +4204,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.1075490781339152</v>
+        <v>0.1067896510527061</v>
       </c>
       <c r="C33">
-        <v>14177.45782393741</v>
+        <v>14400.9981229917</v>
       </c>
       <c r="D33">
-        <v>19957.43218643936</v>
+        <v>20180.97248549365</v>
       </c>
       <c r="E33">
         <v>2900.347386689205</v>
@@ -3999,37 +4237,37 @@
         <v>1184.4</v>
       </c>
       <c r="M33">
-        <v>430.2086079296094</v>
+        <v>412.7248271508542</v>
       </c>
       <c r="N33">
-        <v>754.1913920703907</v>
+        <v>771.6751728491458</v>
       </c>
       <c r="O33">
-        <v>94.27392400879884</v>
+        <v>96.45939660614323</v>
       </c>
       <c r="P33">
-        <v>659.9174680615919</v>
+        <v>675.2157762430027</v>
       </c>
       <c r="Q33">
-        <v>1201.517468061592</v>
+        <v>1216.815776243003</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.1297509360350766</v>
+        <v>0.1297117301202807</v>
       </c>
       <c r="T33">
         <v>1.635595804865411</v>
       </c>
       <c r="U33">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V33">
         <v>0.125</v>
       </c>
       <c r="W33">
-        <v>0.05813203957971733</v>
+        <v>0.05576953957971733</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4037,7 +4275,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>2.753082988506337</v>
+        <v>2.86970863414304</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4048,13 +4286,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.1075970719421127</v>
+        <v>0.1068140550391625</v>
       </c>
       <c r="C34">
-        <v>13954.08566763086</v>
+        <v>14184.57726584899</v>
       </c>
       <c r="D34">
-        <v>19942.94629989094</v>
+        <v>20173.43789810907</v>
       </c>
       <c r="E34">
         <v>3109.233656447333</v>
@@ -4081,37 +4319,37 @@
         <v>1184.4</v>
       </c>
       <c r="M34">
-        <v>444.0863049595969</v>
+        <v>426.0385312524947</v>
       </c>
       <c r="N34">
-        <v>740.3136950404032</v>
+        <v>758.3614687475053</v>
       </c>
       <c r="O34">
-        <v>92.5392118800504</v>
+        <v>94.79518359343817</v>
       </c>
       <c r="P34">
-        <v>647.7744831603528</v>
+        <v>663.5662851540671</v>
       </c>
       <c r="Q34">
-        <v>1189.374483160353</v>
+        <v>1205.166285154067</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.1308747342302987</v>
+        <v>0.1308350034906662</v>
       </c>
       <c r="T34">
         <v>1.657490493601848</v>
       </c>
       <c r="U34">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V34">
         <v>0.125</v>
       </c>
       <c r="W34">
-        <v>0.05813203957971733</v>
+        <v>0.05576953957971733</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4119,7 +4357,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.667049145115514</v>
+        <v>2.78003023932607</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4130,13 +4368,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.1076450657503101</v>
+        <v>0.106838459025619</v>
       </c>
       <c r="C35">
-        <v>13730.73452492034</v>
+        <v>13968.16203269888</v>
       </c>
       <c r="D35">
-        <v>19928.48142693854</v>
+        <v>20165.90893471709</v>
       </c>
       <c r="E35">
         <v>3318.11992620546</v>
@@ -4163,37 +4401,37 @@
         <v>1184.4</v>
       </c>
       <c r="M35">
-        <v>457.9640019895842</v>
+        <v>439.3522353541351</v>
       </c>
       <c r="N35">
-        <v>726.4359980104159</v>
+        <v>745.047764645865</v>
       </c>
       <c r="O35">
-        <v>90.80449975130199</v>
+        <v>93.13097058073312</v>
       </c>
       <c r="P35">
-        <v>635.6314982591139</v>
+        <v>651.9167940651319</v>
       </c>
       <c r="Q35">
-        <v>1177.231498259114</v>
+        <v>1193.516794065132</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.1320320786403036</v>
+        <v>0.1319918074094213</v>
       </c>
       <c r="T35">
         <v>1.680038755136388</v>
       </c>
       <c r="U35">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V35">
         <v>0.125</v>
       </c>
       <c r="W35">
-        <v>0.05813203957971733</v>
+        <v>0.05576953957971733</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4201,7 +4439,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.586229474051407</v>
+        <v>2.695786898740431</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4212,13 +4450,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.1076930595585075</v>
+        <v>0.1068628630120755</v>
       </c>
       <c r="C36">
-        <v>13507.40435011469</v>
+        <v>13751.75241724687</v>
       </c>
       <c r="D36">
-        <v>19914.03752189103</v>
+        <v>20158.38558902321</v>
       </c>
       <c r="E36">
         <v>3527.006195963588</v>
@@ -4245,37 +4483,37 @@
         <v>1184.4</v>
       </c>
       <c r="M36">
-        <v>471.8416990195716</v>
+        <v>452.6659394557756</v>
       </c>
       <c r="N36">
-        <v>712.5583009804284</v>
+        <v>731.7340605442245</v>
       </c>
       <c r="O36">
-        <v>89.06978762255355</v>
+        <v>91.46675756802806</v>
       </c>
       <c r="P36">
-        <v>623.4885133578748</v>
+        <v>640.2673029761964</v>
       </c>
       <c r="Q36">
-        <v>1165.088513357875</v>
+        <v>1181.867302976196</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1332244940930359</v>
+        <v>0.1331836659923812</v>
       </c>
       <c r="T36">
         <v>1.70327029732349</v>
       </c>
       <c r="U36">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V36">
         <v>0.125</v>
       </c>
       <c r="W36">
-        <v>0.05813203957971733</v>
+        <v>0.05576953957971733</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4283,7 +4521,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.510163901285189</v>
+        <v>2.616499048777477</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4294,13 +4532,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.108567928366705</v>
+        <v>0.106887266998532</v>
       </c>
       <c r="C37">
-        <v>13038.844873257</v>
+        <v>13535.34841320791</v>
       </c>
       <c r="D37">
-        <v>19654.36431479146</v>
+        <v>20150.86785474237</v>
       </c>
       <c r="E37">
         <v>3735.892465721715</v>
@@ -4327,45 +4565,45 @@
         <v>1184.4</v>
       </c>
       <c r="M37">
-        <v>505.4591485417022</v>
+        <v>465.9796435574161</v>
       </c>
       <c r="N37">
-        <v>678.9408514582979</v>
+        <v>718.4203564425841</v>
       </c>
       <c r="O37">
-        <v>84.86760643228723</v>
+        <v>89.80254455532301</v>
       </c>
       <c r="P37">
-        <v>594.0732450260107</v>
+        <v>628.617811887261</v>
       </c>
       <c r="Q37">
-        <v>1135.673245026011</v>
+        <v>1170.217811887261</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.134453599252006</v>
+        <v>0.1344121971471245</v>
       </c>
       <c r="T37">
         <v>1.727216656193272</v>
       </c>
       <c r="U37">
-        <v>0.06913661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V37">
         <v>0.125</v>
       </c>
       <c r="W37">
-        <v>0.06049453957971733</v>
+        <v>0.05576953957971733</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y37">
-        <v>2.343216070808308</v>
+        <v>2.541741933098121</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4376,13 +4614,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.1086395471749024</v>
+        <v>0.1080141709849885</v>
       </c>
       <c r="C38">
-        <v>12809.00070975029</v>
+        <v>12985.31965139799</v>
       </c>
       <c r="D38">
-        <v>19633.40642104288</v>
+        <v>19809.72536269057</v>
       </c>
       <c r="E38">
         <v>3944.778735479842</v>
@@ -4409,37 +4647,37 @@
         <v>1184.4</v>
       </c>
       <c r="M38">
-        <v>519.9008385000365</v>
+        <v>505.6130176485806</v>
       </c>
       <c r="N38">
-        <v>664.4991614999636</v>
+        <v>678.7869823514195</v>
       </c>
       <c r="O38">
-        <v>83.06239518749545</v>
+        <v>84.84837279392744</v>
       </c>
       <c r="P38">
-        <v>581.4367663124682</v>
+        <v>593.9386095574921</v>
       </c>
       <c r="Q38">
-        <v>1123.036766312468</v>
+        <v>1135.538609557492</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.135721113947194</v>
+        <v>0.1356791199004535</v>
       </c>
       <c r="T38">
         <v>1.751911338777735</v>
       </c>
       <c r="U38">
-        <v>0.06913661666253409</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V38">
         <v>0.125</v>
       </c>
       <c r="W38">
-        <v>0.06049453957971733</v>
+        <v>0.05883203957971733</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4447,7 +4685,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.278126735508077</v>
+        <v>2.342502978875439</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4458,13 +4696,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.1102327909830998</v>
+        <v>0.1080691999714449</v>
       </c>
       <c r="C39">
-        <v>12145.17082249396</v>
+        <v>12760.07025716571</v>
       </c>
       <c r="D39">
-        <v>19178.46280354468</v>
+        <v>19793.36223821642</v>
       </c>
       <c r="E39">
         <v>4153.66500523797</v>
@@ -4491,45 +4729,45 @@
         <v>1184.4</v>
       </c>
       <c r="M39">
-        <v>570.6678507693092</v>
+        <v>519.6578236943744</v>
       </c>
       <c r="N39">
-        <v>613.7321492306909</v>
+        <v>664.7421763056257</v>
       </c>
       <c r="O39">
-        <v>76.71651865383636</v>
+        <v>83.09277203820321</v>
       </c>
       <c r="P39">
-        <v>537.0156305768545</v>
+        <v>581.6494042674225</v>
       </c>
       <c r="Q39">
-        <v>1078.615630576855</v>
+        <v>1123.249404267423</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.137028867204134</v>
+        <v>0.1369862624237294</v>
       </c>
       <c r="T39">
         <v>1.777389979539482</v>
       </c>
       <c r="U39">
-        <v>0.0738366166625341</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V39">
         <v>0.125</v>
       </c>
       <c r="W39">
-        <v>0.06460703957971733</v>
+        <v>0.05883203957971733</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y39">
-        <v>2.075462983245556</v>
+        <v>2.279192087554482</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4540,13 +4778,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.1103455347912973</v>
+        <v>0.1090552289579014</v>
       </c>
       <c r="C40">
-        <v>11904.88853017011</v>
+        <v>12262.49866178473</v>
       </c>
       <c r="D40">
-        <v>19147.06678097896</v>
+        <v>19504.67691259358</v>
       </c>
       <c r="E40">
         <v>4362.551274996098</v>
@@ -4573,37 +4811,37 @@
         <v>1184.4</v>
       </c>
       <c r="M40">
-        <v>586.0913061955068</v>
+        <v>555.9281288424331</v>
       </c>
       <c r="N40">
-        <v>598.3086938044933</v>
+        <v>628.471871157567</v>
       </c>
       <c r="O40">
-        <v>74.78858672556166</v>
+        <v>78.55898389469587</v>
       </c>
       <c r="P40">
-        <v>523.5201070789316</v>
+        <v>549.9128872628711</v>
       </c>
       <c r="Q40">
-        <v>1065.120107078932</v>
+        <v>1091.512887262871</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1383788060500075</v>
+        <v>0.138335570834853</v>
       </c>
       <c r="T40">
         <v>1.803690511938705</v>
       </c>
       <c r="U40">
-        <v>0.0738366166625341</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V40">
         <v>0.125</v>
       </c>
       <c r="W40">
-        <v>0.06460703957971733</v>
+        <v>0.06128203957971733</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4611,7 +4849,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.020845536318041</v>
+        <v>2.130491224587225</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4622,13 +4860,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.1152357785994947</v>
+        <v>0.1091347579443579</v>
       </c>
       <c r="C41">
-        <v>10426.57225594109</v>
+        <v>12030.69479520049</v>
       </c>
       <c r="D41">
-        <v>17877.63677650806</v>
+        <v>19481.75931576746</v>
       </c>
       <c r="E41">
         <v>4571.437544754224</v>
@@ -4655,45 +4893,45 @@
         <v>1184.4</v>
       </c>
       <c r="M41">
-        <v>715.5666649096418</v>
+        <v>570.5578164435498</v>
       </c>
       <c r="N41">
-        <v>468.8333350903583</v>
+        <v>613.8421835564503</v>
       </c>
       <c r="O41">
-        <v>58.60416688629479</v>
+        <v>76.73027294455629</v>
       </c>
       <c r="P41">
-        <v>410.2291682040635</v>
+        <v>537.111910611894</v>
       </c>
       <c r="Q41">
-        <v>951.8291682040635</v>
+        <v>1078.711910611894</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1397730051859097</v>
+        <v>0.1397291188660133</v>
       </c>
       <c r="T41">
         <v>1.830853356875607</v>
       </c>
       <c r="U41">
-        <v>0.08783661666253409</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V41">
         <v>0.125</v>
       </c>
       <c r="W41">
-        <v>0.07685703957971733</v>
+        <v>0.06128203957971733</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y41">
-        <v>1.655191693634248</v>
+        <v>2.075863244469604</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4704,13 +4942,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.1154710224076921</v>
+        <v>0.1092142869308144</v>
       </c>
       <c r="C42">
-        <v>10160.85025933911</v>
+        <v>11798.94472082746</v>
       </c>
       <c r="D42">
-        <v>17820.80104966421</v>
+        <v>19458.89551115256</v>
       </c>
       <c r="E42">
         <v>4780.323814512352</v>
@@ -4737,45 +4975,45 @@
         <v>1184.4</v>
       </c>
       <c r="M42">
-        <v>733.9145281124531</v>
+        <v>585.1875040446664</v>
       </c>
       <c r="N42">
-        <v>450.485471887547</v>
+        <v>599.2124959553337</v>
       </c>
       <c r="O42">
-        <v>56.31068398594337</v>
+        <v>74.90156199441671</v>
       </c>
       <c r="P42">
-        <v>394.1747879016036</v>
+        <v>524.3109339609169</v>
       </c>
       <c r="Q42">
-        <v>935.7747879016036</v>
+        <v>1065.910933960917</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.141213677626342</v>
+        <v>0.1411691184982124</v>
       </c>
       <c r="T42">
         <v>1.858921629977073</v>
       </c>
       <c r="U42">
-        <v>0.08783661666253409</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V42">
         <v>0.125</v>
       </c>
       <c r="W42">
-        <v>0.07685703957971733</v>
+        <v>0.06128203957971733</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y42">
-        <v>1.613811901293391</v>
+        <v>2.023966663357864</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4786,13 +5024,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.1157062662158896</v>
+        <v>0.1120920659172709</v>
       </c>
       <c r="C43">
-        <v>9895.488496342592</v>
+        <v>10797.35973266416</v>
       </c>
       <c r="D43">
-        <v>17764.32555642582</v>
+        <v>18666.19679274738</v>
       </c>
       <c r="E43">
         <v>4989.21008427048</v>
@@ -4819,45 +5057,45 @@
         <v>1184.4</v>
       </c>
       <c r="M43">
-        <v>752.2623913152645</v>
+        <v>666.6190207144324</v>
       </c>
       <c r="N43">
-        <v>432.1376086847356</v>
+        <v>517.7809792855677</v>
       </c>
       <c r="O43">
-        <v>54.01720108559195</v>
+        <v>64.72262241069596</v>
       </c>
       <c r="P43">
-        <v>378.1204075991436</v>
+        <v>453.0583568748717</v>
       </c>
       <c r="Q43">
-        <v>919.7204075991436</v>
+        <v>994.6583568748717</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1427031864206872</v>
+        <v>0.1426579316772657</v>
       </c>
       <c r="T43">
         <v>1.887941369963334</v>
       </c>
       <c r="U43">
-        <v>0.08783661666253409</v>
+        <v>0.07783661666253411</v>
       </c>
       <c r="V43">
         <v>0.125</v>
       </c>
       <c r="W43">
-        <v>0.07685703957971733</v>
+        <v>0.06810703957971734</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y43">
-        <v>1.574450635408187</v>
+        <v>1.776726980773289</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4868,13 +5106,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.115941510024087</v>
+        <v>0.1136730949037273</v>
       </c>
       <c r="C44">
-        <v>9630.483552946509</v>
+        <v>10179.85725278575</v>
       </c>
       <c r="D44">
-        <v>17708.20688278786</v>
+        <v>18257.58058262711</v>
       </c>
       <c r="E44">
         <v>5198.096354028607</v>
@@ -4901,37 +5139,37 @@
         <v>1184.4</v>
       </c>
       <c r="M44">
-        <v>770.6102545180757</v>
+        <v>717.0935922060435</v>
       </c>
       <c r="N44">
-        <v>413.7897454819243</v>
+        <v>467.3064077939566</v>
       </c>
       <c r="O44">
-        <v>51.72371818524054</v>
+        <v>58.41330097424458</v>
       </c>
       <c r="P44">
-        <v>362.0660272966838</v>
+        <v>408.893106819712</v>
       </c>
       <c r="Q44">
-        <v>903.6660272966838</v>
+        <v>950.493106819712</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1442440575872512</v>
+        <v>0.1441980832418035</v>
       </c>
       <c r="T44">
         <v>1.917961790638776</v>
       </c>
       <c r="U44">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V44">
         <v>0.125</v>
       </c>
       <c r="W44">
-        <v>0.07685703957971733</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4939,7 +5177,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>1.536963715517516</v>
+        <v>1.65166724800364</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4950,13 +5188,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.1161767538322844</v>
+        <v>0.1138549988901838</v>
       </c>
       <c r="C45">
-        <v>9365.832058150278</v>
+        <v>9925.102654381604</v>
       </c>
       <c r="D45">
-        <v>17652.44165774976</v>
+        <v>18211.71225398108</v>
       </c>
       <c r="E45">
         <v>5406.982623786735</v>
@@ -4983,37 +5221,37 @@
         <v>1184.4</v>
       </c>
       <c r="M45">
-        <v>788.9581177208871</v>
+        <v>734.1672491633303</v>
       </c>
       <c r="N45">
-        <v>395.441882279113</v>
+        <v>450.2327508366698</v>
       </c>
       <c r="O45">
-        <v>49.43023528488912</v>
+        <v>56.27909385458372</v>
       </c>
       <c r="P45">
-        <v>346.0116469942238</v>
+        <v>393.953656982086</v>
       </c>
       <c r="Q45">
-        <v>887.6116469942239</v>
+        <v>935.5536569820861</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1458389944087824</v>
+        <v>0.1457922752121147</v>
       </c>
       <c r="T45">
         <v>1.949035559408094</v>
       </c>
       <c r="U45">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V45">
         <v>0.125</v>
       </c>
       <c r="W45">
-        <v>0.07685703957971733</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5259,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>1.501220373296178</v>
+        <v>1.613256381770997</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5032,13 +5270,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.1359085000325571</v>
+        <v>0.1140369028766403</v>
       </c>
       <c r="C46">
-        <v>5468.483215052634</v>
+        <v>9670.577947467631</v>
       </c>
       <c r="D46">
-        <v>13963.97908441024</v>
+        <v>18166.07381682524</v>
       </c>
       <c r="E46">
         <v>5615.868893544863</v>
@@ -5065,45 +5303,45 @@
         <v>1184.4</v>
       </c>
       <c r="M46">
-        <v>1257.664778522221</v>
+        <v>751.2409061206171</v>
       </c>
       <c r="N46">
-        <v>-73.26477852222138</v>
+        <v>433.159093879383</v>
       </c>
       <c r="O46">
-        <v>-9.158097315277672</v>
+        <v>54.14488673492288</v>
       </c>
       <c r="P46">
-        <v>-64.1066812069437</v>
+        <v>379.0142071444602</v>
       </c>
       <c r="Q46">
-        <v>477.4933187930563</v>
+        <v>920.6142071444601</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.147835674228588</v>
+        <v>0.1474434026099369</v>
       </c>
       <c r="T46">
-        <v>1.987936389954748</v>
+        <v>1.981219105633459</v>
       </c>
       <c r="U46">
-        <v>0.1368366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V46">
-        <v>0.1177181730206052</v>
+        <v>0.125</v>
       </c>
       <c r="W46">
-        <v>0.1207284601466997</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y46">
-        <v>0.9417453841648418</v>
+        <v>1.576591464003474</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5114,13 +5352,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.1368188661991825</v>
+        <v>0.1142188068630968</v>
       </c>
       <c r="C47">
-        <v>5126.265161043108</v>
+        <v>9416.281408044244</v>
       </c>
       <c r="D47">
-        <v>13830.64730015884</v>
+        <v>18120.66354715998</v>
       </c>
       <c r="E47">
         <v>5824.755163302991</v>
@@ -5147,45 +5385,45 @@
         <v>1184.4</v>
       </c>
       <c r="M47">
-        <v>1286.248068943181</v>
+        <v>768.3145630779039</v>
       </c>
       <c r="N47">
-        <v>-101.848068943181</v>
+        <v>416.0854369220962</v>
       </c>
       <c r="O47">
-        <v>-12.73100861789763</v>
+        <v>52.01067961526202</v>
       </c>
       <c r="P47">
-        <v>-89.1170603252834</v>
+        <v>364.0747573068342</v>
       </c>
       <c r="Q47">
-        <v>452.4829396747166</v>
+        <v>905.6747573068342</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1496908683054714</v>
+        <v>0.1491545710040436</v>
       </c>
       <c r="T47">
-        <v>2.024080687953925</v>
+        <v>2.014572962630655</v>
       </c>
       <c r="U47">
-        <v>0.1368366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V47">
-        <v>0.1151022136201473</v>
+        <v>0.125</v>
       </c>
       <c r="W47">
-        <v>0.1210864191803849</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y47">
-        <v>0.9208177089611785</v>
+        <v>1.54155609813673</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5196,13 +5434,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.1377292323658078</v>
+        <v>0.1144007108495533</v>
       </c>
       <c r="C48">
-        <v>4786.569200056472</v>
+        <v>9162.211329307022</v>
       </c>
       <c r="D48">
-        <v>13699.83760893034</v>
+        <v>18075.47973818089</v>
       </c>
       <c r="E48">
         <v>6033.641433061119</v>
@@ -5229,45 +5467,45 @@
         <v>1184.4</v>
       </c>
       <c r="M48">
-        <v>1314.831359364141</v>
+        <v>785.3882200351907</v>
       </c>
       <c r="N48">
-        <v>-130.4313593641407</v>
+        <v>399.0117799648094</v>
       </c>
       <c r="O48">
-        <v>-16.30391992051759</v>
+        <v>49.87647249560118</v>
       </c>
       <c r="P48">
-        <v>-114.1274394436231</v>
+        <v>349.1353074692082</v>
       </c>
       <c r="Q48">
-        <v>427.4725605563769</v>
+        <v>890.7353074692082</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1516147732740912</v>
+        <v>0.1509291160053394</v>
       </c>
       <c r="T48">
-        <v>2.061563663656775</v>
+        <v>2.049162147664785</v>
       </c>
       <c r="U48">
-        <v>0.1368366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V48">
-        <v>0.1125999915849267</v>
+        <v>0.125</v>
       </c>
       <c r="W48">
-        <v>0.1214288147778229</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y48">
-        <v>0.9007999326794137</v>
+        <v>1.508044009046801</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5278,13 +5516,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.1386395985324332</v>
+        <v>0.1204223648360098</v>
       </c>
       <c r="C49">
-        <v>4449.324441022447</v>
+        <v>7575.078742588636</v>
       </c>
       <c r="D49">
-        <v>13571.47911965444</v>
+        <v>16697.23342122063</v>
       </c>
       <c r="E49">
         <v>6242.527702819245</v>
@@ -5311,45 +5549,45 @@
         <v>1184.4</v>
       </c>
       <c r="M49">
-        <v>1343.4146497851</v>
+        <v>941.8725734290517</v>
       </c>
       <c r="N49">
-        <v>-159.0146497851001</v>
+        <v>242.5274265709484</v>
       </c>
       <c r="O49">
-        <v>-19.87683122313751</v>
+        <v>30.31592832136855</v>
       </c>
       <c r="P49">
-        <v>-139.1378185619626</v>
+        <v>212.2114982495798</v>
       </c>
       <c r="Q49">
-        <v>402.4621814380374</v>
+        <v>753.8114982495798</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1536112784302061</v>
+        <v>0.1527706249689483</v>
       </c>
       <c r="T49">
-        <v>2.10046109127294</v>
+        <v>2.085056584964353</v>
       </c>
       <c r="U49">
-        <v>0.1368366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V49">
-        <v>0.1102042470831198</v>
+        <v>0.125</v>
       </c>
       <c r="W49">
-        <v>0.121756640349838</v>
+        <v>0.08394453957971734</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y49">
-        <v>0.8816339766649582</v>
+        <v>1.257494945083691</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5360,13 +5598,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.1395499646990585</v>
+        <v>0.1333111457448236</v>
       </c>
       <c r="C50">
-        <v>4114.462625020498</v>
+        <v>5023.467171492048</v>
       </c>
       <c r="D50">
-        <v>13445.50357341061</v>
+        <v>14354.50811988216</v>
       </c>
       <c r="E50">
         <v>6451.413972577371</v>
@@ -5393,37 +5631,37 @@
         <v>1184.4</v>
       </c>
       <c r="M50">
-        <v>1371.99794020606</v>
+        <v>1248.671486540861</v>
       </c>
       <c r="N50">
-        <v>-187.5979402060595</v>
+        <v>-64.27148654086091</v>
       </c>
       <c r="O50">
-        <v>-23.44974252575744</v>
+        <v>-8.033935817607613</v>
       </c>
       <c r="P50">
-        <v>-164.1481976803021</v>
+        <v>-56.23755072325329</v>
       </c>
       <c r="Q50">
-        <v>377.4518023196979</v>
+        <v>485.3624492767467</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1556845722461717</v>
+        <v>0.1550406896418738</v>
       </c>
       <c r="T50">
-        <v>2.14085457379742</v>
+        <v>2.129304370708825</v>
       </c>
       <c r="U50">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V50">
-        <v>0.1079083252688881</v>
+        <v>0.1185660132355039</v>
       </c>
       <c r="W50">
-        <v>0.1220708065230192</v>
+        <v>0.1097708065230192</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5669,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.8632666021511051</v>
+        <v>0.9485281058840309</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5442,13 +5680,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.1404603308656838</v>
+        <v>0.1340985119114489</v>
       </c>
       <c r="C51">
-        <v>3781.918004240362</v>
+        <v>4692.591104689331</v>
       </c>
       <c r="D51">
-        <v>13321.84522238861</v>
+        <v>14232.51832283758</v>
       </c>
       <c r="E51">
         <v>6660.300242335499</v>
@@ -5475,37 +5713,37 @@
         <v>1184.4</v>
       </c>
       <c r="M51">
-        <v>1400.581230627019</v>
+        <v>1274.685475843796</v>
       </c>
       <c r="N51">
-        <v>-216.1812306270192</v>
+        <v>-90.28547584379567</v>
       </c>
       <c r="O51">
-        <v>-27.0226538283774</v>
+        <v>-11.28568448047446</v>
       </c>
       <c r="P51">
-        <v>-189.1585767986418</v>
+        <v>-78.99979136332121</v>
       </c>
       <c r="Q51">
-        <v>352.4414232013582</v>
+        <v>462.6002086366788</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1578391717019789</v>
+        <v>0.1571826639485772</v>
       </c>
       <c r="T51">
-        <v>2.182832114460115</v>
+        <v>2.171055436801155</v>
       </c>
       <c r="U51">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V51">
-        <v>0.1057061145491149</v>
+        <v>0.1161462986796772</v>
       </c>
       <c r="W51">
-        <v>0.1223721495870909</v>
+        <v>0.1100721495870909</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5751,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.8456489163929192</v>
+        <v>0.9291703894374179</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5524,13 +5762,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.1413706970323092</v>
+        <v>0.1348858780780743</v>
       </c>
       <c r="C52">
-        <v>3451.627227560935</v>
+        <v>4363.77099239555</v>
       </c>
       <c r="D52">
-        <v>13200.44071546731</v>
+        <v>14112.58448030192</v>
       </c>
       <c r="E52">
         <v>6869.186512093627</v>
@@ -5557,37 +5795,37 @@
         <v>1184.4</v>
       </c>
       <c r="M52">
-        <v>1429.164521047979</v>
+        <v>1300.699465146731</v>
       </c>
       <c r="N52">
-        <v>-244.7645210479789</v>
+        <v>-116.2994651467304</v>
       </c>
       <c r="O52">
-        <v>-30.59556513099736</v>
+        <v>-14.5374331433413</v>
       </c>
       <c r="P52">
-        <v>-214.1689559169815</v>
+        <v>-101.7620320033891</v>
       </c>
       <c r="Q52">
-        <v>327.4310440830185</v>
+        <v>439.8379679966109</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1600799551360185</v>
+        <v>0.1594103172275487</v>
       </c>
       <c r="T52">
-        <v>2.226488756749317</v>
+        <v>2.214476545537178</v>
       </c>
       <c r="U52">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V52">
-        <v>0.1035919922581326</v>
+        <v>0.1138233727060837</v>
       </c>
       <c r="W52">
-        <v>0.1226614389285998</v>
+        <v>0.1103614389285998</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5833,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.8287359380650607</v>
+        <v>0.9105869816486695</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5606,13 +5844,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.1422810631989345</v>
+        <v>0.1356732442446996</v>
       </c>
       <c r="C53">
-        <v>3123.529232329087</v>
+        <v>4036.955293900839</v>
       </c>
       <c r="D53">
-        <v>13081.22898999359</v>
+        <v>13994.65505156534</v>
       </c>
       <c r="E53">
         <v>7078.072781851755</v>
@@ -5639,37 +5877,37 @@
         <v>1184.4</v>
       </c>
       <c r="M53">
-        <v>1457.747811468939</v>
+        <v>1326.713454449665</v>
       </c>
       <c r="N53">
-        <v>-273.3478114689385</v>
+        <v>-142.313454449665</v>
       </c>
       <c r="O53">
-        <v>-34.16847643361731</v>
+        <v>-17.78918180620812</v>
       </c>
       <c r="P53">
-        <v>-239.1793350353212</v>
+        <v>-124.5242726434568</v>
       </c>
       <c r="Q53">
-        <v>302.4206649646788</v>
+        <v>417.0757273565432</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1624121991183863</v>
+        <v>0.1617288951301517</v>
       </c>
       <c r="T53">
-        <v>2.271927302805426</v>
+        <v>2.259669944425692</v>
       </c>
       <c r="U53">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V53">
-        <v>0.1015607767236594</v>
+        <v>0.1115915418687095</v>
       </c>
       <c r="W53">
-        <v>0.1229393835900495</v>
+        <v>0.1106393835900495</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5915,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.8124862137892752</v>
+        <v>0.892732334949676</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5688,13 +5926,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.1885345307351</v>
+        <v>0.1364606104113249</v>
       </c>
       <c r="C54">
-        <v>-1199.699283284192</v>
+        <v>3712.094176983583</v>
       </c>
       <c r="D54">
-        <v>8966.886744138437</v>
+        <v>13878.68020440621</v>
       </c>
       <c r="E54">
         <v>7286.959051609883</v>
@@ -5721,45 +5959,45 @@
         <v>1184.4</v>
       </c>
       <c r="M54">
-        <v>2408.52220561808</v>
+        <v>1352.7274437526</v>
       </c>
       <c r="N54">
-        <v>-1224.12220561808</v>
+        <v>-168.3274437525997</v>
       </c>
       <c r="O54">
-        <v>-153.0152757022599</v>
+        <v>-21.04093046907497</v>
       </c>
       <c r="P54">
-        <v>-1071.10692991582</v>
+        <v>-147.2865132835248</v>
       </c>
       <c r="Q54">
-        <v>-529.5069299158196</v>
+        <v>394.3134867164753</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1673314144532281</v>
+        <v>0.1641440804453632</v>
       </c>
       <c r="T54">
-        <v>2.367767186729234</v>
+        <v>2.306746401601227</v>
       </c>
       <c r="U54">
-        <v>0.2217366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V54">
-        <v>0.0614692277508013</v>
+        <v>0.1094455506789266</v>
       </c>
       <c r="W54">
-        <v>0.2081066380722127</v>
+        <v>0.1109066380722127</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y54">
-        <v>0.4917538220064104</v>
+        <v>0.8755644054314129</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5770,13 +6008,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.1902938969017254</v>
+        <v>0.1372479765779503</v>
       </c>
       <c r="C55">
-        <v>-1514.594025557142</v>
+        <v>3389.139447700341</v>
       </c>
       <c r="D55">
-        <v>8860.878271623613</v>
+        <v>13764.6117448811</v>
       </c>
       <c r="E55">
         <v>7495.84532136801</v>
@@ -5803,45 +6041,45 @@
         <v>1184.4</v>
       </c>
       <c r="M55">
-        <v>2454.839940341504</v>
+        <v>1378.741433055534</v>
       </c>
       <c r="N55">
-        <v>-1270.439940341504</v>
+        <v>-194.3414330555343</v>
       </c>
       <c r="O55">
-        <v>-158.804992542688</v>
+        <v>-24.29267913194178</v>
       </c>
       <c r="P55">
-        <v>-1111.634947798816</v>
+        <v>-170.0487539235925</v>
       </c>
       <c r="Q55">
-        <v>-570.0349477988156</v>
+        <v>371.5512460764076</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1699171892288287</v>
+        <v>0.1666620396037752</v>
       </c>
       <c r="T55">
-        <v>2.418145211978793</v>
+        <v>2.355826112273594</v>
       </c>
       <c r="U55">
-        <v>0.2217366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V55">
-        <v>0.06030943100078619</v>
+        <v>0.1073805402887582</v>
       </c>
       <c r="W55">
-        <v>0.2083638074795772</v>
+        <v>0.1111638074795772</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y55">
-        <v>0.4824754480062895</v>
+        <v>0.8590443223100656</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5852,13 +6090,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.1920532630683507</v>
+        <v>0.1380353427445756</v>
       </c>
       <c r="C56">
-        <v>-1827.011543972312</v>
+        <v>3068.044483609909</v>
       </c>
       <c r="D56">
-        <v>8757.347022966571</v>
+        <v>13652.40305054879</v>
       </c>
       <c r="E56">
         <v>7704.731591126138</v>
@@ -5885,45 +6123,45 @@
         <v>1184.4</v>
       </c>
       <c r="M56">
-        <v>2501.157675064928</v>
+        <v>1404.755422358469</v>
       </c>
       <c r="N56">
-        <v>-1316.757675064928</v>
+        <v>-220.3554223584688</v>
       </c>
       <c r="O56">
-        <v>-164.594709383116</v>
+        <v>-27.5444277948086</v>
       </c>
       <c r="P56">
-        <v>-1152.162965681812</v>
+        <v>-192.8109945636602</v>
       </c>
       <c r="Q56">
-        <v>-610.5629656818122</v>
+        <v>348.7890054363398</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1726153889946727</v>
+        <v>0.1692894752473356</v>
       </c>
       <c r="T56">
-        <v>2.470713586152244</v>
+        <v>2.407039723409976</v>
       </c>
       <c r="U56">
-        <v>0.2217366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V56">
-        <v>0.05919258968595682</v>
+        <v>0.1053920117648923</v>
       </c>
       <c r="W56">
-        <v>0.2086114520940764</v>
+        <v>0.1114114520940764</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y56">
-        <v>0.4735407174876546</v>
+        <v>0.8431360941191385</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5934,13 +6172,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.1938126292349761</v>
+        <v>0.138822708911201</v>
       </c>
       <c r="C57">
-        <v>-2137.037667968421</v>
+        <v>2748.764170237042</v>
       </c>
       <c r="D57">
-        <v>8656.20716872859</v>
+        <v>13542.00900693405</v>
       </c>
       <c r="E57">
         <v>7913.617860884266</v>
@@ -5967,45 +6205,45 @@
         <v>1184.4</v>
       </c>
       <c r="M57">
-        <v>2547.475409788353</v>
+        <v>1430.769411661404</v>
       </c>
       <c r="N57">
-        <v>-1363.075409788353</v>
+        <v>-246.3694116614035</v>
       </c>
       <c r="O57">
-        <v>-170.3844262235442</v>
+        <v>-30.79617645767544</v>
       </c>
       <c r="P57">
-        <v>-1192.690983564809</v>
+        <v>-215.5732352037281</v>
       </c>
       <c r="Q57">
-        <v>-651.0909835648091</v>
+        <v>326.0267647962719</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1754335087501099</v>
+        <v>0.1720336858083875</v>
       </c>
       <c r="T57">
-        <v>2.525618332511183</v>
+        <v>2.460529495041309</v>
       </c>
       <c r="U57">
-        <v>0.2217366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V57">
-        <v>0.05811636078257577</v>
+        <v>0.103475793369167</v>
       </c>
       <c r="W57">
-        <v>0.2088500914498666</v>
+        <v>0.1116500914498666</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y57">
-        <v>0.4649308862606062</v>
+        <v>0.8278063469533359</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6016,13 +6254,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1955719954016014</v>
+        <v>0.1396100750778263</v>
       </c>
       <c r="C58">
-        <v>-2444.754307228126</v>
+        <v>2431.25484059404</v>
       </c>
       <c r="D58">
-        <v>8557.376799227013</v>
+        <v>13433.38594704918</v>
       </c>
       <c r="E58">
         <v>8122.504130642394</v>
@@ -6049,45 +6287,45 @@
         <v>1184.4</v>
       </c>
       <c r="M58">
-        <v>2593.793144511778</v>
+        <v>1456.783400964338</v>
       </c>
       <c r="N58">
-        <v>-1409.393144511778</v>
+        <v>-272.3834009643381</v>
       </c>
       <c r="O58">
-        <v>-176.1741430639722</v>
+        <v>-34.04792512054226</v>
       </c>
       <c r="P58">
-        <v>-1233.219001447806</v>
+        <v>-238.3354758437958</v>
       </c>
       <c r="Q58">
-        <v>-691.6190014478055</v>
+        <v>303.2645241562042</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.178379724858067</v>
+        <v>0.1749026332131235</v>
       </c>
       <c r="T58">
-        <v>2.583018749159165</v>
+        <v>2.516450619928611</v>
       </c>
       <c r="U58">
-        <v>0.2217366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V58">
-        <v>0.05707856862574406</v>
+        <v>0.1016280113447176</v>
       </c>
       <c r="W58">
-        <v>0.2090802079715214</v>
+        <v>0.1118802079715213</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y58">
-        <v>0.4566285490059525</v>
+        <v>0.8130240907577406</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6098,13 +6336,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1973313615682268</v>
+        <v>0.1571043524868894</v>
       </c>
       <c r="C59">
-        <v>-2750.239672916889</v>
+        <v>190.3997927813034</v>
       </c>
       <c r="D59">
-        <v>8460.777703296377</v>
+        <v>11401.41716899457</v>
       </c>
       <c r="E59">
         <v>8331.39040040052</v>
@@ -6131,45 +6369,45 @@
         <v>1184.4</v>
       </c>
       <c r="M59">
-        <v>2640.110879235202</v>
+        <v>1818.561180276487</v>
       </c>
       <c r="N59">
-        <v>-1455.710879235202</v>
+        <v>-634.1611802764867</v>
       </c>
       <c r="O59">
-        <v>-181.9638599044003</v>
+        <v>-79.27014753456083</v>
       </c>
       <c r="P59">
-        <v>-1273.747019330802</v>
+        <v>-554.8910327419259</v>
       </c>
       <c r="Q59">
-        <v>-732.147019330802</v>
+        <v>-13.29103274192585</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1814629742733709</v>
+        <v>0.1793769066423537</v>
       </c>
       <c r="T59">
-        <v>2.643088952627983</v>
+        <v>2.603662537025062</v>
       </c>
       <c r="U59">
-        <v>0.2217366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V59">
-        <v>0.05607719022880119</v>
+        <v>0.08141051376533347</v>
       </c>
       <c r="W59">
-        <v>0.2093022502292584</v>
+        <v>0.1403022502292584</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y59">
-        <v>0.4486175218304095</v>
+        <v>0.6512841101226678</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6180,13 +6418,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1990907277348521</v>
+        <v>0.1902237930531016</v>
       </c>
       <c r="C60">
-        <v>-3053.568484104535</v>
+        <v>-2556.614113664466</v>
       </c>
       <c r="D60">
-        <v>8366.335161866857</v>
+        <v>8863.289532306926</v>
       </c>
       <c r="E60">
         <v>8540.276670158646</v>
@@ -6213,37 +6451,37 @@
         <v>1184.4</v>
       </c>
       <c r="M60">
-        <v>2686.428613958627</v>
+        <v>2504.697559269056</v>
       </c>
       <c r="N60">
-        <v>-1502.028613958626</v>
+        <v>-1320.297559269055</v>
       </c>
       <c r="O60">
-        <v>-187.7535767448283</v>
+        <v>-165.0371949086319</v>
       </c>
       <c r="P60">
-        <v>-1314.275037213798</v>
+        <v>-1155.260364360423</v>
       </c>
       <c r="Q60">
-        <v>-772.6750372137982</v>
+        <v>-613.6603643604234</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1846930450894035</v>
+        <v>0.1842955815614262</v>
       </c>
       <c r="T60">
-        <v>2.706019641976268</v>
+        <v>2.699536666322596</v>
       </c>
       <c r="U60">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V60">
-        <v>0.05511034212140808</v>
+        <v>0.05910893291372287</v>
       </c>
       <c r="W60">
-        <v>0.2095166358574183</v>
+        <v>0.1945166358574183</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6489,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.4408827369712646</v>
+        <v>0.4728714633097829</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6262,13 +6500,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.2008500939014774</v>
+        <v>0.1918331592197269</v>
       </c>
       <c r="C61">
-        <v>-3354.812160514462</v>
+        <v>-2860.352862211954</v>
       </c>
       <c r="D61">
-        <v>8273.977755215057</v>
+        <v>8768.437053517566</v>
       </c>
       <c r="E61">
         <v>8749.162939916774</v>
@@ -6295,37 +6533,37 @@
         <v>1184.4</v>
       </c>
       <c r="M61">
-        <v>2732.746348682051</v>
+        <v>2547.881999946108</v>
       </c>
       <c r="N61">
-        <v>-1548.346348682051</v>
+        <v>-1363.481999946108</v>
       </c>
       <c r="O61">
-        <v>-193.5432935852564</v>
+        <v>-170.4352499932635</v>
       </c>
       <c r="P61">
-        <v>-1354.803055096795</v>
+        <v>-1193.046749952845</v>
       </c>
       <c r="Q61">
-        <v>-813.2030550967946</v>
+        <v>-651.4467499528447</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1880806803354864</v>
+        <v>0.1876735225751195</v>
       </c>
       <c r="T61">
-        <v>2.772020121048859</v>
+        <v>2.765379024037781</v>
       </c>
       <c r="U61">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V61">
-        <v>0.05417626852612997</v>
+        <v>0.05810708659315129</v>
       </c>
       <c r="W61">
-        <v>0.2097237541761491</v>
+        <v>0.1947237541761491</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6571,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.4334101482090398</v>
+        <v>0.4648566927452104</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6344,13 +6582,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.2026094600681028</v>
+        <v>0.1934425253863523</v>
       </c>
       <c r="C62">
-        <v>-3654.039002645492</v>
+        <v>-3162.082936924771</v>
       </c>
       <c r="D62">
-        <v>8183.637182842156</v>
+        <v>8675.593248562876</v>
       </c>
       <c r="E62">
         <v>8958.049209674902</v>
@@ -6377,37 +6615,37 @@
         <v>1184.4</v>
       </c>
       <c r="M62">
-        <v>2779.064083405476</v>
+        <v>2591.066440623161</v>
       </c>
       <c r="N62">
-        <v>-1594.664083405476</v>
+        <v>-1406.666440623161</v>
       </c>
       <c r="O62">
-        <v>-199.3330104256845</v>
+        <v>-175.8333050778951</v>
       </c>
       <c r="P62">
-        <v>-1395.331072979792</v>
+        <v>-1230.833135545266</v>
       </c>
       <c r="Q62">
-        <v>-853.7310729797915</v>
+        <v>-689.233135545266</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1916376973438736</v>
+        <v>0.1912203606394975</v>
       </c>
       <c r="T62">
-        <v>2.841320624075081</v>
+        <v>2.834513499638726</v>
       </c>
       <c r="U62">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V62">
-        <v>0.05327333071736113</v>
+        <v>0.05713863514993209</v>
       </c>
       <c r="W62">
-        <v>0.2099239685509222</v>
+        <v>0.1949239685509222</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6653,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.4261866457388891</v>
+        <v>0.4571090811994568</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6426,13 +6664,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.2043688262347281</v>
+        <v>0.1950518915529776</v>
       </c>
       <c r="C63">
-        <v>-3951.314360221048</v>
+        <v>-3461.867475262847</v>
       </c>
       <c r="D63">
-        <v>8095.248095024727</v>
+        <v>8584.694979982927</v>
       </c>
       <c r="E63">
         <v>9166.935479433028</v>
@@ -6459,37 +6697,37 @@
         <v>1184.4</v>
       </c>
       <c r="M63">
-        <v>2825.3818181289</v>
+        <v>2634.250881300214</v>
       </c>
       <c r="N63">
-        <v>-1640.9818181289</v>
+        <v>-1449.850881300214</v>
       </c>
       <c r="O63">
-        <v>-205.1227272661125</v>
+        <v>-181.2313601625267</v>
       </c>
       <c r="P63">
-        <v>-1435.859090862788</v>
+        <v>-1268.619521137687</v>
       </c>
       <c r="Q63">
-        <v>-894.2590908627875</v>
+        <v>-727.0195211376869</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1953771254808961</v>
+        <v>0.1949490878353821</v>
       </c>
       <c r="T63">
-        <v>2.914174999051365</v>
+        <v>2.907193332962796</v>
       </c>
       <c r="U63">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V63">
-        <v>0.0523999974269126</v>
+        <v>0.05620193621304797</v>
       </c>
       <c r="W63">
-        <v>0.210117618519965</v>
+        <v>0.195117618519965</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6735,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.4191999794153007</v>
+        <v>0.4496154897043838</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6508,13 +6746,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.2061281924013535</v>
+        <v>0.196661257719603</v>
       </c>
       <c r="C64">
-        <v>-4246.700789838793</v>
+        <v>-3759.766996039525</v>
       </c>
       <c r="D64">
-        <v>8008.74793516511</v>
+        <v>8495.681728964377</v>
       </c>
       <c r="E64">
         <v>9375.821749191156</v>
@@ -6541,37 +6779,37 @@
         <v>1184.4</v>
       </c>
       <c r="M64">
-        <v>2871.699552852325</v>
+        <v>2677.435321977267</v>
       </c>
       <c r="N64">
-        <v>-1687.299552852325</v>
+        <v>-1493.035321977266</v>
       </c>
       <c r="O64">
-        <v>-210.9124441065406</v>
+        <v>-186.6294152471583</v>
       </c>
       <c r="P64">
-        <v>-1476.387108745785</v>
+        <v>-1306.405906730108</v>
       </c>
       <c r="Q64">
-        <v>-934.7871087457846</v>
+        <v>-764.8059067301082</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1993133656251302</v>
+        <v>0.19887406383105</v>
       </c>
       <c r="T64">
-        <v>2.990863814815875</v>
+        <v>2.983698420672344</v>
       </c>
       <c r="U64">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V64">
-        <v>0.05155483617809142</v>
+        <v>0.05529545337090203</v>
       </c>
       <c r="W64">
-        <v>0.2103050217158129</v>
+        <v>0.1953050217158129</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6817,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.4124386894247314</v>
+        <v>0.4423636269672162</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6590,13 +6828,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.2078875585679788</v>
+        <v>0.1982706238862283</v>
       </c>
       <c r="C65">
-        <v>-4540.258202619876</v>
+        <v>-4055.839533789829</v>
       </c>
       <c r="D65">
-        <v>7924.076792142153</v>
+        <v>8408.495460972201</v>
       </c>
       <c r="E65">
         <v>9584.708018949284</v>
@@ -6623,37 +6861,37 @@
         <v>1184.4</v>
       </c>
       <c r="M65">
-        <v>2918.01728757575</v>
+        <v>2720.619762654319</v>
       </c>
       <c r="N65">
-        <v>-1733.61728757575</v>
+        <v>-1536.219762654319</v>
       </c>
       <c r="O65">
-        <v>-216.7021609469687</v>
+        <v>-192.0274703317899</v>
       </c>
       <c r="P65">
-        <v>-1516.915126628781</v>
+        <v>-1344.192292322529</v>
       </c>
       <c r="Q65">
-        <v>-975.3151266287811</v>
+        <v>-802.592292322529</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.2034623755068904</v>
+        <v>0.2030112006913486</v>
       </c>
       <c r="T65">
-        <v>3.07169797197306</v>
+        <v>3.064338918528353</v>
       </c>
       <c r="U65">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V65">
-        <v>0.05073650544510584</v>
+        <v>0.0544177477618401</v>
       </c>
       <c r="W65">
-        <v>0.2104864756038561</v>
+        <v>0.1954864756038561</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6899,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.4058920435608467</v>
+        <v>0.4353419820947209</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6672,13 +6910,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.2096469247346042</v>
+        <v>0.1998799900528537</v>
       </c>
       <c r="C66">
-        <v>-4832.044002590224</v>
+        <v>-4350.140764949118</v>
       </c>
       <c r="D66">
-        <v>7841.177261929933</v>
+        <v>8323.08049957104</v>
       </c>
       <c r="E66">
         <v>9793.594288707412</v>
@@ -6705,37 +6943,37 @@
         <v>1184.4</v>
       </c>
       <c r="M66">
-        <v>2964.335022299174</v>
+        <v>2763.804203331372</v>
       </c>
       <c r="N66">
-        <v>-1779.935022299174</v>
+        <v>-1579.404203331372</v>
       </c>
       <c r="O66">
-        <v>-222.4918777873968</v>
+        <v>-197.4255254164215</v>
       </c>
       <c r="P66">
-        <v>-1557.443144511778</v>
+        <v>-1381.97867791495</v>
       </c>
       <c r="Q66">
-        <v>-1015.843144511777</v>
+        <v>-840.3786779149503</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.2078418859376374</v>
+        <v>0.2073781784883306</v>
       </c>
       <c r="T66">
-        <v>3.157022915638979</v>
+        <v>3.149459444043029</v>
       </c>
       <c r="U66">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V66">
-        <v>0.04994374754752606</v>
+        <v>0.05356747045306134</v>
       </c>
       <c r="W66">
-        <v>0.210662259057898</v>
+        <v>0.1956622590578979</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6981,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3995499803802085</v>
+        <v>0.4285397636244908</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6754,13 +6992,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.2114062909012295</v>
+        <v>0.2014893562194791</v>
       </c>
       <c r="C67">
-        <v>-5122.113216465457</v>
+        <v>-4642.724126418625</v>
       </c>
       <c r="D67">
-        <v>7759.994317812826</v>
+        <v>8239.383407859659</v>
       </c>
       <c r="E67">
         <v>10002.48055846554</v>
@@ -6787,37 +7025,37 @@
         <v>1184.4</v>
       </c>
       <c r="M67">
-        <v>3010.652757022599</v>
+        <v>2806.988644008424</v>
       </c>
       <c r="N67">
-        <v>-1826.252757022599</v>
+        <v>-1622.588644008424</v>
       </c>
       <c r="O67">
-        <v>-228.2815946278249</v>
+        <v>-202.823580501053</v>
       </c>
       <c r="P67">
-        <v>-1597.971162394774</v>
+        <v>-1419.765063507371</v>
       </c>
       <c r="Q67">
-        <v>-1056.371162394774</v>
+        <v>-878.165063507371</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.2124716541072842</v>
+        <v>0.2119946978737114</v>
       </c>
       <c r="T67">
-        <v>3.247223570371522</v>
+        <v>3.239443999587116</v>
       </c>
       <c r="U67">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V67">
-        <v>0.04917538220064105</v>
+        <v>0.05274335552301426</v>
       </c>
       <c r="W67">
-        <v>0.2108326337902769</v>
+        <v>0.195832633790277</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +7063,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3934030576051284</v>
+        <v>0.421946844184114</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6836,13 +7074,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.2131656570678548</v>
+        <v>0.2030987223861044</v>
       </c>
       <c r="C68">
-        <v>-5410.518615456216</v>
+        <v>-4933.640927048406</v>
       </c>
       <c r="D68">
-        <v>7680.475188580197</v>
+        <v>8157.352876988007</v>
       </c>
       <c r="E68">
         <v>10211.36682822367</v>
@@ -6869,37 +7107,37 @@
         <v>1184.4</v>
       </c>
       <c r="M68">
-        <v>3056.970491746024</v>
+        <v>2850.173084685477</v>
       </c>
       <c r="N68">
-        <v>-1872.570491746023</v>
+        <v>-1665.773084685477</v>
       </c>
       <c r="O68">
-        <v>-234.0713114682529</v>
+        <v>-208.2216355856846</v>
       </c>
       <c r="P68">
-        <v>-1638.49918027777</v>
+        <v>-1457.551449099792</v>
       </c>
       <c r="Q68">
-        <v>-1096.89918027777</v>
+        <v>-915.9514490997923</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.2173737615810278</v>
+        <v>0.2168827772229383</v>
       </c>
       <c r="T68">
-        <v>3.342730145970684</v>
+        <v>3.334721764280855</v>
       </c>
       <c r="U68">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V68">
-        <v>0.04843030065214649</v>
+        <v>0.05194421377266555</v>
       </c>
       <c r="W68">
-        <v>0.2109978456519778</v>
+        <v>0.1959978456519778</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +7145,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3874424052171719</v>
+        <v>0.4155537101813244</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6918,13 +7156,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.2149250232344802</v>
+        <v>0.2047080885527297</v>
       </c>
       <c r="C69">
-        <v>-5697.31082966028</v>
+        <v>-5222.940452526485</v>
       </c>
       <c r="D69">
-        <v>7602.56924413426</v>
+        <v>8076.939621268056</v>
       </c>
       <c r="E69">
         <v>10420.25309798179</v>
@@ -6951,37 +7189,37 @@
         <v>1184.4</v>
       </c>
       <c r="M69">
-        <v>3103.288226469448</v>
+        <v>2893.35752536253</v>
       </c>
       <c r="N69">
-        <v>-1918.888226469448</v>
+        <v>-1708.95752536253</v>
       </c>
       <c r="O69">
-        <v>-239.861028308681</v>
+        <v>-213.6196906703162</v>
       </c>
       <c r="P69">
-        <v>-1679.027198160767</v>
+        <v>-1495.337834692214</v>
       </c>
       <c r="Q69">
-        <v>-1137.427198160767</v>
+        <v>-953.7378346922136</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.2225729664774226</v>
+        <v>0.2220671038054515</v>
       </c>
       <c r="T69">
-        <v>3.444024998878887</v>
+        <v>3.435773938956032</v>
       </c>
       <c r="U69">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V69">
-        <v>0.04770746034390549</v>
+        <v>0.0511689269999392</v>
       </c>
       <c r="W69">
-        <v>0.2111581258163145</v>
+        <v>0.1961581258163145</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +7227,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.381659682751244</v>
+        <v>0.4093514159995135</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7000,13 +7238,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.2166843894011055</v>
+        <v>0.206317454719355</v>
       </c>
       <c r="C70">
-        <v>-5982.538455562752</v>
+        <v>-5510.670064124677</v>
       </c>
       <c r="D70">
-        <v>7526.227887989916</v>
+        <v>7998.09627942799</v>
       </c>
       <c r="E70">
         <v>10629.13936773992</v>
@@ -7033,37 +7271,37 @@
         <v>1184.4</v>
       </c>
       <c r="M70">
-        <v>3149.605961192873</v>
+        <v>2936.541966039583</v>
       </c>
       <c r="N70">
-        <v>-1965.205961192873</v>
+        <v>-1752.141966039583</v>
       </c>
       <c r="O70">
-        <v>-245.6507451491091</v>
+        <v>-219.0177457549478</v>
       </c>
       <c r="P70">
-        <v>-1719.555216043764</v>
+        <v>-1533.124220284635</v>
       </c>
       <c r="Q70">
-        <v>-1177.955216043764</v>
+        <v>-991.5242202846349</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.2280971216798421</v>
+        <v>0.2275754507993719</v>
       </c>
       <c r="T70">
-        <v>3.551650780093852</v>
+        <v>3.543141874548408</v>
       </c>
       <c r="U70">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V70">
-        <v>0.04700588004473041</v>
+        <v>0.05041644277935185</v>
       </c>
       <c r="W70">
-        <v>0.2113136918581707</v>
+        <v>0.1963136918581706</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7309,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3760470403578433</v>
+        <v>0.4033315422348148</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7082,13 +7320,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2184437555677309</v>
+        <v>0.2079268208859804</v>
       </c>
       <c r="C71">
-        <v>-6266.248157123783</v>
+        <v>-5796.875291716917</v>
       </c>
       <c r="D71">
-        <v>7451.404456187013</v>
+        <v>7920.77732159388</v>
       </c>
       <c r="E71">
         <v>10838.02563749805</v>
@@ -7115,37 +7353,37 @@
         <v>1184.4</v>
       </c>
       <c r="M71">
-        <v>3195.923695916298</v>
+        <v>2979.726406716636</v>
       </c>
       <c r="N71">
-        <v>-2011.523695916298</v>
+        <v>-1795.326406716636</v>
       </c>
       <c r="O71">
-        <v>-251.4404619895372</v>
+        <v>-224.4158008395794</v>
       </c>
       <c r="P71">
-        <v>-1760.08323392676</v>
+        <v>-1570.910605877056</v>
       </c>
       <c r="Q71">
-        <v>-1218.48323392676</v>
+        <v>-1029.310605877056</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.2339776739920951</v>
+        <v>0.2334391750187065</v>
       </c>
       <c r="T71">
-        <v>3.66622016009688</v>
+        <v>3.657436773727389</v>
       </c>
       <c r="U71">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V71">
-        <v>0.04632463540640099</v>
+        <v>0.04968576969559312</v>
       </c>
       <c r="W71">
-        <v>0.2114647487393933</v>
+        <v>0.1964647487393933</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7391,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3705970832512079</v>
+        <v>0.397486157564745</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7164,13 +7402,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2202031217343562</v>
+        <v>0.2095361870526057</v>
       </c>
       <c r="C72">
-        <v>-6548.484760895777</v>
+        <v>-6081.599921453835</v>
       </c>
       <c r="D72">
-        <v>7378.054122173146</v>
+        <v>7844.938961615087</v>
       </c>
       <c r="E72">
         <v>11046.91190725618</v>
@@ -7197,37 +7435,37 @@
         <v>1184.4</v>
       </c>
       <c r="M72">
-        <v>3242.241430639722</v>
+        <v>3022.910847393688</v>
       </c>
       <c r="N72">
-        <v>-2057.841430639722</v>
+        <v>-1838.510847393688</v>
       </c>
       <c r="O72">
-        <v>-257.2301788299653</v>
+        <v>-229.813855924211</v>
       </c>
       <c r="P72">
-        <v>-1800.611251809757</v>
+        <v>-1608.696991469477</v>
       </c>
       <c r="Q72">
-        <v>-1259.011251809757</v>
+        <v>-1067.096991469477</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.2402502631251649</v>
+        <v>0.2396938141859967</v>
       </c>
       <c r="T72">
-        <v>3.788427498766775</v>
+        <v>3.779351332851636</v>
       </c>
       <c r="U72">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V72">
-        <v>0.04566285490059525</v>
+        <v>0.04897597298565608</v>
       </c>
       <c r="W72">
-        <v>0.2116114897097239</v>
+        <v>0.1966114897097239</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7473,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.365302839204762</v>
+        <v>0.3918077838852487</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7246,13 +7484,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.2219624879009816</v>
+        <v>0.2111455532192311</v>
       </c>
       <c r="C73">
-        <v>-6829.291345577462</v>
+        <v>-6364.886078448459</v>
       </c>
       <c r="D73">
-        <v>7306.133807249586</v>
+        <v>7770.539074378591</v>
       </c>
       <c r="E73">
         <v>11255.7981770143</v>
@@ -7279,37 +7517,37 @@
         <v>1184.4</v>
       </c>
       <c r="M73">
-        <v>3288.559165363146</v>
+        <v>3066.09528807074</v>
       </c>
       <c r="N73">
-        <v>-2104.159165363146</v>
+        <v>-1881.69528807074</v>
       </c>
       <c r="O73">
-        <v>-263.0198956703933</v>
+        <v>-235.2119110088425</v>
       </c>
       <c r="P73">
-        <v>-1841.139269692753</v>
+        <v>-1646.483377061898</v>
       </c>
       <c r="Q73">
-        <v>-1299.539269692753</v>
+        <v>-1104.883377061898</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.2469554446122395</v>
+        <v>0.2463798077786172</v>
       </c>
       <c r="T73">
-        <v>3.919062929758732</v>
+        <v>3.909673792605139</v>
       </c>
       <c r="U73">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V73">
-        <v>0.04501971609917843</v>
+        <v>0.0482861705492384</v>
       </c>
       <c r="W73">
-        <v>0.2117540971315945</v>
+        <v>0.1967540971315944</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7555,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3601577287934274</v>
+        <v>0.3862893643939072</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7328,13 +7566,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.2237218540676069</v>
+        <v>0.2127549193858564</v>
       </c>
       <c r="C74">
-        <v>-7108.709326380737</v>
+        <v>-6646.774304801029</v>
       </c>
       <c r="D74">
-        <v>7235.602096204439</v>
+        <v>7697.537117784148</v>
       </c>
       <c r="E74">
         <v>11464.68444677243</v>
@@ -7361,37 +7599,37 @@
         <v>1184.4</v>
       </c>
       <c r="M74">
-        <v>3334.876900086571</v>
+        <v>3109.279728747793</v>
       </c>
       <c r="N74">
-        <v>-2150.476900086571</v>
+        <v>-1924.879728747793</v>
       </c>
       <c r="O74">
-        <v>-268.8096125108214</v>
+        <v>-240.6099660934742</v>
       </c>
       <c r="P74">
-        <v>-1881.667287575749</v>
+        <v>-1684.269762654319</v>
       </c>
       <c r="Q74">
-        <v>-1340.06728757575</v>
+        <v>-1142.669762654319</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.2541395676341052</v>
+        <v>0.2535433723421393</v>
       </c>
       <c r="T74">
-        <v>4.059029462964402</v>
+        <v>4.049304999483894</v>
       </c>
       <c r="U74">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V74">
-        <v>0.04439444226446761</v>
+        <v>0.04761552929161009</v>
       </c>
       <c r="W74">
-        <v>0.2118927432361908</v>
+        <v>0.1968927432361909</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7637,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.355155538115741</v>
+        <v>0.3809242343328807</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7410,13 +7648,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.2254812202342322</v>
+        <v>0.2143642855524817</v>
       </c>
       <c r="C75">
-        <v>-7386.778534557513</v>
+        <v>-6927.303633266642</v>
       </c>
       <c r="D75">
-        <v>7166.41915778579</v>
+        <v>7625.894059076661</v>
       </c>
       <c r="E75">
         <v>11673.57071653056</v>
@@ -7443,37 +7681,37 @@
         <v>1184.4</v>
       </c>
       <c r="M75">
-        <v>3381.194634809995</v>
+        <v>3152.464169424846</v>
       </c>
       <c r="N75">
-        <v>-2196.794634809995</v>
+        <v>-1968.064169424846</v>
       </c>
       <c r="O75">
-        <v>-274.5993293512494</v>
+        <v>-246.0080211781057</v>
       </c>
       <c r="P75">
-        <v>-1922.195305458746</v>
+        <v>-1722.05614824674</v>
       </c>
       <c r="Q75">
-        <v>-1380.595305458746</v>
+        <v>-1180.45614824674</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.2618558479168498</v>
+        <v>0.261237571317774</v>
       </c>
       <c r="T75">
-        <v>4.209363887518638</v>
+        <v>4.199279258724038</v>
       </c>
       <c r="U75">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V75">
-        <v>0.04378629921974888</v>
+        <v>0.04696326176706749</v>
       </c>
       <c r="W75">
-        <v>0.2120275908173736</v>
+        <v>0.1970275908173736</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7719,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3502903937579911</v>
+        <v>0.3757060941365399</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7492,13 +7730,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.2272405864008575</v>
+        <v>0.215973651719107</v>
       </c>
       <c r="C76">
-        <v>-7663.537292407401</v>
+        <v>-7206.511656846964</v>
       </c>
       <c r="D76">
-        <v>7098.54666969403</v>
+        <v>7555.572305254466</v>
       </c>
       <c r="E76">
         <v>11882.45698628869</v>
@@ -7525,37 +7763,37 @@
         <v>1184.4</v>
       </c>
       <c r="M76">
-        <v>3427.51236953342</v>
+        <v>3195.648610101899</v>
       </c>
       <c r="N76">
-        <v>-2243.11236953342</v>
+        <v>-2011.248610101899</v>
       </c>
       <c r="O76">
-        <v>-280.3890461916775</v>
+        <v>-251.4060762627373</v>
       </c>
       <c r="P76">
-        <v>-1962.723323341742</v>
+        <v>-1759.842533839161</v>
       </c>
       <c r="Q76">
-        <v>-1421.123323341742</v>
+        <v>-1218.242533839161</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.2701656882213441</v>
+        <v>0.269523631753073</v>
       </c>
       <c r="T76">
-        <v>4.371262498577048</v>
+        <v>4.360789999444194</v>
       </c>
       <c r="U76">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V76">
-        <v>0.04319459247353606</v>
+        <v>0.04632862309453954</v>
       </c>
       <c r="W76">
-        <v>0.2121587938693353</v>
+        <v>0.1971587938693352</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7801,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3455567397882885</v>
+        <v>0.3706289847563163</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7574,13 +7812,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.2289999525674829</v>
+        <v>0.2175830178857324</v>
       </c>
       <c r="C77">
-        <v>-7939.02248406304</v>
+        <v>-7484.434594566692</v>
       </c>
       <c r="D77">
-        <v>7031.947747796519</v>
+        <v>7486.535637292867</v>
       </c>
       <c r="E77">
         <v>12091.34325604681</v>
@@ -7607,37 +7845,37 @@
         <v>1184.4</v>
       </c>
       <c r="M77">
-        <v>3473.830104256845</v>
+        <v>3238.833050778951</v>
       </c>
       <c r="N77">
-        <v>-2289.430104256845</v>
+        <v>-2054.433050778951</v>
       </c>
       <c r="O77">
-        <v>-286.1787630321056</v>
+        <v>-256.8041313473689</v>
       </c>
       <c r="P77">
-        <v>-2003.251341224739</v>
+        <v>-1797.628919431583</v>
       </c>
       <c r="Q77">
-        <v>-1461.65134122474</v>
+        <v>-1256.028919431582</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.2791403157501978</v>
+        <v>0.2784725770231959</v>
       </c>
       <c r="T77">
-        <v>4.54611299852013</v>
+        <v>4.535221599421962</v>
       </c>
       <c r="U77">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V77">
-        <v>0.04261866457388891</v>
+        <v>0.04571090811994568</v>
       </c>
       <c r="W77">
-        <v>0.2122864981732446</v>
+        <v>0.1972864981732446</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7883,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3409493165911113</v>
+        <v>0.3656872649595654</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7656,13 +7894,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.2307593187341082</v>
+        <v>0.2191923840523578</v>
       </c>
       <c r="C78">
-        <v>-8213.269622327796</v>
+        <v>-7761.10735367661</v>
       </c>
       <c r="D78">
-        <v>6966.586879289892</v>
+        <v>7418.749147941077</v>
       </c>
       <c r="E78">
         <v>12300.22952580494</v>
@@ -7689,37 +7927,37 @@
         <v>1184.4</v>
       </c>
       <c r="M78">
-        <v>3520.14783898027</v>
+        <v>3282.017491456004</v>
       </c>
       <c r="N78">
-        <v>-2335.74783898027</v>
+        <v>-2097.617491456004</v>
       </c>
       <c r="O78">
-        <v>-291.9684798725337</v>
+        <v>-262.2021864320005</v>
       </c>
       <c r="P78">
-        <v>-2043.779359107736</v>
+        <v>-1835.415305024004</v>
       </c>
       <c r="Q78">
-        <v>-1502.179359107736</v>
+        <v>-1293.815305024004</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.2888628289064561</v>
+        <v>0.2881672677324958</v>
       </c>
       <c r="T78">
-        <v>4.735534373458469</v>
+        <v>4.724189166064544</v>
       </c>
       <c r="U78">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V78">
-        <v>0.04205789267160089</v>
+        <v>0.04510944880257797</v>
       </c>
       <c r="W78">
-        <v>0.2124108418375773</v>
+        <v>0.1974108418375773</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7965,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3364631413728072</v>
+        <v>0.3608755904206238</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7738,13 +7976,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.2325186849007336</v>
+        <v>0.2208017502189831</v>
       </c>
       <c r="C79">
-        <v>-8486.312911820325</v>
+        <v>-8036.563588507681</v>
       </c>
       <c r="D79">
-        <v>6902.429859555491</v>
+        <v>7352.179182868134</v>
       </c>
       <c r="E79">
         <v>12509.11579556307</v>
@@ -7771,37 +8009,37 @@
         <v>1184.4</v>
       </c>
       <c r="M79">
-        <v>3566.465573703694</v>
+        <v>3325.201932133057</v>
       </c>
       <c r="N79">
-        <v>-2382.065573703694</v>
+        <v>-2140.801932133057</v>
       </c>
       <c r="O79">
-        <v>-297.7581967129618</v>
+        <v>-267.6002415166321</v>
       </c>
       <c r="P79">
-        <v>-2084.307376990732</v>
+        <v>-1873.201690616424</v>
       </c>
       <c r="Q79">
-        <v>-1542.707376990732</v>
+        <v>-1331.601690616425</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.2994307779893455</v>
+        <v>0.298704975025213</v>
       </c>
       <c r="T79">
-        <v>4.941427172304489</v>
+        <v>4.929588695023872</v>
       </c>
       <c r="U79">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V79">
-        <v>0.04151168627326841</v>
+        <v>0.0445236118051419</v>
       </c>
       <c r="W79">
-        <v>0.212531955796343</v>
+        <v>0.197531955796343</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +8047,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3320934901861473</v>
+        <v>0.3561888944411352</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7820,13 +8058,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.2342780510673589</v>
+        <v>0.2224111163856085</v>
       </c>
       <c r="C80">
-        <v>-8758.185308661854</v>
+        <v>-8310.835756184657</v>
       </c>
       <c r="D80">
-        <v>6839.443732472087</v>
+        <v>7286.793284949285</v>
       </c>
       <c r="E80">
         <v>12718.0020653212</v>
@@ -7853,37 +8091,37 @@
         <v>1184.4</v>
       </c>
       <c r="M80">
-        <v>3612.783308427119</v>
+        <v>3368.386372810109</v>
       </c>
       <c r="N80">
-        <v>-2428.383308427119</v>
+        <v>-2183.986372810109</v>
       </c>
       <c r="O80">
-        <v>-303.5479135533898</v>
+        <v>-272.9982966012636</v>
       </c>
       <c r="P80">
-        <v>-2124.835394873729</v>
+        <v>-1910.988076208846</v>
       </c>
       <c r="Q80">
-        <v>-1583.235394873729</v>
+        <v>-1369.388076208846</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.3109594497161339</v>
+        <v>0.3102006557081772</v>
       </c>
       <c r="T80">
-        <v>5.16603749831833</v>
+        <v>5.153660908434047</v>
       </c>
       <c r="U80">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V80">
-        <v>0.04097948516720087</v>
+        <v>0.04395279626917854</v>
       </c>
       <c r="W80">
-        <v>0.2126499642689865</v>
+        <v>0.1976499642689865</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +8129,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.327835881337607</v>
+        <v>0.3516223701534283</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7902,13 +8140,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.2360374172339843</v>
+        <v>0.2240204825522338</v>
       </c>
       <c r="C81">
-        <v>-9028.918576925116</v>
+        <v>-8583.955169392995</v>
       </c>
       <c r="D81">
-        <v>6777.596733966954</v>
+        <v>7222.560141499076</v>
       </c>
       <c r="E81">
         <v>12926.88833507933</v>
@@ -7935,37 +8173,37 @@
         <v>1184.4</v>
       </c>
       <c r="M81">
-        <v>3659.101043150544</v>
+        <v>3411.570813487162</v>
       </c>
       <c r="N81">
-        <v>-2474.701043150544</v>
+        <v>-2227.170813487162</v>
       </c>
       <c r="O81">
-        <v>-309.337630393818</v>
+        <v>-278.3963516858953</v>
       </c>
       <c r="P81">
-        <v>-2165.363412756726</v>
+        <v>-1948.774461801267</v>
       </c>
       <c r="Q81">
-        <v>-1623.763412756726</v>
+        <v>-1407.174461801267</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.323586090178807</v>
+        <v>0.3227911631228524</v>
       </c>
       <c r="T81">
-        <v>5.412039283952537</v>
+        <v>5.399073332645194</v>
       </c>
       <c r="U81">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V81">
-        <v>0.04046075750685656</v>
+        <v>0.0433964317594421</v>
       </c>
       <c r="W81">
-        <v>0.2127649851853605</v>
+        <v>0.1977649851853605</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +8211,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3236860600548525</v>
+        <v>0.3471714540755367</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7984,13 +8222,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.2377967834006096</v>
+        <v>0.2256298487188591</v>
       </c>
       <c r="C82">
-        <v>-9298.543342047957</v>
+        <v>-8855.952046379296</v>
       </c>
       <c r="D82">
-        <v>6716.858238602238</v>
+        <v>7159.4495342709</v>
       </c>
       <c r="E82">
         <v>13135.77460483745</v>
@@ -8017,37 +8255,37 @@
         <v>1184.4</v>
       </c>
       <c r="M82">
-        <v>3705.418777873968</v>
+        <v>3454.755254164214</v>
       </c>
       <c r="N82">
-        <v>-2521.018777873968</v>
+        <v>-2270.355254164214</v>
       </c>
       <c r="O82">
-        <v>-315.127347234246</v>
+        <v>-283.7944067705268</v>
       </c>
       <c r="P82">
-        <v>-2205.891430639722</v>
+        <v>-1986.560847393687</v>
       </c>
       <c r="Q82">
-        <v>-1664.291430639722</v>
+        <v>-1444.960847393687</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.3374753946877474</v>
+        <v>0.3366407212789951</v>
       </c>
       <c r="T82">
-        <v>5.682641248150164</v>
+        <v>5.669026999277454</v>
       </c>
       <c r="U82">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V82">
-        <v>0.03995499803802086</v>
+        <v>0.04285397636244908</v>
       </c>
       <c r="W82">
-        <v>0.2128771305788252</v>
+        <v>0.1978771305788252</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8293,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3196399843041668</v>
+        <v>0.3428318108995927</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8066,13 +8304,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.239556149567235</v>
+        <v>0.2272392148854845</v>
       </c>
       <c r="C83">
-        <v>-9567.089141400498</v>
+        <v>-9126.85555835308</v>
       </c>
       <c r="D83">
-        <v>6657.198709007825</v>
+        <v>7097.432292055243</v>
       </c>
       <c r="E83">
         <v>13344.66087459558</v>
@@ -8099,37 +8337,37 @@
         <v>1184.4</v>
       </c>
       <c r="M83">
-        <v>3751.736512597392</v>
+        <v>3497.939694841267</v>
       </c>
       <c r="N83">
-        <v>-2567.336512597392</v>
+        <v>-2313.539694841267</v>
       </c>
       <c r="O83">
-        <v>-320.917064074674</v>
+        <v>-289.1924618551584</v>
       </c>
       <c r="P83">
-        <v>-2246.419448522718</v>
+        <v>-2024.347232986109</v>
       </c>
       <c r="Q83">
-        <v>-1704.819448522718</v>
+        <v>-1482.747232986109</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.3528267312502604</v>
+        <v>0.3519481276621</v>
       </c>
       <c r="T83">
-        <v>5.981727629631751</v>
+        <v>5.967396841344688</v>
       </c>
       <c r="U83">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V83">
-        <v>0.03946172645730454</v>
+        <v>0.04232491492587563</v>
       </c>
       <c r="W83">
-        <v>0.212986506950229</v>
+        <v>0.197986506950229</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8375,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3156938116584364</v>
+        <v>0.3385993194070051</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8148,13 +8386,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2413155157338603</v>
+        <v>0.2288485810521098</v>
       </c>
       <c r="C84">
-        <v>-9834.58447218107</v>
+        <v>-9396.693874446002</v>
       </c>
       <c r="D84">
-        <v>6598.589647985382</v>
+        <v>7036.480245720449</v>
       </c>
       <c r="E84">
         <v>13553.54714435371</v>
@@ -8181,37 +8419,37 @@
         <v>1184.4</v>
       </c>
       <c r="M84">
-        <v>3798.054247320817</v>
+        <v>3541.12413551832</v>
       </c>
       <c r="N84">
-        <v>-2613.654247320817</v>
+        <v>-2356.72413551832</v>
       </c>
       <c r="O84">
-        <v>-326.7067809151021</v>
+        <v>-294.59051693979</v>
       </c>
       <c r="P84">
-        <v>-2286.947466405715</v>
+        <v>-2062.13361857853</v>
       </c>
       <c r="Q84">
-        <v>-1745.347466405715</v>
+        <v>-1520.53361857853</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.3698837718752749</v>
+        <v>0.3689563569766612</v>
       </c>
       <c r="T84">
-        <v>6.314045831277959</v>
+        <v>6.29891888808606</v>
       </c>
       <c r="U84">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V84">
-        <v>0.03898048589075205</v>
+        <v>0.04180875742677959</v>
       </c>
       <c r="W84">
-        <v>0.2130932156052571</v>
+        <v>0.1980932156052571</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8457,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3118438871260164</v>
+        <v>0.3344700594142367</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8230,13 +8468,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2430748819004856</v>
+        <v>0.2304579472187352</v>
       </c>
       <c r="C85">
-        <v>-10101.05683680432</v>
+        <v>-9665.494204374236</v>
       </c>
       <c r="D85">
-        <v>6541.003553120263</v>
+        <v>6976.566185550344</v>
       </c>
       <c r="E85">
         <v>13762.43341411183</v>
@@ -8263,37 +8501,37 @@
         <v>1184.4</v>
       </c>
       <c r="M85">
-        <v>3844.371982044242</v>
+        <v>3584.308576195373</v>
       </c>
       <c r="N85">
-        <v>-2659.971982044242</v>
+        <v>-2399.908576195373</v>
       </c>
       <c r="O85">
-        <v>-332.4964977555302</v>
+        <v>-299.9885720244216</v>
       </c>
       <c r="P85">
-        <v>-2327.475484288712</v>
+        <v>-2099.920004170951</v>
       </c>
       <c r="Q85">
-        <v>-1785.875484288712</v>
+        <v>-1558.320004170952</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.3889475231620558</v>
+        <v>0.3879655544458765</v>
       </c>
       <c r="T85">
-        <v>6.68546029194137</v>
+        <v>6.669443528561711</v>
       </c>
       <c r="U85">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V85">
-        <v>0.03851084148242973</v>
+        <v>0.04130503745778224</v>
       </c>
       <c r="W85">
-        <v>0.213197352967393</v>
+        <v>0.198197352967393</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8539,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3080867318594379</v>
+        <v>0.330440299662258</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8312,13 +8550,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.244834248067111</v>
+        <v>0.2320673133853605</v>
       </c>
       <c r="C86">
-        <v>-10366.53278593316</v>
+        <v>-9933.282838939629</v>
       </c>
       <c r="D86">
-        <v>6484.413873749548</v>
+        <v>6917.663820743075</v>
       </c>
       <c r="E86">
         <v>13971.31968386996</v>
@@ -8345,37 +8583,37 @@
         <v>1184.4</v>
       </c>
       <c r="M86">
-        <v>3890.689716767666</v>
+        <v>3627.493016872425</v>
       </c>
       <c r="N86">
-        <v>-2706.289716767666</v>
+        <v>-2443.093016872425</v>
       </c>
       <c r="O86">
-        <v>-338.2862145959582</v>
+        <v>-305.3866271090531</v>
       </c>
       <c r="P86">
-        <v>-2368.003502171708</v>
+        <v>-2137.706389763372</v>
       </c>
       <c r="Q86">
-        <v>-1826.403502171708</v>
+        <v>-1596.106389763372</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.4103942433596841</v>
+        <v>0.4093509015987437</v>
       </c>
       <c r="T86">
-        <v>7.103301560187702</v>
+        <v>7.086283749096815</v>
       </c>
       <c r="U86">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V86">
-        <v>0.03805237908382939</v>
+        <v>0.04081331082138008</v>
       </c>
       <c r="W86">
-        <v>0.2132990108685256</v>
+        <v>0.1982990108685256</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8621,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3044190326706351</v>
+        <v>0.3265064865710406</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8394,13 +8632,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.2465936142337363</v>
+        <v>0.2336766795519858</v>
       </c>
       <c r="C87">
-        <v>-10631.03795929622</v>
+        <v>-10200.08518849641</v>
       </c>
       <c r="D87">
-        <v>6428.794970144608</v>
+        <v>6859.747740944423</v>
       </c>
       <c r="E87">
         <v>14180.20595362809</v>
@@ -8427,37 +8665,37 @@
         <v>1184.4</v>
       </c>
       <c r="M87">
-        <v>3937.007451491091</v>
+        <v>3670.677457549478</v>
       </c>
       <c r="N87">
-        <v>-2752.607451491091</v>
+        <v>-2486.277457549478</v>
       </c>
       <c r="O87">
-        <v>-344.0759314363863</v>
+        <v>-310.7846821936847</v>
       </c>
       <c r="P87">
-        <v>-2408.531520054704</v>
+        <v>-2175.492775355793</v>
       </c>
       <c r="Q87">
-        <v>-1866.931520054704</v>
+        <v>-1633.892775355793</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.4347005262503297</v>
+        <v>0.4335876283719933</v>
       </c>
       <c r="T87">
-        <v>7.576854997533549</v>
+        <v>7.558702665703269</v>
       </c>
       <c r="U87">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V87">
-        <v>0.03760470403578434</v>
+        <v>0.04033315422348149</v>
       </c>
       <c r="W87">
-        <v>0.2133982768190434</v>
+        <v>0.1983982768190433</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8703,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3008376322862747</v>
+        <v>0.3226652337878519</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8476,13 +8714,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2483529804003617</v>
+        <v>0.2352860457186112</v>
       </c>
       <c r="C88">
-        <v>-10894.59712442247</v>
+        <v>-10465.9258195016</v>
       </c>
       <c r="D88">
-        <v>6374.122074776486</v>
+        <v>6802.79337969736</v>
       </c>
       <c r="E88">
         <v>14389.09222338621</v>
@@ -8509,37 +8747,37 @@
         <v>1184.4</v>
       </c>
       <c r="M88">
-        <v>3983.325186214515</v>
+        <v>3713.861898226531</v>
       </c>
       <c r="N88">
-        <v>-2798.925186214515</v>
+        <v>-2529.461898226531</v>
       </c>
       <c r="O88">
-        <v>-349.8656482768144</v>
+        <v>-316.1827372783163</v>
       </c>
       <c r="P88">
-        <v>-2449.059537937701</v>
+        <v>-2213.279160948214</v>
       </c>
       <c r="Q88">
-        <v>-1907.459537937701</v>
+        <v>-1671.679160948214</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.4624791352682104</v>
+        <v>0.4612867446842785</v>
       </c>
       <c r="T88">
-        <v>8.118058925928803</v>
+        <v>8.098609998967788</v>
       </c>
       <c r="U88">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V88">
-        <v>0.03716744003536824</v>
+        <v>0.03986416405809216</v>
       </c>
       <c r="W88">
-        <v>0.213495234259084</v>
+        <v>0.1984952342590839</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8785,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2973395202829459</v>
+        <v>0.3189133124647373</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8558,13 +8796,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.250112346566987</v>
+        <v>0.2368954118852365</v>
       </c>
       <c r="C89">
-        <v>-11157.23421341603</v>
+        <v>-10730.82848925961</v>
       </c>
       <c r="D89">
-        <v>6320.371255541057</v>
+        <v>6746.776979697483</v>
       </c>
       <c r="E89">
         <v>14597.97849314434</v>
@@ -8591,37 +8829,37 @@
         <v>1184.4</v>
       </c>
       <c r="M89">
-        <v>4029.64292093794</v>
+        <v>3757.046338903584</v>
       </c>
       <c r="N89">
-        <v>-2845.24292093794</v>
+        <v>-2572.646338903583</v>
       </c>
       <c r="O89">
-        <v>-355.6553651172425</v>
+        <v>-321.5807923629479</v>
       </c>
       <c r="P89">
-        <v>-2489.587555820697</v>
+        <v>-2251.065546540635</v>
       </c>
       <c r="Q89">
-        <v>-1947.987555820697</v>
+        <v>-1709.465546540635</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.4945313764426881</v>
+        <v>0.4932472635061461</v>
       </c>
       <c r="T89">
-        <v>8.742524997154096</v>
+        <v>8.721579998888387</v>
       </c>
       <c r="U89">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V89">
-        <v>0.03674022808093871</v>
+        <v>0.03940595527581525</v>
       </c>
       <c r="W89">
-        <v>0.2135899627924569</v>
+        <v>0.1985899627924569</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8867,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2939218246475097</v>
+        <v>0.3152476422065219</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8640,13 +8878,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2518717127336123</v>
+        <v>0.2385047780518618</v>
       </c>
       <c r="C90">
-        <v>-11418.97235788591</v>
+        <v>-10994.81617896431</v>
       </c>
       <c r="D90">
-        <v>6267.519380829304</v>
+        <v>6691.675559750909</v>
       </c>
       <c r="E90">
         <v>14806.86476290247</v>
@@ -8673,37 +8911,37 @@
         <v>1184.4</v>
       </c>
       <c r="M90">
-        <v>4075.960655661365</v>
+        <v>3800.230779580636</v>
       </c>
       <c r="N90">
-        <v>-2891.560655661365</v>
+        <v>-2615.830779580636</v>
       </c>
       <c r="O90">
-        <v>-361.4450819576706</v>
+        <v>-326.9788474475795</v>
       </c>
       <c r="P90">
-        <v>-2530.115573703694</v>
+        <v>-2288.851932133057</v>
       </c>
       <c r="Q90">
-        <v>-1988.515573703694</v>
+        <v>-1747.251932133057</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.5319256578129122</v>
+        <v>0.5305345354649916</v>
       </c>
       <c r="T90">
-        <v>9.471068746916938</v>
+        <v>9.448378332129089</v>
       </c>
       <c r="U90">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V90">
-        <v>0.03632272548910986</v>
+        <v>0.03895816032949916</v>
       </c>
       <c r="W90">
-        <v>0.2136825384046169</v>
+        <v>0.1986825384046169</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8949,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2905818039128789</v>
+        <v>0.3116652826359932</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8722,13 +8960,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2536310789002377</v>
+        <v>0.2401141442184871</v>
       </c>
       <c r="C91">
-        <v>-11679.83392213776</v>
+        <v>-11257.91112513501</v>
       </c>
       <c r="D91">
-        <v>6215.544086335583</v>
+        <v>6637.466883338332</v>
       </c>
       <c r="E91">
         <v>15015.7510326606</v>
@@ -8755,37 +8993,37 @@
         <v>1184.4</v>
       </c>
       <c r="M91">
-        <v>4122.278390384789</v>
+        <v>3843.415220257689</v>
       </c>
       <c r="N91">
-        <v>-2937.878390384789</v>
+        <v>-2659.015220257689</v>
       </c>
       <c r="O91">
-        <v>-367.2347987980987</v>
+        <v>-332.3769025322111</v>
       </c>
       <c r="P91">
-        <v>-2570.64359158669</v>
+        <v>-2326.638317725478</v>
       </c>
       <c r="Q91">
-        <v>-2029.043591586691</v>
+        <v>-1785.038317725478</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.5761188994322678</v>
+        <v>0.5746013114163544</v>
       </c>
       <c r="T91">
-        <v>10.33207499663666</v>
+        <v>10.30732181686809</v>
       </c>
       <c r="U91">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V91">
-        <v>0.03591460497799627</v>
+        <v>0.03852042819096546</v>
       </c>
       <c r="W91">
-        <v>0.2137730336659418</v>
+        <v>0.1987730336659418</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +9031,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2873168398239702</v>
+        <v>0.3081634255277237</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8804,13 +9042,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.255390445066863</v>
+        <v>0.2417235103851125</v>
       </c>
       <c r="C92">
-        <v>-11939.84053472765</v>
+        <v>-11520.13484953685</v>
       </c>
       <c r="D92">
-        <v>6164.423743503826</v>
+        <v>6584.129428694617</v>
       </c>
       <c r="E92">
         <v>15224.63730241873</v>
@@ -8837,37 +9075,37 @@
         <v>1184.4</v>
       </c>
       <c r="M92">
-        <v>4168.596125108214</v>
+        <v>3886.599660934742</v>
       </c>
       <c r="N92">
-        <v>-2984.196125108214</v>
+        <v>-2702.199660934742</v>
       </c>
       <c r="O92">
-        <v>-373.0245156385268</v>
+        <v>-337.7749576168427</v>
       </c>
       <c r="P92">
-        <v>-2611.171609469688</v>
+        <v>-2364.424703317899</v>
       </c>
       <c r="Q92">
-        <v>-2069.571609469688</v>
+        <v>-1822.824703317899</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.6291507893754946</v>
+        <v>0.62748144255799</v>
       </c>
       <c r="T92">
-        <v>11.36528249630033</v>
+        <v>11.33805399855491</v>
       </c>
       <c r="U92">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V92">
-        <v>0.03551555381157408</v>
+        <v>0.03809242343328807</v>
       </c>
       <c r="W92">
-        <v>0.2138615179214595</v>
+        <v>0.1988615179214595</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +9113,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2841244304925927</v>
+        <v>0.3047393874663046</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8886,13 +9124,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2571498112334883</v>
+        <v>0.2433328765517379</v>
       </c>
       <c r="C93">
-        <v>-12199.01311847148</v>
+        <v>-11781.50818766998</v>
       </c>
       <c r="D93">
-        <v>6114.13742951812</v>
+        <v>6531.642360319625</v>
       </c>
       <c r="E93">
         <v>15433.52357217685</v>
@@ -8919,37 +9157,37 @@
         <v>1184.4</v>
       </c>
       <c r="M93">
-        <v>4214.913859831639</v>
+        <v>3929.784101611795</v>
       </c>
       <c r="N93">
-        <v>-3030.513859831638</v>
+        <v>-2745.384101611794</v>
       </c>
       <c r="O93">
-        <v>-378.8142324789548</v>
+        <v>-343.1730127014743</v>
       </c>
       <c r="P93">
-        <v>-2651.699627352684</v>
+        <v>-2402.21108891032</v>
       </c>
       <c r="Q93">
-        <v>-2110.099627352684</v>
+        <v>-1860.61108891032</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.6939675437505497</v>
+        <v>0.6921127139533223</v>
       </c>
       <c r="T93">
-        <v>12.62809166255592</v>
+        <v>12.59783777617212</v>
       </c>
       <c r="U93">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V93">
-        <v>0.03512527300045789</v>
+        <v>0.0376738253735816</v>
       </c>
       <c r="W93">
-        <v>0.2139480574680647</v>
+        <v>0.1989480574680647</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +9195,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2810021840036632</v>
+        <v>0.3013906029886528</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8968,13 +9206,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2589091774001137</v>
+        <v>0.2449422427183632</v>
       </c>
       <c r="C94">
-        <v>-12457.37191899747</v>
+        <v>-12042.05131590688</v>
       </c>
       <c r="D94">
-        <v>6064.664898750258</v>
+        <v>6479.985501840846</v>
       </c>
       <c r="E94">
         <v>15642.40984193498</v>
@@ -9001,37 +9239,37 @@
         <v>1184.4</v>
       </c>
       <c r="M94">
-        <v>4261.231594555064</v>
+        <v>3972.968542288847</v>
       </c>
       <c r="N94">
-        <v>-3076.831594555063</v>
+        <v>-2788.568542288847</v>
       </c>
       <c r="O94">
-        <v>-384.6039493193829</v>
+        <v>-348.5710677861059</v>
       </c>
       <c r="P94">
-        <v>-2692.22764523568</v>
+        <v>-2439.997474502741</v>
       </c>
       <c r="Q94">
-        <v>-2150.627645235681</v>
+        <v>-1898.397474502741</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.7749884867193687</v>
+        <v>0.7729018031974878</v>
       </c>
       <c r="T94">
-        <v>14.20660312037542</v>
+        <v>14.17256749819364</v>
       </c>
       <c r="U94">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V94">
-        <v>0.03474347655480074</v>
+        <v>0.03726432727169485</v>
       </c>
       <c r="W94">
-        <v>0.2140327157201785</v>
+        <v>0.1990327157201785</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9277,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2779478124384059</v>
+        <v>0.2981146181735588</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9050,13 +9288,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.260668543566739</v>
+        <v>0.2465516088849886</v>
       </c>
       <c r="C95">
-        <v>-12714.93653192354</v>
+        <v>-12301.7837773522</v>
       </c>
       <c r="D95">
-        <v>6015.986555582308</v>
+        <v>6429.139310153656</v>
       </c>
       <c r="E95">
         <v>15851.29611169311</v>
@@ -9083,37 +9321,37 @@
         <v>1184.4</v>
       </c>
       <c r="M95">
-        <v>4307.549329278488</v>
+        <v>4016.152982965899</v>
       </c>
       <c r="N95">
-        <v>-3123.149329278488</v>
+        <v>-2831.752982965899</v>
       </c>
       <c r="O95">
-        <v>-390.3936661598109</v>
+        <v>-353.9691228707374</v>
       </c>
       <c r="P95">
-        <v>-2732.755663118677</v>
+        <v>-2477.783860095162</v>
       </c>
       <c r="Q95">
-        <v>-2191.155663118677</v>
+        <v>-1936.183860095162</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.8791582705364214</v>
+        <v>0.8767734893685577</v>
       </c>
       <c r="T95">
-        <v>16.23611785185762</v>
+        <v>16.19721999793559</v>
       </c>
       <c r="U95">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V95">
-        <v>0.03436989078539428</v>
+        <v>0.03686363558060136</v>
       </c>
       <c r="W95">
-        <v>0.21411555336472</v>
+        <v>0.1991155533647199</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9359,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2749591262831542</v>
+        <v>0.2949090846448109</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9132,13 +9370,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2624279097333644</v>
+        <v>0.2481609750516139</v>
       </c>
       <c r="C96">
-        <v>-12971.72592873634</v>
+        <v>-12560.72450649437</v>
       </c>
       <c r="D96">
-        <v>5968.083428527637</v>
+        <v>6379.084850769614</v>
       </c>
       <c r="E96">
         <v>16060.18238145124</v>
@@ -9165,37 +9403,37 @@
         <v>1184.4</v>
       </c>
       <c r="M96">
-        <v>4353.867064001913</v>
+        <v>4059.337423642952</v>
       </c>
       <c r="N96">
-        <v>-3169.467064001913</v>
+        <v>-2874.937423642952</v>
       </c>
       <c r="O96">
-        <v>-396.1833830002391</v>
+        <v>-359.367177955369</v>
       </c>
       <c r="P96">
-        <v>-2773.283681001673</v>
+        <v>-2515.570245687583</v>
       </c>
       <c r="Q96">
-        <v>-2231.683681001673</v>
+        <v>-1973.970245687583</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>1.018051315625825</v>
+        <v>1.015269070929984</v>
       </c>
       <c r="T96">
-        <v>18.94213749383389</v>
+        <v>18.89675666425819</v>
       </c>
       <c r="U96">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V96">
-        <v>0.03400425364937944</v>
+        <v>0.03647146924463751</v>
       </c>
       <c r="W96">
-        <v>0.2141966285061861</v>
+        <v>0.1991966285061861</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9441,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2720340291950356</v>
+        <v>0.2917717539571001</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9214,13 +9452,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2641872758999897</v>
+        <v>0.2497703412182393</v>
       </c>
       <c r="C97">
-        <v>-13227.75848144355</v>
+        <v>-12818.89185271473</v>
       </c>
       <c r="D97">
-        <v>5920.937145578554</v>
+        <v>6329.803774307381</v>
       </c>
       <c r="E97">
         <v>16269.06865120936</v>
@@ -9247,37 +9485,37 @@
         <v>1184.4</v>
       </c>
       <c r="M97">
-        <v>4400.184798725337</v>
+        <v>4102.521864320005</v>
       </c>
       <c r="N97">
-        <v>-3215.784798725337</v>
+        <v>-2918.121864320005</v>
       </c>
       <c r="O97">
-        <v>-401.9730998406671</v>
+        <v>-364.7652330400006</v>
       </c>
       <c r="P97">
-        <v>-2813.81169888467</v>
+        <v>-2553.356631280004</v>
       </c>
       <c r="Q97">
-        <v>-2272.21169888467</v>
+        <v>-2011.756631280005</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>1.212501578750991</v>
+        <v>1.209162885115982</v>
       </c>
       <c r="T97">
-        <v>22.73056499260068</v>
+        <v>22.67610799710984</v>
       </c>
       <c r="U97">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V97">
-        <v>0.03364631413728072</v>
+        <v>0.03608755904206238</v>
       </c>
       <c r="W97">
-        <v>0.2142759968025687</v>
+        <v>0.1992759968025687</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9523,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2691705130982458</v>
+        <v>0.2887004723364991</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9296,13 +9534,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2659466420666151</v>
+        <v>0.2513797073848646</v>
       </c>
       <c r="C98">
-        <v>-13483.05198606697</v>
+        <v>-13076.30360271522</v>
       </c>
       <c r="D98">
-        <v>5874.529910713264</v>
+        <v>6281.278294065016</v>
       </c>
       <c r="E98">
         <v>16477.95492096749</v>
@@ -9329,37 +9567,37 @@
         <v>1184.4</v>
       </c>
       <c r="M98">
-        <v>4446.502533448761</v>
+        <v>4145.706304997057</v>
       </c>
       <c r="N98">
-        <v>-3262.102533448761</v>
+        <v>-2961.306304997057</v>
       </c>
       <c r="O98">
-        <v>-407.7628166810951</v>
+        <v>-370.1632881246322</v>
       </c>
       <c r="P98">
-        <v>-2854.339716767666</v>
+        <v>-2591.143016872425</v>
       </c>
       <c r="Q98">
-        <v>-2312.739716767666</v>
+        <v>-2049.543016872425</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>1.504176973438735</v>
+        <v>1.500003606394974</v>
       </c>
       <c r="T98">
-        <v>28.41320624075079</v>
+        <v>28.34513499638724</v>
       </c>
       <c r="U98">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V98">
-        <v>0.03329583169835072</v>
+        <v>0.03571164696870757</v>
       </c>
       <c r="W98">
-        <v>0.2143537115927767</v>
+        <v>0.1993537115927767</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9605,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2663666535868057</v>
+        <v>0.2856931757496606</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9378,13 +9616,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2677060082332404</v>
+        <v>0.2529890735514899</v>
       </c>
       <c r="C99">
-        <v>-13737.62368503932</v>
+        <v>-13332.97700192233</v>
       </c>
       <c r="D99">
-        <v>5828.844481499043</v>
+        <v>6233.491164616028</v>
       </c>
       <c r="E99">
         <v>16686.84119072562</v>
@@ -9411,37 +9649,37 @@
         <v>1184.4</v>
       </c>
       <c r="M99">
-        <v>4492.820268172186</v>
+        <v>4188.89074567411</v>
       </c>
       <c r="N99">
-        <v>-3308.420268172186</v>
+        <v>-3004.49074567411</v>
       </c>
       <c r="O99">
-        <v>-413.5525335215232</v>
+        <v>-375.5613432092637</v>
       </c>
       <c r="P99">
-        <v>-2894.867734650662</v>
+        <v>-2628.929402464846</v>
       </c>
       <c r="Q99">
-        <v>-2353.267734650663</v>
+        <v>-2087.329402464846</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.990302631251647</v>
+        <v>1.984738141859965</v>
       </c>
       <c r="T99">
-        <v>37.88427498766772</v>
+        <v>37.79351332851632</v>
       </c>
       <c r="U99">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V99">
-        <v>0.0329525757014605</v>
+        <v>0.03534348565975182</v>
       </c>
       <c r="W99">
-        <v>0.2144298240161762</v>
+        <v>0.1994298240161762</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9687,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.263620605611684</v>
+        <v>0.2827478852780145</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9460,13 +9698,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2694653743998657</v>
+        <v>0.2545984397181152</v>
       </c>
       <c r="C100">
-        <v>-13991.49028856407</v>
+        <v>-13588.92877492142</v>
       </c>
       <c r="D100">
-        <v>5783.864147732419</v>
+        <v>6186.425661375071</v>
       </c>
       <c r="E100">
         <v>16895.72746048374</v>
@@ -9493,37 +9731,37 @@
         <v>1184.4</v>
       </c>
       <c r="M100">
-        <v>4539.13800289561</v>
+        <v>4232.075186351163</v>
       </c>
       <c r="N100">
-        <v>-3354.73800289561</v>
+        <v>-3047.675186351163</v>
       </c>
       <c r="O100">
-        <v>-419.3422503619512</v>
+        <v>-380.9593982938954</v>
       </c>
       <c r="P100">
-        <v>-2935.395752533659</v>
+        <v>-2666.715788057268</v>
       </c>
       <c r="Q100">
-        <v>-2393.795752533659</v>
+        <v>-2125.115788057268</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>2.96255394687747</v>
+        <v>2.954207212789947</v>
       </c>
       <c r="T100">
-        <v>56.82641248150158</v>
+        <v>56.69026999277447</v>
       </c>
       <c r="U100">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V100">
-        <v>0.03261632492899662</v>
+        <v>0.0349828378468972</v>
       </c>
       <c r="W100">
-        <v>0.2145043831248125</v>
+        <v>0.1995043831248125</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,7 +9769,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2609305994319729</v>
+        <v>0.2798627027751777</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9542,13 +9780,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.271224740566491</v>
+        <v>0.2562078058847406</v>
       </c>
       <c r="C101">
-        <v>-14244.66799499387</v>
+        <v>-13844.17514497218</v>
       </c>
       <c r="D101">
-        <v>5739.572711060751</v>
+        <v>6140.065561082441</v>
       </c>
       <c r="E101">
         <v>17104.61373024187</v>
@@ -9575,37 +9813,37 @@
         <v>1184.4</v>
       </c>
       <c r="M101">
-        <v>4585.455737619035</v>
+        <v>4275.259627028216</v>
       </c>
       <c r="N101">
-        <v>-3401.055737619035</v>
+        <v>-3090.859627028216</v>
       </c>
       <c r="O101">
-        <v>-425.1319672023794</v>
+        <v>-386.3574533785269</v>
       </c>
       <c r="P101">
-        <v>-2975.923770416656</v>
+        <v>-2704.502173649689</v>
       </c>
       <c r="Q101">
-        <v>-2434.323770416656</v>
+        <v>-2162.902173649689</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>5.87930789375494</v>
+        <v>5.862614425579895</v>
       </c>
       <c r="T101">
-        <v>113.6528249630031</v>
+        <v>113.3805399855489</v>
       </c>
       <c r="U101">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V101">
-        <v>0.03228686710143099</v>
+        <v>0.0346294758484437</v>
       </c>
       <c r="W101">
-        <v>0.2145774359888299</v>
+        <v>0.1995774359888299</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9613,7 +9851,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.258294936811448</v>
+        <v>0.2770358067875496</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/ireland/ireland_heathcare_information_and_technology.xlsx
+++ b/research/traditional_assets/database/data/ireland/ireland_heathcare_information_and_technology.xlsx
@@ -1522,7 +1522,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1659,22 +1659,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1060331274725552</v>
+        <v>0.1059919064590117</v>
       </c>
       <c r="C2">
-        <v>21112.86897858459</v>
+        <v>20917.02254674257</v>
       </c>
       <c r="D2">
-        <v>20417.36897858459</v>
+        <v>20430.4088165007</v>
       </c>
       <c r="E2">
-        <v>-3575.126975812746</v>
+        <v>-3366.240706054618</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>208.8862697581275</v>
       </c>
       <c r="G2">
         <v>695.5</v>
@@ -1695,28 +1695,28 @@
         <v>1184.4</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>11.7470570784545</v>
       </c>
       <c r="N2">
-        <v>1184.4</v>
+        <v>1172.652942921546</v>
       </c>
       <c r="O2">
-        <v>148.05</v>
+        <v>146.5816178651932</v>
       </c>
       <c r="P2">
-        <v>1036.35</v>
+        <v>1026.071325056352</v>
       </c>
       <c r="Q2">
-        <v>1577.95</v>
+        <v>1567.671325056353</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1060331274725552</v>
+        <v>0.106565490972944</v>
       </c>
       <c r="T2">
-        <v>1.174055766301309</v>
+        <v>1.184432521811548</v>
       </c>
       <c r="U2">
         <v>0.0562366166625341</v>
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>100.8252528347998</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1741,22 +1741,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1059919064590117</v>
+        <v>0.1059506854454682</v>
       </c>
       <c r="C3">
-        <v>20917.02254674257</v>
+        <v>20721.19278169433</v>
       </c>
       <c r="D3">
-        <v>20430.4088165007</v>
+        <v>20443.46532121058</v>
       </c>
       <c r="E3">
-        <v>-3366.240706054618</v>
+        <v>-3157.354436296491</v>
       </c>
       <c r="F3">
-        <v>208.8862697581275</v>
+        <v>417.7725395162549</v>
       </c>
       <c r="G3">
         <v>695.5</v>
@@ -1777,28 +1777,28 @@
         <v>1184.4</v>
       </c>
       <c r="M3">
-        <v>11.7470570784545</v>
+        <v>23.49411415690901</v>
       </c>
       <c r="N3">
-        <v>1172.652942921546</v>
+        <v>1160.905885843091</v>
       </c>
       <c r="O3">
-        <v>146.5816178651932</v>
+        <v>145.1132357303864</v>
       </c>
       <c r="P3">
-        <v>1026.071325056352</v>
+        <v>1015.792650112705</v>
       </c>
       <c r="Q3">
-        <v>1567.671325056353</v>
+        <v>1557.392650112705</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.106565490972944</v>
+        <v>0.1071087190345651</v>
       </c>
       <c r="T3">
-        <v>1.184432521811548</v>
+        <v>1.195021047842404</v>
       </c>
       <c r="U3">
         <v>0.0562366166625341</v>
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>100.8252528347998</v>
+        <v>50.4126264173999</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1823,22 +1823,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1059506854454682</v>
+        <v>0.1059094644319246</v>
       </c>
       <c r="C4">
-        <v>20721.19278169433</v>
+        <v>20525.37971541413</v>
       </c>
       <c r="D4">
-        <v>20443.46532121058</v>
+        <v>20456.53852468851</v>
       </c>
       <c r="E4">
-        <v>-3157.354436296491</v>
+        <v>-2948.468166538364</v>
       </c>
       <c r="F4">
-        <v>417.7725395162549</v>
+        <v>626.6588092743823</v>
       </c>
       <c r="G4">
         <v>695.5</v>
@@ -1859,28 +1859,28 @@
         <v>1184.4</v>
       </c>
       <c r="M4">
-        <v>23.49411415690901</v>
+        <v>35.2411712353635</v>
       </c>
       <c r="N4">
-        <v>1160.905885843091</v>
+        <v>1149.158828764637</v>
       </c>
       <c r="O4">
-        <v>145.1132357303864</v>
+        <v>143.6448535955796</v>
       </c>
       <c r="P4">
-        <v>1015.792650112705</v>
+        <v>1005.513975169057</v>
       </c>
       <c r="Q4">
-        <v>1557.392650112705</v>
+        <v>1547.113975169057</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1071087190345651</v>
+        <v>0.1076631476747764</v>
       </c>
       <c r="T4">
-        <v>1.195021047842404</v>
+        <v>1.205827893997607</v>
       </c>
       <c r="U4">
         <v>0.0562366166625341</v>
@@ -1897,7 +1897,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>50.4126264173999</v>
+        <v>33.60841761159995</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1905,22 +1905,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1059094644319246</v>
+        <v>0.1058682434183811</v>
       </c>
       <c r="C5">
-        <v>20525.37971541413</v>
+        <v>20329.58337995811</v>
       </c>
       <c r="D5">
-        <v>20456.53852468851</v>
+        <v>20469.62845899062</v>
       </c>
       <c r="E5">
-        <v>-2948.468166538364</v>
+        <v>-2739.581896780236</v>
       </c>
       <c r="F5">
-        <v>626.6588092743823</v>
+        <v>835.5450790325099</v>
       </c>
       <c r="G5">
         <v>695.5</v>
@@ -1941,28 +1941,28 @@
         <v>1184.4</v>
       </c>
       <c r="M5">
-        <v>35.2411712353635</v>
+        <v>46.98822831381802</v>
       </c>
       <c r="N5">
-        <v>1149.158828764637</v>
+        <v>1137.411771686182</v>
       </c>
       <c r="O5">
-        <v>143.6448535955796</v>
+        <v>142.1764714607727</v>
       </c>
       <c r="P5">
-        <v>1005.513975169057</v>
+        <v>995.2353002254092</v>
       </c>
       <c r="Q5">
-        <v>1547.113975169057</v>
+        <v>1536.835300225409</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1076631476747764</v>
+        <v>0.1082291269116588</v>
       </c>
       <c r="T5">
-        <v>1.205827893997607</v>
+        <v>1.216859882781044</v>
       </c>
       <c r="U5">
         <v>0.0562366166625341</v>
@@ -1979,7 +1979,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>33.60841761159995</v>
+        <v>25.20631320869995</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1987,22 +1987,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1058682434183811</v>
+        <v>0.1058270224048376</v>
       </c>
       <c r="C6">
-        <v>20329.58337995811</v>
+        <v>20133.80380746448</v>
       </c>
       <c r="D6">
-        <v>20469.62845899062</v>
+        <v>20482.73515625512</v>
       </c>
       <c r="E6">
-        <v>-2739.581896780236</v>
+        <v>-2530.695627022109</v>
       </c>
       <c r="F6">
-        <v>835.5450790325099</v>
+        <v>1044.431348790637</v>
       </c>
       <c r="G6">
         <v>695.5</v>
@@ -2023,28 +2023,28 @@
         <v>1184.4</v>
       </c>
       <c r="M6">
-        <v>46.98822831381802</v>
+        <v>58.73528539227252</v>
       </c>
       <c r="N6">
-        <v>1137.411771686182</v>
+        <v>1125.664714607728</v>
       </c>
       <c r="O6">
-        <v>142.1764714607727</v>
+        <v>140.7080893259659</v>
       </c>
       <c r="P6">
-        <v>995.2353002254092</v>
+        <v>984.9566252817616</v>
       </c>
       <c r="Q6">
-        <v>1536.835300225409</v>
+        <v>1526.556625281762</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1082291269116588</v>
+        <v>0.1088070215008966</v>
       </c>
       <c r="T6">
-        <v>1.216859882781044</v>
+        <v>1.228124123959922</v>
       </c>
       <c r="U6">
         <v>0.0562366166625341</v>
@@ -2061,7 +2061,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>25.20631320869995</v>
+        <v>20.16505056695996</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2069,22 +2069,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1058270224048376</v>
+        <v>0.1057858013912941</v>
       </c>
       <c r="C7">
-        <v>20133.80380746448</v>
+        <v>19938.04103015386</v>
       </c>
       <c r="D7">
-        <v>20482.73515625512</v>
+        <v>20495.85864870262</v>
       </c>
       <c r="E7">
-        <v>-2530.695627022109</v>
+        <v>-2321.809357263981</v>
       </c>
       <c r="F7">
-        <v>1044.431348790637</v>
+        <v>1253.317618548765</v>
       </c>
       <c r="G7">
         <v>695.5</v>
@@ -2105,28 +2105,28 @@
         <v>1184.4</v>
       </c>
       <c r="M7">
-        <v>58.73528539227252</v>
+        <v>70.48234247072702</v>
       </c>
       <c r="N7">
-        <v>1125.664714607728</v>
+        <v>1113.917657529273</v>
       </c>
       <c r="O7">
-        <v>140.7080893259659</v>
+        <v>139.2397071911591</v>
       </c>
       <c r="P7">
-        <v>984.9566252817616</v>
+        <v>974.677950338114</v>
       </c>
       <c r="Q7">
-        <v>1526.556625281762</v>
+        <v>1516.277950338114</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1088070215008966</v>
+        <v>0.1093972117196926</v>
       </c>
       <c r="T7">
-        <v>1.228124123959922</v>
+        <v>1.239628029844734</v>
       </c>
       <c r="U7">
         <v>0.0562366166625341</v>
@@ -2143,7 +2143,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>20.16505056695996</v>
+        <v>16.80420880579997</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2151,22 +2151,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1057858013912941</v>
+        <v>0.1057445803777506</v>
       </c>
       <c r="C8">
-        <v>19938.04103015386</v>
+        <v>19742.29508032943</v>
       </c>
       <c r="D8">
-        <v>20495.85864870262</v>
+        <v>20508.99896863632</v>
       </c>
       <c r="E8">
-        <v>-2321.809357263981</v>
+        <v>-2112.923087505854</v>
       </c>
       <c r="F8">
-        <v>1253.317618548765</v>
+        <v>1462.203888306892</v>
       </c>
       <c r="G8">
         <v>695.5</v>
@@ -2187,28 +2187,28 @@
         <v>1184.4</v>
       </c>
       <c r="M8">
-        <v>70.482342470727</v>
+        <v>82.22939954918151</v>
       </c>
       <c r="N8">
-        <v>1113.917657529273</v>
+        <v>1102.170600450818</v>
       </c>
       <c r="O8">
-        <v>139.2397071911591</v>
+        <v>137.7713250563523</v>
       </c>
       <c r="P8">
-        <v>974.677950338114</v>
+        <v>964.3992753944661</v>
       </c>
       <c r="Q8">
-        <v>1516.277950338114</v>
+        <v>1505.999275394466</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1093972117196926</v>
+        <v>0.1100000942012584</v>
       </c>
       <c r="T8">
-        <v>1.239628029844734</v>
+        <v>1.251379331555025</v>
       </c>
       <c r="U8">
         <v>0.0562366166625341</v>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>16.80420880579997</v>
+        <v>14.40360754782855</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2233,22 +2233,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1057445803777506</v>
+        <v>0.1057033593642071</v>
       </c>
       <c r="C9">
-        <v>19742.29508032943</v>
+        <v>19546.56599037734</v>
       </c>
       <c r="D9">
-        <v>20508.99896863633</v>
+        <v>20522.15614844236</v>
       </c>
       <c r="E9">
-        <v>-2112.923087505854</v>
+        <v>-1904.036817747726</v>
       </c>
       <c r="F9">
-        <v>1462.203888306892</v>
+        <v>1671.09015806502</v>
       </c>
       <c r="G9">
         <v>695.5</v>
@@ -2269,28 +2269,28 @@
         <v>1184.4</v>
       </c>
       <c r="M9">
-        <v>82.22939954918154</v>
+        <v>93.97645662763604</v>
       </c>
       <c r="N9">
-        <v>1102.170600450818</v>
+        <v>1090.423543372364</v>
       </c>
       <c r="O9">
-        <v>137.7713250563523</v>
+        <v>136.3029429215455</v>
       </c>
       <c r="P9">
-        <v>964.3992753944661</v>
+        <v>954.1206004508185</v>
       </c>
       <c r="Q9">
-        <v>1505.999275394466</v>
+        <v>1495.720600450818</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1100000942012584</v>
+        <v>0.1106160828237279</v>
       </c>
       <c r="T9">
-        <v>1.251379331555025</v>
+        <v>1.263386096345974</v>
       </c>
       <c r="U9">
         <v>0.0562366166625341</v>
@@ -2307,7 +2307,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>14.40360754782854</v>
+        <v>12.60315660434997</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1057033593642071</v>
+        <v>0.1056621383506635</v>
       </c>
       <c r="C10">
-        <v>19546.56599037734</v>
+        <v>19350.85379276686</v>
       </c>
       <c r="D10">
-        <v>20522.15614844236</v>
+        <v>20535.33022059001</v>
       </c>
       <c r="E10">
-        <v>-1904.036817747726</v>
+        <v>-1695.150547989599</v>
       </c>
       <c r="F10">
-        <v>1671.09015806502</v>
+        <v>1879.976427823147</v>
       </c>
       <c r="G10">
         <v>695.5</v>
@@ -2351,28 +2351,28 @@
         <v>1184.4</v>
       </c>
       <c r="M10">
-        <v>93.97645662763604</v>
+        <v>105.7235137060905</v>
       </c>
       <c r="N10">
-        <v>1090.423543372364</v>
+        <v>1078.67648629391</v>
       </c>
       <c r="O10">
-        <v>136.3029429215455</v>
+        <v>134.8345607867387</v>
       </c>
       <c r="P10">
-        <v>954.1206004508185</v>
+        <v>943.8419255071709</v>
       </c>
       <c r="Q10">
-        <v>1495.720600450818</v>
+        <v>1485.441925507171</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1106160828237279</v>
+        <v>0.1112456096576802</v>
       </c>
       <c r="T10">
-        <v>1.263386096345974</v>
+        <v>1.275656746077384</v>
       </c>
       <c r="U10">
         <v>0.0562366166625341</v>
@@ -2389,7 +2389,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>12.60315660434997</v>
+        <v>11.20280587053331</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2397,22 +2397,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1056621383506635</v>
+        <v>0.10562091733712</v>
       </c>
       <c r="C11">
-        <v>19350.85379276686</v>
+        <v>19155.15852005067</v>
       </c>
       <c r="D11">
-        <v>20535.33022059001</v>
+        <v>20548.52121763194</v>
       </c>
       <c r="E11">
-        <v>-1695.150547989599</v>
+        <v>-1486.264278231472</v>
       </c>
       <c r="F11">
-        <v>1879.976427823147</v>
+        <v>2088.862697581274</v>
       </c>
       <c r="G11">
         <v>695.5</v>
@@ -2433,28 +2433,28 @@
         <v>1184.4</v>
       </c>
       <c r="M11">
-        <v>105.7235137060905</v>
+        <v>117.470570784545</v>
       </c>
       <c r="N11">
-        <v>1078.67648629391</v>
+        <v>1066.929429215455</v>
       </c>
       <c r="O11">
-        <v>134.8345607867387</v>
+        <v>133.3661786519319</v>
       </c>
       <c r="P11">
-        <v>943.8419255071709</v>
+        <v>933.5632505635231</v>
       </c>
       <c r="Q11">
-        <v>1485.441925507171</v>
+        <v>1475.163250563523</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1112456096576802</v>
+        <v>0.1118891259768314</v>
       </c>
       <c r="T11">
-        <v>1.275656746077384</v>
+        <v>1.288200076913937</v>
       </c>
       <c r="U11">
         <v>0.0562366166625341</v>
@@ -2471,7 +2471,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>11.20280587053331</v>
+        <v>10.08252528347998</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2479,22 +2479,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.10562091733712</v>
+        <v>0.1055796963235765</v>
       </c>
       <c r="C12">
-        <v>19155.15852005067</v>
+        <v>18959.48020486518</v>
       </c>
       <c r="D12">
-        <v>20548.52121763194</v>
+        <v>20561.72917220458</v>
       </c>
       <c r="E12">
-        <v>-1486.264278231472</v>
+        <v>-1277.378008473344</v>
       </c>
       <c r="F12">
-        <v>2088.862697581274</v>
+        <v>2297.748967339402</v>
       </c>
       <c r="G12">
         <v>695.5</v>
@@ -2515,28 +2515,28 @@
         <v>1184.4</v>
       </c>
       <c r="M12">
-        <v>117.470570784545</v>
+        <v>129.2176278629995</v>
       </c>
       <c r="N12">
-        <v>1066.929429215455</v>
+        <v>1055.182372137001</v>
       </c>
       <c r="O12">
-        <v>133.3661786519319</v>
+        <v>131.8977965171251</v>
       </c>
       <c r="P12">
-        <v>933.5632505635231</v>
+        <v>923.2845756198756</v>
       </c>
       <c r="Q12">
-        <v>1475.163250563523</v>
+        <v>1464.884575619876</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1118891259768314</v>
+        <v>0.1125471033368624</v>
       </c>
       <c r="T12">
-        <v>1.288200076913937</v>
+        <v>1.301025280353558</v>
       </c>
       <c r="U12">
         <v>0.0562366166625341</v>
@@ -2553,7 +2553,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>10.08252528347998</v>
+        <v>9.165932075890892</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2561,22 +2561,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1055796963235765</v>
+        <v>0.105695975310033</v>
       </c>
       <c r="C13">
-        <v>18959.48020486518</v>
+        <v>18713.37958281746</v>
       </c>
       <c r="D13">
-        <v>20561.72917220458</v>
+        <v>20524.51481991499</v>
       </c>
       <c r="E13">
-        <v>-1277.378008473344</v>
+        <v>-1068.491738715217</v>
       </c>
       <c r="F13">
-        <v>2297.748967339402</v>
+        <v>2506.635237097529</v>
       </c>
       <c r="G13">
         <v>695.5</v>
@@ -2597,45 +2597,45 @@
         <v>1184.4</v>
       </c>
       <c r="M13">
-        <v>129.2176278629995</v>
+        <v>144.7246377971003</v>
       </c>
       <c r="N13">
-        <v>1055.182372137001</v>
+        <v>1039.6753622029</v>
       </c>
       <c r="O13">
-        <v>131.8977965171251</v>
+        <v>129.9594202753625</v>
       </c>
       <c r="P13">
-        <v>923.2845756198756</v>
+        <v>909.7159419275373</v>
       </c>
       <c r="Q13">
-        <v>1464.884575619876</v>
+        <v>1451.315941927537</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1125471033368624</v>
+        <v>0.1132200347278033</v>
       </c>
       <c r="T13">
-        <v>1.301025280353558</v>
+        <v>1.314141965689534</v>
       </c>
       <c r="U13">
-        <v>0.0562366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V13">
         <v>0.125</v>
       </c>
       <c r="W13">
-        <v>0.04920703957971734</v>
+        <v>0.05051953957971733</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y13">
-        <v>9.165932075890892</v>
+        <v>8.183817337725827</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2643,22 +2643,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.105695975310033</v>
+        <v>0.1056678792964894</v>
       </c>
       <c r="C14">
-        <v>18713.37958281746</v>
+        <v>18513.47291655999</v>
       </c>
       <c r="D14">
-        <v>20524.51481991499</v>
+        <v>20533.49442341565</v>
       </c>
       <c r="E14">
-        <v>-1068.491738715217</v>
+        <v>-859.6054689570888</v>
       </c>
       <c r="F14">
-        <v>2506.635237097529</v>
+        <v>2715.521506855657</v>
       </c>
       <c r="G14">
         <v>695.5</v>
@@ -2679,28 +2679,28 @@
         <v>1184.4</v>
       </c>
       <c r="M14">
-        <v>144.7246377971003</v>
+        <v>156.785024280192</v>
       </c>
       <c r="N14">
-        <v>1039.6753622029</v>
+        <v>1027.614975719808</v>
       </c>
       <c r="O14">
-        <v>129.9594202753625</v>
+        <v>128.451871964976</v>
       </c>
       <c r="P14">
-        <v>909.7159419275373</v>
+        <v>899.1631037548322</v>
       </c>
       <c r="Q14">
-        <v>1451.315941927537</v>
+        <v>1440.763103754832</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1132200347278033</v>
+        <v>0.1139084358058922</v>
       </c>
       <c r="T14">
-        <v>1.314141965689534</v>
+        <v>1.327560184021739</v>
       </c>
       <c r="U14">
         <v>0.05773661666253409</v>
@@ -2717,7 +2717,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>8.183817337725827</v>
+        <v>7.554292927131532</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2725,22 +2725,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1056678792964894</v>
+        <v>0.1056397832829459</v>
       </c>
       <c r="C15">
-        <v>18513.47291655999</v>
+        <v>18313.57411100692</v>
       </c>
       <c r="D15">
-        <v>20533.49442341565</v>
+        <v>20542.4818876207</v>
       </c>
       <c r="E15">
-        <v>-859.6054689570888</v>
+        <v>-650.7191991989612</v>
       </c>
       <c r="F15">
-        <v>2715.521506855657</v>
+        <v>2924.407776613785</v>
       </c>
       <c r="G15">
         <v>695.5</v>
@@ -2761,28 +2761,28 @@
         <v>1184.4</v>
       </c>
       <c r="M15">
-        <v>156.785024280192</v>
+        <v>168.8454107632837</v>
       </c>
       <c r="N15">
-        <v>1027.614975719808</v>
+        <v>1015.554589236716</v>
       </c>
       <c r="O15">
-        <v>128.451871964976</v>
+        <v>126.9443236545895</v>
       </c>
       <c r="P15">
-        <v>899.1631037548322</v>
+        <v>888.6102655821268</v>
       </c>
       <c r="Q15">
-        <v>1440.763103754832</v>
+        <v>1430.210265582127</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1139084358058922</v>
+        <v>0.1146128462113785</v>
       </c>
       <c r="T15">
-        <v>1.327560184021739</v>
+        <v>1.341290453943065</v>
       </c>
       <c r="U15">
         <v>0.05773661666253409</v>
@@ -2799,7 +2799,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>7.554292927131532</v>
+        <v>7.014700575193564</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2807,22 +2807,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1056397832829459</v>
+        <v>0.1058348122694024</v>
       </c>
       <c r="C16">
-        <v>18313.57411100692</v>
+        <v>18042.46294640996</v>
       </c>
       <c r="D16">
-        <v>20542.4818876207</v>
+        <v>20480.25699278187</v>
       </c>
       <c r="E16">
-        <v>-650.7191991989612</v>
+        <v>-441.8329294408336</v>
       </c>
       <c r="F16">
-        <v>2924.407776613785</v>
+        <v>3133.294046371912</v>
       </c>
       <c r="G16">
         <v>695.5</v>
@@ -2843,45 +2843,45 @@
         <v>1184.4</v>
       </c>
       <c r="M16">
-        <v>168.8454107632837</v>
+        <v>186.2323971252077</v>
       </c>
       <c r="N16">
-        <v>1015.554589236716</v>
+        <v>998.1676028747925</v>
       </c>
       <c r="O16">
-        <v>126.9443236545895</v>
+        <v>124.7709503593491</v>
       </c>
       <c r="P16">
-        <v>888.6102655821268</v>
+        <v>873.3966525154434</v>
       </c>
       <c r="Q16">
-        <v>1430.210265582127</v>
+        <v>1414.996652515443</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1146128462113785</v>
+        <v>0.1153338309793468</v>
       </c>
       <c r="T16">
-        <v>1.341290453943065</v>
+        <v>1.355343789039011</v>
       </c>
       <c r="U16">
-        <v>0.05773661666253409</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V16">
         <v>0.125</v>
       </c>
       <c r="W16">
-        <v>0.05051953957971733</v>
+        <v>0.05200703957971733</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y16">
-        <v>7.014700575193564</v>
+        <v>6.359795708389582</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2889,22 +2889,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1058348122694024</v>
+        <v>0.1058215912558589</v>
       </c>
       <c r="C17">
-        <v>18042.46294640996</v>
+        <v>17837.78298818478</v>
       </c>
       <c r="D17">
-        <v>20480.25699278187</v>
+        <v>20484.46330431482</v>
       </c>
       <c r="E17">
-        <v>-441.8329294408341</v>
+        <v>-232.9466596827065</v>
       </c>
       <c r="F17">
-        <v>3133.294046371912</v>
+        <v>3342.18031613004</v>
       </c>
       <c r="G17">
         <v>695.5</v>
@@ -2925,28 +2925,28 @@
         <v>1184.4</v>
       </c>
       <c r="M17">
-        <v>186.2323971252077</v>
+        <v>198.6478902668882</v>
       </c>
       <c r="N17">
-        <v>998.1676028747925</v>
+        <v>985.7521097331119</v>
       </c>
       <c r="O17">
-        <v>124.7709503593491</v>
+        <v>123.219013716639</v>
       </c>
       <c r="P17">
-        <v>873.3966525154434</v>
+        <v>862.5330960164729</v>
       </c>
       <c r="Q17">
-        <v>1414.996652515443</v>
+        <v>1404.133096016473</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1153338309793468</v>
+        <v>0.1160719820513144</v>
       </c>
       <c r="T17">
-        <v>1.355343789039011</v>
+        <v>1.369731727351527</v>
       </c>
       <c r="U17">
         <v>0.05943661666253409</v>
@@ -2963,7 +2963,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>6.359795708389583</v>
+        <v>5.962308476615234</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2971,22 +2971,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1058215912558589</v>
+        <v>0.1058083702423154</v>
       </c>
       <c r="C18">
-        <v>17837.78298818478</v>
+        <v>17633.10475813042</v>
       </c>
       <c r="D18">
-        <v>20484.46330431482</v>
+        <v>20488.67134401859</v>
       </c>
       <c r="E18">
-        <v>-232.9466596827065</v>
+        <v>-24.06038992457889</v>
       </c>
       <c r="F18">
-        <v>3342.18031613004</v>
+        <v>3551.066585888167</v>
       </c>
       <c r="G18">
         <v>695.5</v>
@@ -3007,28 +3007,28 @@
         <v>1184.4</v>
       </c>
       <c r="M18">
-        <v>198.6478902668882</v>
+        <v>211.0633834085687</v>
       </c>
       <c r="N18">
-        <v>985.7521097331119</v>
+        <v>973.3366165914314</v>
       </c>
       <c r="O18">
-        <v>123.219013716639</v>
+        <v>121.6670770739289</v>
       </c>
       <c r="P18">
-        <v>862.5330960164729</v>
+        <v>851.6695395175025</v>
       </c>
       <c r="Q18">
-        <v>1404.133096016473</v>
+        <v>1393.269539517502</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1160719820513144</v>
+        <v>0.1168279198961005</v>
       </c>
       <c r="T18">
-        <v>1.369731727351527</v>
+        <v>1.384466362972779</v>
       </c>
       <c r="U18">
         <v>0.05943661666253409</v>
@@ -3045,7 +3045,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>5.962308476615234</v>
+        <v>5.611584448579043</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3053,22 +3053,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1058083702423154</v>
+        <v>0.1059211492287718</v>
       </c>
       <c r="C19">
-        <v>17633.10475813042</v>
+        <v>17388.37814960157</v>
       </c>
       <c r="D19">
-        <v>20488.67134401859</v>
+        <v>20452.83100524787</v>
       </c>
       <c r="E19">
-        <v>-24.06038992457889</v>
+        <v>184.8258798335487</v>
       </c>
       <c r="F19">
-        <v>3551.066585888167</v>
+        <v>3759.952855646295</v>
       </c>
       <c r="G19">
         <v>695.5</v>
@@ -3089,45 +3089,45 @@
         <v>1184.4</v>
       </c>
       <c r="M19">
-        <v>211.0633834085687</v>
+        <v>226.4868388347662</v>
       </c>
       <c r="N19">
-        <v>973.3366165914314</v>
+        <v>957.9131611652339</v>
       </c>
       <c r="O19">
-        <v>121.6670770739289</v>
+        <v>119.7391451456542</v>
       </c>
       <c r="P19">
-        <v>851.6695395175025</v>
+        <v>838.1740160195797</v>
       </c>
       <c r="Q19">
-        <v>1393.269539517502</v>
+        <v>1379.77401601958</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1168279198961005</v>
+        <v>0.117602295249296</v>
       </c>
       <c r="T19">
-        <v>1.384466362972779</v>
+        <v>1.399560379950646</v>
       </c>
       <c r="U19">
-        <v>0.05943661666253409</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V19">
         <v>0.125</v>
       </c>
       <c r="W19">
-        <v>0.05200703957971733</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y19">
-        <v>5.611584448579043</v>
+        <v>5.229442938466198</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3135,22 +3135,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1059211492287718</v>
+        <v>0.1059149282152283</v>
       </c>
       <c r="C20">
-        <v>17388.37814960157</v>
+        <v>17181.46560468606</v>
       </c>
       <c r="D20">
-        <v>20452.83100524786</v>
+        <v>20454.80473009048</v>
       </c>
       <c r="E20">
-        <v>184.8258798335482</v>
+        <v>393.7121495916758</v>
       </c>
       <c r="F20">
-        <v>3759.952855646294</v>
+        <v>3968.839125404422</v>
       </c>
       <c r="G20">
         <v>695.5</v>
@@ -3171,28 +3171,28 @@
         <v>1184.4</v>
       </c>
       <c r="M20">
-        <v>226.4868388347662</v>
+        <v>239.0694409922532</v>
       </c>
       <c r="N20">
-        <v>957.9131611652339</v>
+        <v>945.3305590077468</v>
       </c>
       <c r="O20">
-        <v>119.7391451456542</v>
+        <v>118.1663198759684</v>
       </c>
       <c r="P20">
-        <v>838.1740160195797</v>
+        <v>827.1642391317785</v>
       </c>
       <c r="Q20">
-        <v>1379.77401601958</v>
+        <v>1368.764239131779</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.117602295249296</v>
+        <v>0.1183957909815827</v>
       </c>
       <c r="T20">
-        <v>1.399560379950646</v>
+        <v>1.415027088705744</v>
       </c>
       <c r="U20">
         <v>0.0602366166625341</v>
@@ -3209,7 +3209,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.229442938466198</v>
+        <v>4.954209099599556</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3217,22 +3217,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1059149282152283</v>
+        <v>0.1059087072016848</v>
       </c>
       <c r="C21">
-        <v>17181.46560468606</v>
+        <v>16974.55344074135</v>
       </c>
       <c r="D21">
-        <v>20454.80473009048</v>
+        <v>20456.7788359039</v>
       </c>
       <c r="E21">
-        <v>393.7121495916758</v>
+        <v>602.598419349803</v>
       </c>
       <c r="F21">
-        <v>3968.839125404422</v>
+        <v>4177.725395162549</v>
       </c>
       <c r="G21">
         <v>695.5</v>
@@ -3253,28 +3253,28 @@
         <v>1184.4</v>
       </c>
       <c r="M21">
-        <v>239.0694409922532</v>
+        <v>251.6520431497403</v>
       </c>
       <c r="N21">
-        <v>945.3305590077468</v>
+        <v>932.7479568502598</v>
       </c>
       <c r="O21">
-        <v>118.1663198759684</v>
+        <v>116.5934946062825</v>
       </c>
       <c r="P21">
-        <v>827.1642391317785</v>
+        <v>816.1544622439774</v>
       </c>
       <c r="Q21">
-        <v>1368.764239131779</v>
+        <v>1357.754462243977</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1183957909815827</v>
+        <v>0.1192091241071767</v>
       </c>
       <c r="T21">
-        <v>1.415027088705744</v>
+        <v>1.43088046517972</v>
       </c>
       <c r="U21">
         <v>0.0602366166625341</v>
@@ -3291,7 +3291,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>4.954209099599556</v>
+        <v>4.706498644619578</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3299,22 +3299,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1059087072016848</v>
+        <v>0.1059024861881413</v>
       </c>
       <c r="C22">
-        <v>16974.55344074135</v>
+        <v>16767.64165787775</v>
       </c>
       <c r="D22">
-        <v>20456.7788359039</v>
+        <v>20458.75332279843</v>
       </c>
       <c r="E22">
-        <v>602.598419349803</v>
+        <v>811.484689107931</v>
       </c>
       <c r="F22">
-        <v>4177.725395162549</v>
+        <v>4386.611664920677</v>
       </c>
       <c r="G22">
         <v>695.5</v>
@@ -3335,28 +3335,28 @@
         <v>1184.4</v>
       </c>
       <c r="M22">
-        <v>251.6520431497403</v>
+        <v>264.2346453072273</v>
       </c>
       <c r="N22">
-        <v>932.7479568502598</v>
+        <v>920.1653546927728</v>
       </c>
       <c r="O22">
-        <v>116.5934946062825</v>
+        <v>115.0206693365966</v>
       </c>
       <c r="P22">
-        <v>816.1544622439774</v>
+        <v>805.1446853561762</v>
       </c>
       <c r="Q22">
-        <v>1357.754462243977</v>
+        <v>1346.744685356176</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1192091241071767</v>
+        <v>0.1200430479448109</v>
       </c>
       <c r="T22">
-        <v>1.43088046517972</v>
+        <v>1.447135192956835</v>
       </c>
       <c r="U22">
         <v>0.0602366166625341</v>
@@ -3373,7 +3373,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>4.706498644619578</v>
+        <v>4.482379661542454</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1059024861881413</v>
+        <v>0.1058962651745978</v>
       </c>
       <c r="C23">
-        <v>16767.64165787776</v>
+        <v>16560.73025620564</v>
       </c>
       <c r="D23">
-        <v>20458.75332279844</v>
+        <v>20460.72819088444</v>
       </c>
       <c r="E23">
-        <v>811.4846891079301</v>
+        <v>1020.370958866058</v>
       </c>
       <c r="F23">
-        <v>4386.611664920676</v>
+        <v>4595.497934678804</v>
       </c>
       <c r="G23">
         <v>695.5</v>
@@ -3417,28 +3417,28 @@
         <v>1184.4</v>
       </c>
       <c r="M23">
-        <v>264.2346453072273</v>
+        <v>276.8172474647143</v>
       </c>
       <c r="N23">
-        <v>920.1653546927728</v>
+        <v>907.5827525352859</v>
       </c>
       <c r="O23">
-        <v>115.0206693365966</v>
+        <v>113.4478440669107</v>
       </c>
       <c r="P23">
-        <v>805.1446853561762</v>
+        <v>794.1349084683751</v>
       </c>
       <c r="Q23">
-        <v>1346.744685356176</v>
+        <v>1335.734908468375</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1200430479448109</v>
+        <v>0.1208983544449486</v>
       </c>
       <c r="T23">
-        <v>1.447135192956835</v>
+        <v>1.463806708625671</v>
       </c>
       <c r="U23">
         <v>0.0602366166625341</v>
@@ -3455,7 +3455,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>4.482379661542455</v>
+        <v>4.278635131472344</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3463,22 +3463,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1058962651745978</v>
+        <v>0.1060912941610542</v>
       </c>
       <c r="C24">
-        <v>16560.73025620564</v>
+        <v>16290.11263946518</v>
       </c>
       <c r="D24">
-        <v>20460.72819088444</v>
+        <v>20398.99684390211</v>
       </c>
       <c r="E24">
-        <v>1020.370958866058</v>
+        <v>1229.257228624186</v>
       </c>
       <c r="F24">
-        <v>4595.497934678804</v>
+        <v>4804.384204436932</v>
       </c>
       <c r="G24">
         <v>695.5</v>
@@ -3499,45 +3499,45 @@
         <v>1184.4</v>
       </c>
       <c r="M24">
-        <v>276.8172474647143</v>
+        <v>294.2042338266382</v>
       </c>
       <c r="N24">
-        <v>907.5827525352859</v>
+        <v>890.1957661733618</v>
       </c>
       <c r="O24">
-        <v>113.4478440669107</v>
+        <v>111.2744707716702</v>
       </c>
       <c r="P24">
-        <v>794.1349084683751</v>
+        <v>778.9212954016916</v>
       </c>
       <c r="Q24">
-        <v>1335.734908468375</v>
+        <v>1320.521295401692</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1208983544449486</v>
+        <v>0.1217758766983367</v>
       </c>
       <c r="T24">
-        <v>1.463806708625671</v>
+        <v>1.480911250675515</v>
       </c>
       <c r="U24">
-        <v>0.0602366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V24">
         <v>0.125</v>
       </c>
       <c r="W24">
-        <v>0.05270703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y24">
-        <v>4.278635131472344</v>
+        <v>4.025774831975788</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3545,22 +3545,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1060912941610542</v>
+        <v>0.1060938231475107</v>
       </c>
       <c r="C25">
-        <v>16290.11263946518</v>
+        <v>16080.42833123704</v>
       </c>
       <c r="D25">
-        <v>20398.99684390211</v>
+        <v>20398.19880543209</v>
       </c>
       <c r="E25">
-        <v>1229.257228624186</v>
+        <v>1438.143498382313</v>
       </c>
       <c r="F25">
-        <v>4804.384204436932</v>
+        <v>5013.270474195059</v>
       </c>
       <c r="G25">
         <v>695.5</v>
@@ -3581,28 +3581,28 @@
         <v>1184.4</v>
       </c>
       <c r="M25">
-        <v>294.2042338266382</v>
+        <v>306.9957222538834</v>
       </c>
       <c r="N25">
-        <v>890.1957661733618</v>
+        <v>877.4042777461167</v>
       </c>
       <c r="O25">
-        <v>111.2744707716702</v>
+        <v>109.6755347182646</v>
       </c>
       <c r="P25">
-        <v>778.9212954016916</v>
+        <v>767.7287430278521</v>
       </c>
       <c r="Q25">
-        <v>1320.521295401692</v>
+        <v>1309.328743027852</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1217758766983367</v>
+        <v>0.1226764916426034</v>
       </c>
       <c r="T25">
-        <v>1.480911250675515</v>
+        <v>1.498465912252987</v>
       </c>
       <c r="U25">
         <v>0.0612366166625341</v>
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.025774831975788</v>
+        <v>3.858034213976797</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3627,22 +3627,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1060938231475107</v>
+        <v>0.1060963521339672</v>
       </c>
       <c r="C26">
-        <v>16080.42833123704</v>
+        <v>15870.74408544731</v>
       </c>
       <c r="D26">
-        <v>20398.1988054321</v>
+        <v>20397.40082940049</v>
       </c>
       <c r="E26">
-        <v>1438.143498382312</v>
+        <v>1647.02976814044</v>
       </c>
       <c r="F26">
-        <v>5013.270474195058</v>
+        <v>5222.156743953186</v>
       </c>
       <c r="G26">
         <v>695.5</v>
@@ -3663,28 +3663,28 @@
         <v>1184.4</v>
       </c>
       <c r="M26">
-        <v>306.9957222538833</v>
+        <v>319.7872106811285</v>
       </c>
       <c r="N26">
-        <v>877.4042777461168</v>
+        <v>864.6127893188716</v>
       </c>
       <c r="O26">
-        <v>109.6755347182646</v>
+        <v>108.0765986648589</v>
       </c>
       <c r="P26">
-        <v>767.7287430278523</v>
+        <v>756.5361906540127</v>
       </c>
       <c r="Q26">
-        <v>1309.328743027852</v>
+        <v>1298.136190654013</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1226764916426033</v>
+        <v>0.1236011229853838</v>
       </c>
       <c r="T26">
-        <v>1.498465912252986</v>
+        <v>1.516488698139191</v>
       </c>
       <c r="U26">
         <v>0.0612366166625341</v>
@@ -3701,7 +3701,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>3.858034213976798</v>
+        <v>3.703712845417725</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3709,22 +3709,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1060963521339672</v>
+        <v>0.1060988811204237</v>
       </c>
       <c r="C27">
-        <v>15870.74408544731</v>
+        <v>15661.05990208865</v>
       </c>
       <c r="D27">
-        <v>20397.40082940049</v>
+        <v>20396.60291579997</v>
       </c>
       <c r="E27">
-        <v>1647.02976814044</v>
+        <v>1855.916037898568</v>
       </c>
       <c r="F27">
-        <v>5222.156743953186</v>
+        <v>5431.043013711314</v>
       </c>
       <c r="G27">
         <v>695.5</v>
@@ -3745,28 +3745,28 @@
         <v>1184.4</v>
       </c>
       <c r="M27">
-        <v>319.7872106811285</v>
+        <v>332.5786991083737</v>
       </c>
       <c r="N27">
-        <v>864.6127893188716</v>
+        <v>851.8213008916264</v>
       </c>
       <c r="O27">
-        <v>108.0765986648589</v>
+        <v>106.4776626114533</v>
       </c>
       <c r="P27">
-        <v>756.5361906540127</v>
+        <v>745.3436382801731</v>
       </c>
       <c r="Q27">
-        <v>1298.136190654013</v>
+        <v>1286.943638280173</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1236011229853838</v>
+        <v>0.1245507443644556</v>
       </c>
       <c r="T27">
-        <v>1.516488698139191</v>
+        <v>1.534998586346644</v>
       </c>
       <c r="U27">
         <v>0.0612366166625341</v>
@@ -3783,7 +3783,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>3.703712845417725</v>
+        <v>3.561262351363197</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3791,22 +3791,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1060988811204237</v>
+        <v>0.1061014101068802</v>
       </c>
       <c r="C28">
-        <v>15661.05990208865</v>
+        <v>15451.37578115376</v>
       </c>
       <c r="D28">
-        <v>20396.60291579997</v>
+        <v>20395.8050646232</v>
       </c>
       <c r="E28">
-        <v>1855.916037898568</v>
+        <v>2064.802307656696</v>
       </c>
       <c r="F28">
-        <v>5431.043013711314</v>
+        <v>5639.929283469442</v>
       </c>
       <c r="G28">
         <v>695.5</v>
@@ -3827,28 +3827,28 @@
         <v>1184.4</v>
       </c>
       <c r="M28">
-        <v>332.5786991083737</v>
+        <v>345.3701875356188</v>
       </c>
       <c r="N28">
-        <v>851.8213008916264</v>
+        <v>839.0298124643813</v>
       </c>
       <c r="O28">
-        <v>106.4776626114533</v>
+        <v>104.8787265580477</v>
       </c>
       <c r="P28">
-        <v>745.3436382801731</v>
+        <v>734.1510859063336</v>
       </c>
       <c r="Q28">
-        <v>1286.943638280173</v>
+        <v>1275.751085906334</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1245507443644556</v>
+        <v>0.1255263827676116</v>
       </c>
       <c r="T28">
-        <v>1.534998586346644</v>
+        <v>1.554015594778959</v>
       </c>
       <c r="U28">
         <v>0.0612366166625341</v>
@@ -3865,7 +3865,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>3.561262351363197</v>
+        <v>3.429363745757153</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3873,22 +3873,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1061014101068802</v>
+        <v>0.1061039390933366</v>
       </c>
       <c r="C29">
-        <v>15451.37578115376</v>
+        <v>15241.6917226353</v>
       </c>
       <c r="D29">
-        <v>20395.8050646232</v>
+        <v>20395.00727586287</v>
       </c>
       <c r="E29">
-        <v>2064.802307656696</v>
+        <v>2273.688577414824</v>
       </c>
       <c r="F29">
-        <v>5639.929283469442</v>
+        <v>5848.81555322757</v>
       </c>
       <c r="G29">
         <v>695.5</v>
@@ -3909,28 +3909,28 @@
         <v>1184.4</v>
       </c>
       <c r="M29">
-        <v>345.3701875356188</v>
+        <v>358.161675962864</v>
       </c>
       <c r="N29">
-        <v>839.0298124643813</v>
+        <v>826.2383240371362</v>
       </c>
       <c r="O29">
-        <v>104.8787265580477</v>
+        <v>103.279790504642</v>
       </c>
       <c r="P29">
-        <v>734.1510859063336</v>
+        <v>722.9585335324941</v>
       </c>
       <c r="Q29">
-        <v>1275.751085906334</v>
+        <v>1264.558533532494</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1255263827676116</v>
+        <v>0.1265291222375219</v>
       </c>
       <c r="T29">
-        <v>1.554015594778959</v>
+        <v>1.573560853445505</v>
       </c>
       <c r="U29">
         <v>0.0612366166625341</v>
@@ -3947,7 +3947,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.429363745757153</v>
+        <v>3.306886469122969</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3955,22 +3955,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1061039390933366</v>
+        <v>0.1061064680797931</v>
       </c>
       <c r="C30">
-        <v>15241.6917226353</v>
+        <v>15032.00772652596</v>
       </c>
       <c r="D30">
-        <v>20395.00727586287</v>
+        <v>20394.20954951166</v>
       </c>
       <c r="E30">
-        <v>2273.688577414824</v>
+        <v>2482.574847172951</v>
       </c>
       <c r="F30">
-        <v>5848.81555322757</v>
+        <v>6057.701822985697</v>
       </c>
       <c r="G30">
         <v>695.5</v>
@@ -3991,28 +3991,28 @@
         <v>1184.4</v>
       </c>
       <c r="M30">
-        <v>358.161675962864</v>
+        <v>370.9531643901091</v>
       </c>
       <c r="N30">
-        <v>826.2383240371362</v>
+        <v>813.446835609891</v>
       </c>
       <c r="O30">
-        <v>103.279790504642</v>
+        <v>101.6808544512364</v>
       </c>
       <c r="P30">
-        <v>722.9585335324941</v>
+        <v>711.7659811586545</v>
       </c>
       <c r="Q30">
-        <v>1264.558533532494</v>
+        <v>1253.365981158654</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1265291222375219</v>
+        <v>0.1275601078896832</v>
       </c>
       <c r="T30">
-        <v>1.573560853445505</v>
+        <v>1.593656682778714</v>
       </c>
       <c r="U30">
         <v>0.0612366166625341</v>
@@ -4029,7 +4029,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.306886469122969</v>
+        <v>3.192855901222177</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4037,22 +4037,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1061064680797931</v>
+        <v>0.1061089970662496</v>
       </c>
       <c r="C31">
-        <v>15032.00772652597</v>
+        <v>14822.3237928184</v>
       </c>
       <c r="D31">
-        <v>20394.20954951166</v>
+        <v>20393.41188556223</v>
       </c>
       <c r="E31">
-        <v>2482.57484717295</v>
+        <v>2691.461116931078</v>
       </c>
       <c r="F31">
-        <v>6057.701822985696</v>
+        <v>6266.588092743824</v>
       </c>
       <c r="G31">
         <v>695.5</v>
@@ -4073,28 +4073,28 @@
         <v>1184.4</v>
       </c>
       <c r="M31">
-        <v>370.9531643901091</v>
+        <v>383.7446528173542</v>
       </c>
       <c r="N31">
-        <v>813.446835609891</v>
+        <v>800.6553471826459</v>
       </c>
       <c r="O31">
-        <v>101.6808544512364</v>
+        <v>100.0819183978307</v>
       </c>
       <c r="P31">
-        <v>711.7659811586545</v>
+        <v>700.5734287848152</v>
       </c>
       <c r="Q31">
-        <v>1253.365981158654</v>
+        <v>1242.173428784815</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1275601078896832</v>
+        <v>0.1286205502747634</v>
       </c>
       <c r="T31">
-        <v>1.593656682778714</v>
+        <v>1.6143266786643</v>
       </c>
       <c r="U31">
         <v>0.0612366166625341</v>
@@ -4111,7 +4111,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.192855901222177</v>
+        <v>3.086427371181438</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4119,22 +4119,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1061089970662496</v>
+        <v>0.1067896510527061</v>
       </c>
       <c r="C32">
-        <v>14822.3237928184</v>
+        <v>14400.9981229917</v>
       </c>
       <c r="D32">
-        <v>20393.41188556223</v>
+        <v>20180.97248549365</v>
       </c>
       <c r="E32">
-        <v>2691.461116931078</v>
+        <v>2900.347386689205</v>
       </c>
       <c r="F32">
-        <v>6266.588092743824</v>
+        <v>6475.474362501951</v>
       </c>
       <c r="G32">
         <v>695.5</v>
@@ -4155,45 +4155,45 @@
         <v>1184.4</v>
       </c>
       <c r="M32">
-        <v>383.7446528173542</v>
+        <v>412.7248271508542</v>
       </c>
       <c r="N32">
-        <v>800.6553471826459</v>
+        <v>771.6751728491458</v>
       </c>
       <c r="O32">
-        <v>100.0819183978307</v>
+        <v>96.45939660614323</v>
       </c>
       <c r="P32">
-        <v>700.5734287848152</v>
+        <v>675.2157762430027</v>
       </c>
       <c r="Q32">
-        <v>1242.173428784815</v>
+        <v>1216.815776243003</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1286205502747634</v>
+        <v>0.1297117301202807</v>
       </c>
       <c r="T32">
-        <v>1.6143266786643</v>
+        <v>1.635595804865411</v>
       </c>
       <c r="U32">
-        <v>0.0612366166625341</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V32">
         <v>0.125</v>
       </c>
       <c r="W32">
-        <v>0.05358203957971733</v>
+        <v>0.05576953957971733</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y32">
-        <v>3.086427371181438</v>
+        <v>2.86970863414304</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4201,22 +4201,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1067896510527061</v>
+        <v>0.1068140550391625</v>
       </c>
       <c r="C33">
-        <v>14400.9981229917</v>
+        <v>14184.57726584899</v>
       </c>
       <c r="D33">
-        <v>20180.97248549365</v>
+        <v>20173.43789810907</v>
       </c>
       <c r="E33">
-        <v>2900.347386689205</v>
+        <v>3109.233656447333</v>
       </c>
       <c r="F33">
-        <v>6475.474362501951</v>
+        <v>6684.360632260079</v>
       </c>
       <c r="G33">
         <v>695.5</v>
@@ -4237,28 +4237,28 @@
         <v>1184.4</v>
       </c>
       <c r="M33">
-        <v>412.7248271508542</v>
+        <v>426.0385312524947</v>
       </c>
       <c r="N33">
-        <v>771.6751728491458</v>
+        <v>758.3614687475053</v>
       </c>
       <c r="O33">
-        <v>96.45939660614323</v>
+        <v>94.79518359343817</v>
       </c>
       <c r="P33">
-        <v>675.2157762430027</v>
+        <v>663.5662851540671</v>
       </c>
       <c r="Q33">
-        <v>1216.815776243003</v>
+        <v>1205.166285154067</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1297117301202807</v>
+        <v>0.1308350034906662</v>
       </c>
       <c r="T33">
-        <v>1.635595804865411</v>
+        <v>1.657490493601848</v>
       </c>
       <c r="U33">
         <v>0.06373661666253409</v>
@@ -4275,7 +4275,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>2.86970863414304</v>
+        <v>2.78003023932607</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4283,22 +4283,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1068140550391625</v>
+        <v>0.106838459025619</v>
       </c>
       <c r="C34">
-        <v>14184.57726584899</v>
+        <v>13968.16203269888</v>
       </c>
       <c r="D34">
-        <v>20173.43789810907</v>
+        <v>20165.90893471709</v>
       </c>
       <c r="E34">
-        <v>3109.233656447333</v>
+        <v>3318.11992620546</v>
       </c>
       <c r="F34">
-        <v>6684.360632260079</v>
+        <v>6893.246902018206</v>
       </c>
       <c r="G34">
         <v>695.5</v>
@@ -4319,28 +4319,28 @@
         <v>1184.4</v>
       </c>
       <c r="M34">
-        <v>426.0385312524947</v>
+        <v>439.3522353541351</v>
       </c>
       <c r="N34">
-        <v>758.3614687475053</v>
+        <v>745.047764645865</v>
       </c>
       <c r="O34">
-        <v>94.79518359343817</v>
+        <v>93.13097058073312</v>
       </c>
       <c r="P34">
-        <v>663.5662851540671</v>
+        <v>651.9167940651319</v>
       </c>
       <c r="Q34">
-        <v>1205.166285154067</v>
+        <v>1193.516794065132</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1308350034906662</v>
+        <v>0.1319918074094213</v>
       </c>
       <c r="T34">
-        <v>1.657490493601848</v>
+        <v>1.680038755136388</v>
       </c>
       <c r="U34">
         <v>0.06373661666253409</v>
@@ -4357,7 +4357,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.78003023932607</v>
+        <v>2.695786898740431</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4365,22 +4365,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.106838459025619</v>
+        <v>0.1068628630120755</v>
       </c>
       <c r="C35">
-        <v>13968.16203269888</v>
+        <v>13751.75241724687</v>
       </c>
       <c r="D35">
-        <v>20165.90893471709</v>
+        <v>20158.38558902321</v>
       </c>
       <c r="E35">
-        <v>3318.11992620546</v>
+        <v>3527.006195963588</v>
       </c>
       <c r="F35">
-        <v>6893.246902018206</v>
+        <v>7102.133171776334</v>
       </c>
       <c r="G35">
         <v>695.5</v>
@@ -4401,28 +4401,28 @@
         <v>1184.4</v>
       </c>
       <c r="M35">
-        <v>439.3522353541351</v>
+        <v>452.6659394557756</v>
       </c>
       <c r="N35">
-        <v>745.047764645865</v>
+        <v>731.7340605442245</v>
       </c>
       <c r="O35">
-        <v>93.13097058073312</v>
+        <v>91.46675756802806</v>
       </c>
       <c r="P35">
-        <v>651.9167940651319</v>
+        <v>640.2673029761964</v>
       </c>
       <c r="Q35">
-        <v>1193.516794065132</v>
+        <v>1181.867302976196</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1319918074094213</v>
+        <v>0.1331836659923812</v>
       </c>
       <c r="T35">
-        <v>1.680038755136388</v>
+        <v>1.70327029732349</v>
       </c>
       <c r="U35">
         <v>0.06373661666253409</v>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.695786898740431</v>
+        <v>2.616499048777477</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1068628630120755</v>
+        <v>0.106887266998532</v>
       </c>
       <c r="C36">
-        <v>13751.75241724687</v>
+        <v>13535.34841320791</v>
       </c>
       <c r="D36">
-        <v>20158.38558902321</v>
+        <v>20150.86785474237</v>
       </c>
       <c r="E36">
-        <v>3527.006195963588</v>
+        <v>3735.892465721715</v>
       </c>
       <c r="F36">
-        <v>7102.133171776334</v>
+        <v>7311.019441534461</v>
       </c>
       <c r="G36">
         <v>695.5</v>
@@ -4483,28 +4483,28 @@
         <v>1184.4</v>
       </c>
       <c r="M36">
-        <v>452.6659394557756</v>
+        <v>465.9796435574161</v>
       </c>
       <c r="N36">
-        <v>731.7340605442245</v>
+        <v>718.4203564425841</v>
       </c>
       <c r="O36">
-        <v>91.46675756802806</v>
+        <v>89.80254455532301</v>
       </c>
       <c r="P36">
-        <v>640.2673029761964</v>
+        <v>628.617811887261</v>
       </c>
       <c r="Q36">
-        <v>1181.867302976196</v>
+        <v>1170.217811887261</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1331836659923812</v>
+        <v>0.1344121971471245</v>
       </c>
       <c r="T36">
-        <v>1.70327029732349</v>
+        <v>1.727216656193272</v>
       </c>
       <c r="U36">
         <v>0.06373661666253409</v>
@@ -4521,7 +4521,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.616499048777477</v>
+        <v>2.541741933098121</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4529,22 +4529,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.106887266998532</v>
+        <v>0.1080141709849885</v>
       </c>
       <c r="C37">
-        <v>13535.34841320791</v>
+        <v>12985.31965139799</v>
       </c>
       <c r="D37">
-        <v>20150.86785474237</v>
+        <v>19809.72536269058</v>
       </c>
       <c r="E37">
-        <v>3735.892465721715</v>
+        <v>3944.778735479843</v>
       </c>
       <c r="F37">
-        <v>7311.019441534461</v>
+        <v>7519.905711292589</v>
       </c>
       <c r="G37">
         <v>695.5</v>
@@ -4565,45 +4565,45 @@
         <v>1184.4</v>
       </c>
       <c r="M37">
-        <v>465.9796435574161</v>
+        <v>505.6130176485806</v>
       </c>
       <c r="N37">
-        <v>718.4203564425841</v>
+        <v>678.7869823514195</v>
       </c>
       <c r="O37">
-        <v>89.80254455532301</v>
+        <v>84.84837279392744</v>
       </c>
       <c r="P37">
-        <v>628.617811887261</v>
+        <v>593.9386095574921</v>
       </c>
       <c r="Q37">
-        <v>1170.217811887261</v>
+        <v>1135.538609557492</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1344121971471245</v>
+        <v>0.1356791199004535</v>
       </c>
       <c r="T37">
-        <v>1.727216656193272</v>
+        <v>1.751911338777735</v>
       </c>
       <c r="U37">
-        <v>0.06373661666253409</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V37">
         <v>0.125</v>
       </c>
       <c r="W37">
-        <v>0.05576953957971733</v>
+        <v>0.05883203957971733</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y37">
-        <v>2.541741933098121</v>
+        <v>2.342502978875439</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4611,22 +4611,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1080141709849885</v>
+        <v>0.1080691999714449</v>
       </c>
       <c r="C38">
-        <v>12985.31965139799</v>
+        <v>12760.07025716571</v>
       </c>
       <c r="D38">
-        <v>19809.72536269057</v>
+        <v>19793.36223821642</v>
       </c>
       <c r="E38">
-        <v>3944.778735479842</v>
+        <v>4153.66500523797</v>
       </c>
       <c r="F38">
-        <v>7519.905711292588</v>
+        <v>7728.791981050716</v>
       </c>
       <c r="G38">
         <v>695.5</v>
@@ -4647,28 +4647,28 @@
         <v>1184.4</v>
       </c>
       <c r="M38">
-        <v>505.6130176485806</v>
+        <v>519.6578236943744</v>
       </c>
       <c r="N38">
-        <v>678.7869823514195</v>
+        <v>664.7421763056257</v>
       </c>
       <c r="O38">
-        <v>84.84837279392744</v>
+        <v>83.09277203820321</v>
       </c>
       <c r="P38">
-        <v>593.9386095574921</v>
+        <v>581.6494042674225</v>
       </c>
       <c r="Q38">
-        <v>1135.538609557492</v>
+        <v>1123.249404267423</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1356791199004535</v>
+        <v>0.1369862624237294</v>
       </c>
       <c r="T38">
-        <v>1.751911338777735</v>
+        <v>1.777389979539482</v>
       </c>
       <c r="U38">
         <v>0.0672366166625341</v>
@@ -4685,7 +4685,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.342502978875439</v>
+        <v>2.279192087554482</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4693,22 +4693,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1080691999714449</v>
+        <v>0.1090552289579014</v>
       </c>
       <c r="C39">
-        <v>12760.07025716571</v>
+        <v>12262.49866178473</v>
       </c>
       <c r="D39">
-        <v>19793.36223821642</v>
+        <v>19504.67691259358</v>
       </c>
       <c r="E39">
-        <v>4153.66500523797</v>
+        <v>4362.551274996098</v>
       </c>
       <c r="F39">
-        <v>7728.791981050716</v>
+        <v>7937.678250808844</v>
       </c>
       <c r="G39">
         <v>695.5</v>
@@ -4729,45 +4729,45 @@
         <v>1184.4</v>
       </c>
       <c r="M39">
-        <v>519.6578236943744</v>
+        <v>555.9281288424331</v>
       </c>
       <c r="N39">
-        <v>664.7421763056257</v>
+        <v>628.471871157567</v>
       </c>
       <c r="O39">
-        <v>83.09277203820321</v>
+        <v>78.55898389469587</v>
       </c>
       <c r="P39">
-        <v>581.6494042674225</v>
+        <v>549.9128872628711</v>
       </c>
       <c r="Q39">
-        <v>1123.249404267423</v>
+        <v>1091.512887262871</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1369862624237294</v>
+        <v>0.138335570834853</v>
       </c>
       <c r="T39">
-        <v>1.777389979539482</v>
+        <v>1.803690511938705</v>
       </c>
       <c r="U39">
-        <v>0.0672366166625341</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V39">
         <v>0.125</v>
       </c>
       <c r="W39">
-        <v>0.05883203957971733</v>
+        <v>0.06128203957971733</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y39">
-        <v>2.279192087554482</v>
+        <v>2.130491224587225</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4775,22 +4775,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1090552289579014</v>
+        <v>0.1091347579443579</v>
       </c>
       <c r="C40">
-        <v>12262.49866178473</v>
+        <v>12030.69479520049</v>
       </c>
       <c r="D40">
-        <v>19504.67691259358</v>
+        <v>19481.75931576746</v>
       </c>
       <c r="E40">
-        <v>4362.551274996098</v>
+        <v>4571.437544754224</v>
       </c>
       <c r="F40">
-        <v>7937.678250808844</v>
+        <v>8146.564520566971</v>
       </c>
       <c r="G40">
         <v>695.5</v>
@@ -4811,28 +4811,28 @@
         <v>1184.4</v>
       </c>
       <c r="M40">
-        <v>555.9281288424331</v>
+        <v>570.5578164435498</v>
       </c>
       <c r="N40">
-        <v>628.471871157567</v>
+        <v>613.8421835564503</v>
       </c>
       <c r="O40">
-        <v>78.55898389469587</v>
+        <v>76.73027294455629</v>
       </c>
       <c r="P40">
-        <v>549.9128872628711</v>
+        <v>537.111910611894</v>
       </c>
       <c r="Q40">
-        <v>1091.512887262871</v>
+        <v>1078.711910611894</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.138335570834853</v>
+        <v>0.1397291188660133</v>
       </c>
       <c r="T40">
-        <v>1.803690511938705</v>
+        <v>1.830853356875607</v>
       </c>
       <c r="U40">
         <v>0.07003661666253409</v>
@@ -4849,7 +4849,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.130491224587225</v>
+        <v>2.075863244469604</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4857,22 +4857,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1091347579443579</v>
+        <v>0.1092142869308144</v>
       </c>
       <c r="C41">
-        <v>12030.69479520049</v>
+        <v>11798.94472082746</v>
       </c>
       <c r="D41">
-        <v>19481.75931576746</v>
+        <v>19458.89551115256</v>
       </c>
       <c r="E41">
-        <v>4571.437544754224</v>
+        <v>4780.323814512352</v>
       </c>
       <c r="F41">
-        <v>8146.564520566971</v>
+        <v>8355.450790325098</v>
       </c>
       <c r="G41">
         <v>695.5</v>
@@ -4893,28 +4893,28 @@
         <v>1184.4</v>
       </c>
       <c r="M41">
-        <v>570.5578164435498</v>
+        <v>585.1875040446664</v>
       </c>
       <c r="N41">
-        <v>613.8421835564503</v>
+        <v>599.2124959553337</v>
       </c>
       <c r="O41">
-        <v>76.73027294455629</v>
+        <v>74.90156199441671</v>
       </c>
       <c r="P41">
-        <v>537.111910611894</v>
+        <v>524.3109339609169</v>
       </c>
       <c r="Q41">
-        <v>1078.711910611894</v>
+        <v>1065.910933960917</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1397291188660133</v>
+        <v>0.1411691184982124</v>
       </c>
       <c r="T41">
-        <v>1.830853356875607</v>
+        <v>1.858921629977073</v>
       </c>
       <c r="U41">
         <v>0.07003661666253409</v>
@@ -4931,7 +4931,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.075863244469604</v>
+        <v>2.023966663357864</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4939,22 +4939,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1092142869308144</v>
+        <v>0.1120920659172709</v>
       </c>
       <c r="C42">
-        <v>11798.94472082746</v>
+        <v>10797.35973266416</v>
       </c>
       <c r="D42">
-        <v>19458.89551115256</v>
+        <v>18666.19679274738</v>
       </c>
       <c r="E42">
-        <v>4780.323814512352</v>
+        <v>4989.21008427048</v>
       </c>
       <c r="F42">
-        <v>8355.450790325098</v>
+        <v>8564.337060083226</v>
       </c>
       <c r="G42">
         <v>695.5</v>
@@ -4975,45 +4975,45 @@
         <v>1184.4</v>
       </c>
       <c r="M42">
-        <v>585.1875040446664</v>
+        <v>666.6190207144324</v>
       </c>
       <c r="N42">
-        <v>599.2124959553337</v>
+        <v>517.7809792855677</v>
       </c>
       <c r="O42">
-        <v>74.90156199441671</v>
+        <v>64.72262241069596</v>
       </c>
       <c r="P42">
-        <v>524.3109339609169</v>
+        <v>453.0583568748717</v>
       </c>
       <c r="Q42">
-        <v>1065.910933960917</v>
+        <v>994.6583568748717</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1411691184982124</v>
+        <v>0.1426579316772657</v>
       </c>
       <c r="T42">
-        <v>1.858921629977073</v>
+        <v>1.887941369963334</v>
       </c>
       <c r="U42">
-        <v>0.07003661666253409</v>
+        <v>0.07783661666253411</v>
       </c>
       <c r="V42">
         <v>0.125</v>
       </c>
       <c r="W42">
-        <v>0.06128203957971733</v>
+        <v>0.06810703957971734</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y42">
-        <v>2.023966663357864</v>
+        <v>1.776726980773289</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -5021,22 +5021,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1120920659172709</v>
+        <v>0.1136730949037273</v>
       </c>
       <c r="C43">
-        <v>10797.35973266416</v>
+        <v>10179.85725278575</v>
       </c>
       <c r="D43">
-        <v>18666.19679274738</v>
+        <v>18257.5805826271</v>
       </c>
       <c r="E43">
-        <v>4989.21008427048</v>
+        <v>5198.096354028608</v>
       </c>
       <c r="F43">
-        <v>8564.337060083226</v>
+        <v>8773.223329841354</v>
       </c>
       <c r="G43">
         <v>695.5</v>
@@ -5057,45 +5057,45 @@
         <v>1184.4</v>
       </c>
       <c r="M43">
-        <v>666.6190207144324</v>
+        <v>717.0935922060437</v>
       </c>
       <c r="N43">
-        <v>517.7809792855677</v>
+        <v>467.3064077939564</v>
       </c>
       <c r="O43">
-        <v>64.72262241069596</v>
+        <v>58.41330097424455</v>
       </c>
       <c r="P43">
-        <v>453.0583568748717</v>
+        <v>408.8931068197119</v>
       </c>
       <c r="Q43">
-        <v>994.6583568748717</v>
+        <v>950.4931068197119</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1426579316772657</v>
+        <v>0.1441980832418036</v>
       </c>
       <c r="T43">
-        <v>1.887941369963334</v>
+        <v>1.917961790638777</v>
       </c>
       <c r="U43">
-        <v>0.07783661666253411</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V43">
         <v>0.125</v>
       </c>
       <c r="W43">
-        <v>0.06810703957971734</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y43">
-        <v>1.776726980773289</v>
+        <v>1.651667248003639</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5103,22 +5103,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1136730949037273</v>
+        <v>0.1138549988901838</v>
       </c>
       <c r="C44">
-        <v>10179.85725278575</v>
+        <v>9925.102654381604</v>
       </c>
       <c r="D44">
-        <v>18257.58058262711</v>
+        <v>18211.71225398108</v>
       </c>
       <c r="E44">
-        <v>5198.096354028607</v>
+        <v>5406.982623786735</v>
       </c>
       <c r="F44">
-        <v>8773.223329841352</v>
+        <v>8982.10959959948</v>
       </c>
       <c r="G44">
         <v>695.5</v>
@@ -5139,28 +5139,28 @@
         <v>1184.4</v>
       </c>
       <c r="M44">
-        <v>717.0935922060435</v>
+        <v>734.1672491633303</v>
       </c>
       <c r="N44">
-        <v>467.3064077939566</v>
+        <v>450.2327508366698</v>
       </c>
       <c r="O44">
-        <v>58.41330097424458</v>
+        <v>56.27909385458372</v>
       </c>
       <c r="P44">
-        <v>408.893106819712</v>
+        <v>393.953656982086</v>
       </c>
       <c r="Q44">
-        <v>950.493106819712</v>
+        <v>935.5536569820861</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1441980832418035</v>
+        <v>0.1457922752121147</v>
       </c>
       <c r="T44">
-        <v>1.917961790638776</v>
+        <v>1.949035559408094</v>
       </c>
       <c r="U44">
         <v>0.0817366166625341</v>
@@ -5177,7 +5177,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>1.65166724800364</v>
+        <v>1.613256381770997</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5185,22 +5185,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1138549988901838</v>
+        <v>0.1140369028766403</v>
       </c>
       <c r="C45">
-        <v>9925.102654381604</v>
+        <v>9670.577947467631</v>
       </c>
       <c r="D45">
-        <v>18211.71225398108</v>
+        <v>18166.07381682524</v>
       </c>
       <c r="E45">
-        <v>5406.982623786735</v>
+        <v>5615.868893544863</v>
       </c>
       <c r="F45">
-        <v>8982.10959959948</v>
+        <v>9190.995869357608</v>
       </c>
       <c r="G45">
         <v>695.5</v>
@@ -5221,28 +5221,28 @@
         <v>1184.4</v>
       </c>
       <c r="M45">
-        <v>734.1672491633303</v>
+        <v>751.2409061206171</v>
       </c>
       <c r="N45">
-        <v>450.2327508366698</v>
+        <v>433.159093879383</v>
       </c>
       <c r="O45">
-        <v>56.27909385458372</v>
+        <v>54.14488673492288</v>
       </c>
       <c r="P45">
-        <v>393.953656982086</v>
+        <v>379.0142071444602</v>
       </c>
       <c r="Q45">
-        <v>935.5536569820861</v>
+        <v>920.6142071444601</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1457922752121147</v>
+        <v>0.1474434026099369</v>
       </c>
       <c r="T45">
-        <v>1.949035559408094</v>
+        <v>1.981219105633459</v>
       </c>
       <c r="U45">
         <v>0.0817366166625341</v>
@@ -5259,7 +5259,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>1.613256381770997</v>
+        <v>1.576591464003474</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5267,22 +5267,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1140369028766403</v>
+        <v>0.1142188068630968</v>
       </c>
       <c r="C46">
-        <v>9670.577947467631</v>
+        <v>9416.281408044244</v>
       </c>
       <c r="D46">
-        <v>18166.07381682524</v>
+        <v>18120.66354715998</v>
       </c>
       <c r="E46">
-        <v>5615.868893544863</v>
+        <v>5824.755163302991</v>
       </c>
       <c r="F46">
-        <v>9190.995869357608</v>
+        <v>9399.882139115736</v>
       </c>
       <c r="G46">
         <v>695.5</v>
@@ -5303,28 +5303,28 @@
         <v>1184.4</v>
       </c>
       <c r="M46">
-        <v>751.2409061206171</v>
+        <v>768.3145630779039</v>
       </c>
       <c r="N46">
-        <v>433.159093879383</v>
+        <v>416.0854369220962</v>
       </c>
       <c r="O46">
-        <v>54.14488673492288</v>
+        <v>52.01067961526202</v>
       </c>
       <c r="P46">
-        <v>379.0142071444602</v>
+        <v>364.0747573068342</v>
       </c>
       <c r="Q46">
-        <v>920.6142071444601</v>
+        <v>905.6747573068342</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1474434026099369</v>
+        <v>0.1491545710040436</v>
       </c>
       <c r="T46">
-        <v>1.981219105633459</v>
+        <v>2.014572962630655</v>
       </c>
       <c r="U46">
         <v>0.0817366166625341</v>
@@ -5341,7 +5341,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>1.576591464003474</v>
+        <v>1.54155609813673</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5349,22 +5349,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1142188068630968</v>
+        <v>0.1144007108495533</v>
       </c>
       <c r="C47">
-        <v>9416.281408044244</v>
+        <v>9162.211329307022</v>
       </c>
       <c r="D47">
-        <v>18120.66354715998</v>
+        <v>18075.47973818089</v>
       </c>
       <c r="E47">
-        <v>5824.755163302991</v>
+        <v>6033.641433061119</v>
       </c>
       <c r="F47">
-        <v>9399.882139115736</v>
+        <v>9608.768408873864</v>
       </c>
       <c r="G47">
         <v>695.5</v>
@@ -5385,28 +5385,28 @@
         <v>1184.4</v>
       </c>
       <c r="M47">
-        <v>768.3145630779039</v>
+        <v>785.3882200351907</v>
       </c>
       <c r="N47">
-        <v>416.0854369220962</v>
+        <v>399.0117799648094</v>
       </c>
       <c r="O47">
-        <v>52.01067961526202</v>
+        <v>49.87647249560118</v>
       </c>
       <c r="P47">
-        <v>364.0747573068342</v>
+        <v>349.1353074692082</v>
       </c>
       <c r="Q47">
-        <v>905.6747573068342</v>
+        <v>890.7353074692082</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1491545710040436</v>
+        <v>0.1509291160053394</v>
       </c>
       <c r="T47">
-        <v>2.014572962630655</v>
+        <v>2.049162147664785</v>
       </c>
       <c r="U47">
         <v>0.0817366166625341</v>
@@ -5423,7 +5423,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>1.54155609813673</v>
+        <v>1.508044009046801</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5431,22 +5431,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1144007108495533</v>
+        <v>0.1204223648360098</v>
       </c>
       <c r="C48">
-        <v>9162.211329307022</v>
+        <v>7575.078742588636</v>
       </c>
       <c r="D48">
-        <v>18075.47973818089</v>
+        <v>16697.23342122063</v>
       </c>
       <c r="E48">
-        <v>6033.641433061119</v>
+        <v>6242.527702819245</v>
       </c>
       <c r="F48">
-        <v>9608.768408873864</v>
+        <v>9817.65467863199</v>
       </c>
       <c r="G48">
         <v>695.5</v>
@@ -5467,45 +5467,45 @@
         <v>1184.4</v>
       </c>
       <c r="M48">
-        <v>785.3882200351907</v>
+        <v>941.8725734290517</v>
       </c>
       <c r="N48">
-        <v>399.0117799648094</v>
+        <v>242.5274265709484</v>
       </c>
       <c r="O48">
-        <v>49.87647249560118</v>
+        <v>30.31592832136855</v>
       </c>
       <c r="P48">
-        <v>349.1353074692082</v>
+        <v>212.2114982495798</v>
       </c>
       <c r="Q48">
-        <v>890.7353074692082</v>
+        <v>753.8114982495798</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1509291160053394</v>
+        <v>0.1527706249689483</v>
       </c>
       <c r="T48">
-        <v>2.049162147664785</v>
+        <v>2.085056584964353</v>
       </c>
       <c r="U48">
-        <v>0.0817366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V48">
         <v>0.125</v>
       </c>
       <c r="W48">
-        <v>0.07151953957971734</v>
+        <v>0.08394453957971734</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y48">
-        <v>1.508044009046801</v>
+        <v>1.257494945083691</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1204223648360098</v>
+        <v>0.1333111457448236</v>
       </c>
       <c r="C49">
-        <v>7575.078742588636</v>
+        <v>5023.467171492046</v>
       </c>
       <c r="D49">
-        <v>16697.23342122063</v>
+        <v>14354.50811988216</v>
       </c>
       <c r="E49">
-        <v>6242.527702819245</v>
+        <v>6451.413972577373</v>
       </c>
       <c r="F49">
-        <v>9817.65467863199</v>
+        <v>10026.54094839012</v>
       </c>
       <c r="G49">
         <v>695.5</v>
@@ -5549,45 +5549,45 @@
         <v>1184.4</v>
       </c>
       <c r="M49">
-        <v>941.8725734290517</v>
+        <v>1248.671486540861</v>
       </c>
       <c r="N49">
-        <v>242.5274265709484</v>
+        <v>-64.27148654086113</v>
       </c>
       <c r="O49">
-        <v>30.31592832136855</v>
+        <v>-8.033935817607642</v>
       </c>
       <c r="P49">
-        <v>212.2114982495798</v>
+        <v>-56.23755072325349</v>
       </c>
       <c r="Q49">
-        <v>753.8114982495798</v>
+        <v>485.3624492767465</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1527706249689483</v>
+        <v>0.1550406896418738</v>
       </c>
       <c r="T49">
-        <v>2.085056584964353</v>
+        <v>2.129304370708825</v>
       </c>
       <c r="U49">
-        <v>0.0959366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V49">
-        <v>0.125</v>
+        <v>0.1185660132355039</v>
       </c>
       <c r="W49">
-        <v>0.08394453957971734</v>
+        <v>0.1097708065230192</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y49">
-        <v>1.257494945083691</v>
+        <v>0.9485281058840307</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5595,22 +5595,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1333111457448236</v>
+        <v>0.1340985119114489</v>
       </c>
       <c r="C50">
-        <v>5023.467171492048</v>
+        <v>4692.591104689331</v>
       </c>
       <c r="D50">
-        <v>14354.50811988216</v>
+        <v>14232.51832283758</v>
       </c>
       <c r="E50">
-        <v>6451.413972577371</v>
+        <v>6660.300242335499</v>
       </c>
       <c r="F50">
-        <v>10026.54094839012</v>
+        <v>10235.42721814824</v>
       </c>
       <c r="G50">
         <v>695.5</v>
@@ -5631,37 +5631,37 @@
         <v>1184.4</v>
       </c>
       <c r="M50">
-        <v>1248.671486540861</v>
+        <v>1274.685475843796</v>
       </c>
       <c r="N50">
-        <v>-64.27148654086091</v>
+        <v>-90.28547584379567</v>
       </c>
       <c r="O50">
-        <v>-8.033935817607613</v>
+        <v>-11.28568448047446</v>
       </c>
       <c r="P50">
-        <v>-56.23755072325329</v>
+        <v>-78.99979136332121</v>
       </c>
       <c r="Q50">
-        <v>485.3624492767467</v>
+        <v>462.6002086366788</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1550406896418738</v>
+        <v>0.1571826639485772</v>
       </c>
       <c r="T50">
-        <v>2.129304370708825</v>
+        <v>2.171055436801155</v>
       </c>
       <c r="U50">
         <v>0.1245366166625341</v>
       </c>
       <c r="V50">
-        <v>0.1185660132355039</v>
+        <v>0.1161462986796772</v>
       </c>
       <c r="W50">
-        <v>0.1097708065230192</v>
+        <v>0.1100721495870909</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5669,7 +5669,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.9485281058840309</v>
+        <v>0.9291703894374179</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5677,22 +5677,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1340985119114489</v>
+        <v>0.1348858780780743</v>
       </c>
       <c r="C51">
-        <v>4692.591104689331</v>
+        <v>4363.77099239555</v>
       </c>
       <c r="D51">
-        <v>14232.51832283758</v>
+        <v>14112.58448030192</v>
       </c>
       <c r="E51">
-        <v>6660.300242335499</v>
+        <v>6869.186512093627</v>
       </c>
       <c r="F51">
-        <v>10235.42721814824</v>
+        <v>10444.31348790637</v>
       </c>
       <c r="G51">
         <v>695.5</v>
@@ -5713,37 +5713,37 @@
         <v>1184.4</v>
       </c>
       <c r="M51">
-        <v>1274.685475843796</v>
+        <v>1300.699465146731</v>
       </c>
       <c r="N51">
-        <v>-90.28547584379567</v>
+        <v>-116.2994651467304</v>
       </c>
       <c r="O51">
-        <v>-11.28568448047446</v>
+        <v>-14.5374331433413</v>
       </c>
       <c r="P51">
-        <v>-78.99979136332121</v>
+        <v>-101.7620320033891</v>
       </c>
       <c r="Q51">
-        <v>462.6002086366788</v>
+        <v>439.8379679966109</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1571826639485772</v>
+        <v>0.1594103172275487</v>
       </c>
       <c r="T51">
-        <v>2.171055436801155</v>
+        <v>2.214476545537178</v>
       </c>
       <c r="U51">
         <v>0.1245366166625341</v>
       </c>
       <c r="V51">
-        <v>0.1161462986796772</v>
+        <v>0.1138233727060837</v>
       </c>
       <c r="W51">
-        <v>0.1100721495870909</v>
+        <v>0.1103614389285998</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5751,7 +5751,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.9291703894374179</v>
+        <v>0.9105869816486695</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5759,22 +5759,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1348858780780743</v>
+        <v>0.1356732442446996</v>
       </c>
       <c r="C52">
-        <v>4363.77099239555</v>
+        <v>4036.955293900839</v>
       </c>
       <c r="D52">
-        <v>14112.58448030192</v>
+        <v>13994.65505156534</v>
       </c>
       <c r="E52">
-        <v>6869.186512093627</v>
+        <v>7078.072781851755</v>
       </c>
       <c r="F52">
-        <v>10444.31348790637</v>
+        <v>10653.1997576645</v>
       </c>
       <c r="G52">
         <v>695.5</v>
@@ -5795,37 +5795,37 @@
         <v>1184.4</v>
       </c>
       <c r="M52">
-        <v>1300.699465146731</v>
+        <v>1326.713454449665</v>
       </c>
       <c r="N52">
-        <v>-116.2994651467304</v>
+        <v>-142.313454449665</v>
       </c>
       <c r="O52">
-        <v>-14.5374331433413</v>
+        <v>-17.78918180620812</v>
       </c>
       <c r="P52">
-        <v>-101.7620320033891</v>
+        <v>-124.5242726434568</v>
       </c>
       <c r="Q52">
-        <v>439.8379679966109</v>
+        <v>417.0757273565432</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1594103172275487</v>
+        <v>0.1617288951301517</v>
       </c>
       <c r="T52">
-        <v>2.214476545537178</v>
+        <v>2.259669944425692</v>
       </c>
       <c r="U52">
         <v>0.1245366166625341</v>
       </c>
       <c r="V52">
-        <v>0.1138233727060837</v>
+        <v>0.1115915418687095</v>
       </c>
       <c r="W52">
-        <v>0.1103614389285998</v>
+        <v>0.1106393835900495</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.9105869816486695</v>
+        <v>0.892732334949676</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5841,22 +5841,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1356732442446996</v>
+        <v>0.1364606104113249</v>
       </c>
       <c r="C53">
-        <v>4036.955293900839</v>
+        <v>3712.094176983583</v>
       </c>
       <c r="D53">
-        <v>13994.65505156534</v>
+        <v>13878.68020440621</v>
       </c>
       <c r="E53">
-        <v>7078.072781851755</v>
+        <v>7286.959051609883</v>
       </c>
       <c r="F53">
-        <v>10653.1997576645</v>
+        <v>10862.08602742263</v>
       </c>
       <c r="G53">
         <v>695.5</v>
@@ -5877,37 +5877,37 @@
         <v>1184.4</v>
       </c>
       <c r="M53">
-        <v>1326.713454449665</v>
+        <v>1352.7274437526</v>
       </c>
       <c r="N53">
-        <v>-142.313454449665</v>
+        <v>-168.3274437525997</v>
       </c>
       <c r="O53">
-        <v>-17.78918180620812</v>
+        <v>-21.04093046907497</v>
       </c>
       <c r="P53">
-        <v>-124.5242726434568</v>
+        <v>-147.2865132835248</v>
       </c>
       <c r="Q53">
-        <v>417.0757273565432</v>
+        <v>394.3134867164753</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1617288951301517</v>
+        <v>0.1641440804453632</v>
       </c>
       <c r="T53">
-        <v>2.259669944425692</v>
+        <v>2.306746401601227</v>
       </c>
       <c r="U53">
         <v>0.1245366166625341</v>
       </c>
       <c r="V53">
-        <v>0.1115915418687095</v>
+        <v>0.1094455506789266</v>
       </c>
       <c r="W53">
-        <v>0.1106393835900495</v>
+        <v>0.1109066380722127</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5915,7 +5915,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.892732334949676</v>
+        <v>0.8755644054314129</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5923,22 +5923,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1364606104113249</v>
+        <v>0.1372479765779503</v>
       </c>
       <c r="C54">
-        <v>3712.094176983583</v>
+        <v>3389.139447700341</v>
       </c>
       <c r="D54">
-        <v>13878.68020440621</v>
+        <v>13764.6117448811</v>
       </c>
       <c r="E54">
-        <v>7286.959051609883</v>
+        <v>7495.84532136801</v>
       </c>
       <c r="F54">
-        <v>10862.08602742263</v>
+        <v>11070.97229718076</v>
       </c>
       <c r="G54">
         <v>695.5</v>
@@ -5959,37 +5959,37 @@
         <v>1184.4</v>
       </c>
       <c r="M54">
-        <v>1352.7274437526</v>
+        <v>1378.741433055534</v>
       </c>
       <c r="N54">
-        <v>-168.3274437525997</v>
+        <v>-194.3414330555343</v>
       </c>
       <c r="O54">
-        <v>-21.04093046907497</v>
+        <v>-24.29267913194178</v>
       </c>
       <c r="P54">
-        <v>-147.2865132835248</v>
+        <v>-170.0487539235925</v>
       </c>
       <c r="Q54">
-        <v>394.3134867164753</v>
+        <v>371.5512460764076</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1641440804453632</v>
+        <v>0.1666620396037752</v>
       </c>
       <c r="T54">
-        <v>2.306746401601227</v>
+        <v>2.355826112273594</v>
       </c>
       <c r="U54">
         <v>0.1245366166625341</v>
       </c>
       <c r="V54">
-        <v>0.1094455506789266</v>
+        <v>0.1073805402887582</v>
       </c>
       <c r="W54">
-        <v>0.1109066380722127</v>
+        <v>0.1111638074795772</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.8755644054314129</v>
+        <v>0.8590443223100656</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -6005,22 +6005,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1372479765779503</v>
+        <v>0.1380353427445756</v>
       </c>
       <c r="C55">
-        <v>3389.139447700341</v>
+        <v>3068.044483609909</v>
       </c>
       <c r="D55">
-        <v>13764.6117448811</v>
+        <v>13652.40305054879</v>
       </c>
       <c r="E55">
-        <v>7495.84532136801</v>
+        <v>7704.731591126138</v>
       </c>
       <c r="F55">
-        <v>11070.97229718076</v>
+        <v>11279.85856693888</v>
       </c>
       <c r="G55">
         <v>695.5</v>
@@ -6041,37 +6041,37 @@
         <v>1184.4</v>
       </c>
       <c r="M55">
-        <v>1378.741433055534</v>
+        <v>1404.755422358469</v>
       </c>
       <c r="N55">
-        <v>-194.3414330555343</v>
+        <v>-220.3554223584688</v>
       </c>
       <c r="O55">
-        <v>-24.29267913194178</v>
+        <v>-27.5444277948086</v>
       </c>
       <c r="P55">
-        <v>-170.0487539235925</v>
+        <v>-192.8109945636602</v>
       </c>
       <c r="Q55">
-        <v>371.5512460764076</v>
+        <v>348.7890054363398</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1666620396037752</v>
+        <v>0.1692894752473356</v>
       </c>
       <c r="T55">
-        <v>2.355826112273594</v>
+        <v>2.407039723409976</v>
       </c>
       <c r="U55">
         <v>0.1245366166625341</v>
       </c>
       <c r="V55">
-        <v>0.1073805402887582</v>
+        <v>0.1053920117648923</v>
       </c>
       <c r="W55">
-        <v>0.1111638074795772</v>
+        <v>0.1114114520940764</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -6079,7 +6079,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.8590443223100656</v>
+        <v>0.8431360941191385</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6087,22 +6087,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1380353427445756</v>
+        <v>0.138822708911201</v>
       </c>
       <c r="C56">
-        <v>3068.044483609909</v>
+        <v>2748.764170237042</v>
       </c>
       <c r="D56">
-        <v>13652.40305054879</v>
+        <v>13542.00900693405</v>
       </c>
       <c r="E56">
-        <v>7704.731591126138</v>
+        <v>7913.617860884266</v>
       </c>
       <c r="F56">
-        <v>11279.85856693888</v>
+        <v>11488.74483669701</v>
       </c>
       <c r="G56">
         <v>695.5</v>
@@ -6123,37 +6123,37 @@
         <v>1184.4</v>
       </c>
       <c r="M56">
-        <v>1404.755422358469</v>
+        <v>1430.769411661404</v>
       </c>
       <c r="N56">
-        <v>-220.3554223584688</v>
+        <v>-246.3694116614035</v>
       </c>
       <c r="O56">
-        <v>-27.5444277948086</v>
+        <v>-30.79617645767544</v>
       </c>
       <c r="P56">
-        <v>-192.8109945636602</v>
+        <v>-215.5732352037281</v>
       </c>
       <c r="Q56">
-        <v>348.7890054363398</v>
+        <v>326.0267647962719</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1692894752473356</v>
+        <v>0.1720336858083875</v>
       </c>
       <c r="T56">
-        <v>2.407039723409976</v>
+        <v>2.460529495041309</v>
       </c>
       <c r="U56">
         <v>0.1245366166625341</v>
       </c>
       <c r="V56">
-        <v>0.1053920117648923</v>
+        <v>0.103475793369167</v>
       </c>
       <c r="W56">
-        <v>0.1114114520940764</v>
+        <v>0.1116500914498666</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.8431360941191385</v>
+        <v>0.8278063469533359</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6169,22 +6169,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.138822708911201</v>
+        <v>0.1396100750778263</v>
       </c>
       <c r="C57">
-        <v>2748.764170237042</v>
+        <v>2431.25484059404</v>
       </c>
       <c r="D57">
-        <v>13542.00900693405</v>
+        <v>13433.38594704918</v>
       </c>
       <c r="E57">
-        <v>7913.617860884266</v>
+        <v>8122.504130642394</v>
       </c>
       <c r="F57">
-        <v>11488.74483669701</v>
+        <v>11697.63110645514</v>
       </c>
       <c r="G57">
         <v>695.5</v>
@@ -6205,37 +6205,37 @@
         <v>1184.4</v>
       </c>
       <c r="M57">
-        <v>1430.769411661404</v>
+        <v>1456.783400964338</v>
       </c>
       <c r="N57">
-        <v>-246.3694116614035</v>
+        <v>-272.3834009643381</v>
       </c>
       <c r="O57">
-        <v>-30.79617645767544</v>
+        <v>-34.04792512054226</v>
       </c>
       <c r="P57">
-        <v>-215.5732352037281</v>
+        <v>-238.3354758437958</v>
       </c>
       <c r="Q57">
-        <v>326.0267647962719</v>
+        <v>303.2645241562042</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1720336858083875</v>
+        <v>0.1749026332131235</v>
       </c>
       <c r="T57">
-        <v>2.460529495041309</v>
+        <v>2.516450619928611</v>
       </c>
       <c r="U57">
         <v>0.1245366166625341</v>
       </c>
       <c r="V57">
-        <v>0.103475793369167</v>
+        <v>0.1016280113447176</v>
       </c>
       <c r="W57">
-        <v>0.1116500914498666</v>
+        <v>0.1118802079715213</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6243,7 +6243,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.8278063469533359</v>
+        <v>0.8130240907577406</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6251,22 +6251,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1396100750778263</v>
+        <v>0.1571043524868894</v>
       </c>
       <c r="C58">
-        <v>2431.25484059404</v>
+        <v>190.3997927813034</v>
       </c>
       <c r="D58">
-        <v>13433.38594704918</v>
+        <v>11401.41716899457</v>
       </c>
       <c r="E58">
-        <v>8122.504130642394</v>
+        <v>8331.39040040052</v>
       </c>
       <c r="F58">
-        <v>11697.63110645514</v>
+        <v>11906.51737621327</v>
       </c>
       <c r="G58">
         <v>695.5</v>
@@ -6287,45 +6287,45 @@
         <v>1184.4</v>
       </c>
       <c r="M58">
-        <v>1456.783400964338</v>
+        <v>1818.561180276487</v>
       </c>
       <c r="N58">
-        <v>-272.3834009643381</v>
+        <v>-634.1611802764867</v>
       </c>
       <c r="O58">
-        <v>-34.04792512054226</v>
+        <v>-79.27014753456083</v>
       </c>
       <c r="P58">
-        <v>-238.3354758437958</v>
+        <v>-554.8910327419259</v>
       </c>
       <c r="Q58">
-        <v>303.2645241562042</v>
+        <v>-13.29103274192585</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1749026332131235</v>
+        <v>0.1793769066423537</v>
       </c>
       <c r="T58">
-        <v>2.516450619928611</v>
+        <v>2.603662537025062</v>
       </c>
       <c r="U58">
-        <v>0.1245366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V58">
-        <v>0.1016280113447176</v>
+        <v>0.08141051376533347</v>
       </c>
       <c r="W58">
-        <v>0.1118802079715213</v>
+        <v>0.1403022502292584</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y58">
-        <v>0.8130240907577406</v>
+        <v>0.6512841101226678</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6333,22 +6333,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1571043524868894</v>
+        <v>0.1902237930531016</v>
       </c>
       <c r="C59">
-        <v>190.3997927813034</v>
+        <v>-2556.614113664467</v>
       </c>
       <c r="D59">
-        <v>11401.41716899457</v>
+        <v>8863.289532306926</v>
       </c>
       <c r="E59">
-        <v>8331.39040040052</v>
+        <v>8540.276670158648</v>
       </c>
       <c r="F59">
-        <v>11906.51737621327</v>
+        <v>12115.40364597139</v>
       </c>
       <c r="G59">
         <v>695.5</v>
@@ -6369,45 +6369,45 @@
         <v>1184.4</v>
       </c>
       <c r="M59">
-        <v>1818.561180276487</v>
+        <v>2504.697559269056</v>
       </c>
       <c r="N59">
-        <v>-634.1611802764867</v>
+        <v>-1320.297559269056</v>
       </c>
       <c r="O59">
-        <v>-79.27014753456083</v>
+        <v>-165.037194908632</v>
       </c>
       <c r="P59">
-        <v>-554.8910327419259</v>
+        <v>-1155.260364360424</v>
       </c>
       <c r="Q59">
-        <v>-13.29103274192585</v>
+        <v>-613.6603643604238</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1793769066423537</v>
+        <v>0.1842955815614262</v>
       </c>
       <c r="T59">
-        <v>2.603662537025062</v>
+        <v>2.699536666322597</v>
       </c>
       <c r="U59">
-        <v>0.1527366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V59">
-        <v>0.08141051376533347</v>
+        <v>0.05910893291372286</v>
       </c>
       <c r="W59">
-        <v>0.1403022502292584</v>
+        <v>0.1945166358574183</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y59">
-        <v>0.6512841101226678</v>
+        <v>0.4728714633097829</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6415,22 +6415,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1902237930531016</v>
+        <v>0.1918331592197269</v>
       </c>
       <c r="C60">
-        <v>-2556.614113664466</v>
+        <v>-2860.352862211954</v>
       </c>
       <c r="D60">
-        <v>8863.289532306926</v>
+        <v>8768.437053517566</v>
       </c>
       <c r="E60">
-        <v>8540.276670158646</v>
+        <v>8749.162939916774</v>
       </c>
       <c r="F60">
-        <v>12115.40364597139</v>
+        <v>12324.28991572952</v>
       </c>
       <c r="G60">
         <v>695.5</v>
@@ -6451,37 +6451,37 @@
         <v>1184.4</v>
       </c>
       <c r="M60">
-        <v>2504.697559269056</v>
+        <v>2547.881999946108</v>
       </c>
       <c r="N60">
-        <v>-1320.297559269055</v>
+        <v>-1363.481999946108</v>
       </c>
       <c r="O60">
-        <v>-165.0371949086319</v>
+        <v>-170.4352499932635</v>
       </c>
       <c r="P60">
-        <v>-1155.260364360423</v>
+        <v>-1193.046749952845</v>
       </c>
       <c r="Q60">
-        <v>-613.6603643604234</v>
+        <v>-651.4467499528447</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1842955815614262</v>
+        <v>0.1876735225751195</v>
       </c>
       <c r="T60">
-        <v>2.699536666322596</v>
+        <v>2.765379024037781</v>
       </c>
       <c r="U60">
         <v>0.2067366166625341</v>
       </c>
       <c r="V60">
-        <v>0.05910893291372287</v>
+        <v>0.05810708659315129</v>
       </c>
       <c r="W60">
-        <v>0.1945166358574183</v>
+        <v>0.1947237541761491</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6489,7 +6489,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.4728714633097829</v>
+        <v>0.4648566927452104</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6497,22 +6497,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1918331592197269</v>
+        <v>0.1934425253863523</v>
       </c>
       <c r="C61">
-        <v>-2860.352862211954</v>
+        <v>-3162.082936924771</v>
       </c>
       <c r="D61">
-        <v>8768.437053517566</v>
+        <v>8675.593248562876</v>
       </c>
       <c r="E61">
-        <v>8749.162939916774</v>
+        <v>8958.049209674902</v>
       </c>
       <c r="F61">
-        <v>12324.28991572952</v>
+        <v>12533.17618548765</v>
       </c>
       <c r="G61">
         <v>695.5</v>
@@ -6533,37 +6533,37 @@
         <v>1184.4</v>
       </c>
       <c r="M61">
-        <v>2547.881999946108</v>
+        <v>2591.066440623161</v>
       </c>
       <c r="N61">
-        <v>-1363.481999946108</v>
+        <v>-1406.666440623161</v>
       </c>
       <c r="O61">
-        <v>-170.4352499932635</v>
+        <v>-175.8333050778951</v>
       </c>
       <c r="P61">
-        <v>-1193.046749952845</v>
+        <v>-1230.833135545266</v>
       </c>
       <c r="Q61">
-        <v>-651.4467499528447</v>
+        <v>-689.233135545266</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1876735225751195</v>
+        <v>0.1912203606394975</v>
       </c>
       <c r="T61">
-        <v>2.765379024037781</v>
+        <v>2.834513499638726</v>
       </c>
       <c r="U61">
         <v>0.2067366166625341</v>
       </c>
       <c r="V61">
-        <v>0.05810708659315129</v>
+        <v>0.05713863514993209</v>
       </c>
       <c r="W61">
-        <v>0.1947237541761491</v>
+        <v>0.1949239685509222</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6571,7 +6571,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.4648566927452104</v>
+        <v>0.4571090811994568</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1934425253863523</v>
+        <v>0.1950518915529776</v>
       </c>
       <c r="C62">
-        <v>-3162.082936924771</v>
+        <v>-3461.867475262847</v>
       </c>
       <c r="D62">
-        <v>8675.593248562876</v>
+        <v>8584.694979982927</v>
       </c>
       <c r="E62">
-        <v>8958.049209674902</v>
+        <v>9166.935479433028</v>
       </c>
       <c r="F62">
-        <v>12533.17618548765</v>
+        <v>12742.06245524577</v>
       </c>
       <c r="G62">
         <v>695.5</v>
@@ -6615,37 +6615,37 @@
         <v>1184.4</v>
       </c>
       <c r="M62">
-        <v>2591.066440623161</v>
+        <v>2634.250881300214</v>
       </c>
       <c r="N62">
-        <v>-1406.666440623161</v>
+        <v>-1449.850881300214</v>
       </c>
       <c r="O62">
-        <v>-175.8333050778951</v>
+        <v>-181.2313601625267</v>
       </c>
       <c r="P62">
-        <v>-1230.833135545266</v>
+        <v>-1268.619521137687</v>
       </c>
       <c r="Q62">
-        <v>-689.233135545266</v>
+        <v>-727.0195211376869</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1912203606394975</v>
+        <v>0.1949490878353821</v>
       </c>
       <c r="T62">
-        <v>2.834513499638726</v>
+        <v>2.907193332962796</v>
       </c>
       <c r="U62">
         <v>0.2067366166625341</v>
       </c>
       <c r="V62">
-        <v>0.05713863514993209</v>
+        <v>0.05620193621304797</v>
       </c>
       <c r="W62">
-        <v>0.1949239685509222</v>
+        <v>0.195117618519965</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6653,7 +6653,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.4571090811994568</v>
+        <v>0.4496154897043838</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6661,22 +6661,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1950518915529776</v>
+        <v>0.196661257719603</v>
       </c>
       <c r="C63">
-        <v>-3461.867475262847</v>
+        <v>-3759.766996039525</v>
       </c>
       <c r="D63">
-        <v>8584.694979982927</v>
+        <v>8495.681728964377</v>
       </c>
       <c r="E63">
-        <v>9166.935479433028</v>
+        <v>9375.821749191156</v>
       </c>
       <c r="F63">
-        <v>12742.06245524577</v>
+        <v>12950.9487250039</v>
       </c>
       <c r="G63">
         <v>695.5</v>
@@ -6697,37 +6697,37 @@
         <v>1184.4</v>
       </c>
       <c r="M63">
-        <v>2634.250881300214</v>
+        <v>2677.435321977267</v>
       </c>
       <c r="N63">
-        <v>-1449.850881300214</v>
+        <v>-1493.035321977266</v>
       </c>
       <c r="O63">
-        <v>-181.2313601625267</v>
+        <v>-186.6294152471583</v>
       </c>
       <c r="P63">
-        <v>-1268.619521137687</v>
+        <v>-1306.405906730108</v>
       </c>
       <c r="Q63">
-        <v>-727.0195211376869</v>
+        <v>-764.8059067301082</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1949490878353821</v>
+        <v>0.19887406383105</v>
       </c>
       <c r="T63">
-        <v>2.907193332962796</v>
+        <v>2.983698420672344</v>
       </c>
       <c r="U63">
         <v>0.2067366166625341</v>
       </c>
       <c r="V63">
-        <v>0.05620193621304797</v>
+        <v>0.05529545337090203</v>
       </c>
       <c r="W63">
-        <v>0.195117618519965</v>
+        <v>0.1953050217158129</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6735,7 +6735,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.4496154897043838</v>
+        <v>0.4423636269672162</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6743,22 +6743,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.196661257719603</v>
+        <v>0.1982706238862283</v>
       </c>
       <c r="C64">
-        <v>-3759.766996039525</v>
+        <v>-4055.839533789829</v>
       </c>
       <c r="D64">
-        <v>8495.681728964377</v>
+        <v>8408.495460972201</v>
       </c>
       <c r="E64">
-        <v>9375.821749191156</v>
+        <v>9584.708018949284</v>
       </c>
       <c r="F64">
-        <v>12950.9487250039</v>
+        <v>13159.83499476203</v>
       </c>
       <c r="G64">
         <v>695.5</v>
@@ -6779,37 +6779,37 @@
         <v>1184.4</v>
       </c>
       <c r="M64">
-        <v>2677.435321977267</v>
+        <v>2720.619762654319</v>
       </c>
       <c r="N64">
-        <v>-1493.035321977266</v>
+        <v>-1536.219762654319</v>
       </c>
       <c r="O64">
-        <v>-186.6294152471583</v>
+        <v>-192.0274703317899</v>
       </c>
       <c r="P64">
-        <v>-1306.405906730108</v>
+        <v>-1344.192292322529</v>
       </c>
       <c r="Q64">
-        <v>-764.8059067301082</v>
+        <v>-802.592292322529</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.19887406383105</v>
+        <v>0.2030112006913486</v>
       </c>
       <c r="T64">
-        <v>2.983698420672344</v>
+        <v>3.064338918528353</v>
       </c>
       <c r="U64">
         <v>0.2067366166625341</v>
       </c>
       <c r="V64">
-        <v>0.05529545337090203</v>
+        <v>0.0544177477618401</v>
       </c>
       <c r="W64">
-        <v>0.1953050217158129</v>
+        <v>0.1954864756038561</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6817,7 +6817,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.4423636269672162</v>
+        <v>0.4353419820947209</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6825,22 +6825,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1982706238862283</v>
+        <v>0.1998799900528537</v>
       </c>
       <c r="C65">
-        <v>-4055.839533789829</v>
+        <v>-4350.140764949118</v>
       </c>
       <c r="D65">
-        <v>8408.495460972201</v>
+        <v>8323.08049957104</v>
       </c>
       <c r="E65">
-        <v>9584.708018949284</v>
+        <v>9793.594288707412</v>
       </c>
       <c r="F65">
-        <v>13159.83499476203</v>
+        <v>13368.72126452016</v>
       </c>
       <c r="G65">
         <v>695.5</v>
@@ -6861,37 +6861,37 @@
         <v>1184.4</v>
       </c>
       <c r="M65">
-        <v>2720.619762654319</v>
+        <v>2763.804203331372</v>
       </c>
       <c r="N65">
-        <v>-1536.219762654319</v>
+        <v>-1579.404203331372</v>
       </c>
       <c r="O65">
-        <v>-192.0274703317899</v>
+        <v>-197.4255254164215</v>
       </c>
       <c r="P65">
-        <v>-1344.192292322529</v>
+        <v>-1381.97867791495</v>
       </c>
       <c r="Q65">
-        <v>-802.592292322529</v>
+        <v>-840.3786779149503</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2030112006913486</v>
+        <v>0.2073781784883306</v>
       </c>
       <c r="T65">
-        <v>3.064338918528353</v>
+        <v>3.149459444043029</v>
       </c>
       <c r="U65">
         <v>0.2067366166625341</v>
       </c>
       <c r="V65">
-        <v>0.0544177477618401</v>
+        <v>0.05356747045306134</v>
       </c>
       <c r="W65">
-        <v>0.1954864756038561</v>
+        <v>0.1956622590578979</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6899,7 +6899,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.4353419820947209</v>
+        <v>0.4285397636244908</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6907,22 +6907,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1998799900528537</v>
+        <v>0.2014893562194791</v>
       </c>
       <c r="C66">
-        <v>-4350.140764949118</v>
+        <v>-4642.724126418625</v>
       </c>
       <c r="D66">
-        <v>8323.08049957104</v>
+        <v>8239.383407859659</v>
       </c>
       <c r="E66">
-        <v>9793.594288707412</v>
+        <v>10002.48055846554</v>
       </c>
       <c r="F66">
-        <v>13368.72126452016</v>
+        <v>13577.60753427828</v>
       </c>
       <c r="G66">
         <v>695.5</v>
@@ -6943,37 +6943,37 @@
         <v>1184.4</v>
       </c>
       <c r="M66">
-        <v>2763.804203331372</v>
+        <v>2806.988644008424</v>
       </c>
       <c r="N66">
-        <v>-1579.404203331372</v>
+        <v>-1622.588644008424</v>
       </c>
       <c r="O66">
-        <v>-197.4255254164215</v>
+        <v>-202.823580501053</v>
       </c>
       <c r="P66">
-        <v>-1381.97867791495</v>
+        <v>-1419.765063507371</v>
       </c>
       <c r="Q66">
-        <v>-840.3786779149503</v>
+        <v>-878.165063507371</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2073781784883306</v>
+        <v>0.2119946978737114</v>
       </c>
       <c r="T66">
-        <v>3.149459444043029</v>
+        <v>3.239443999587116</v>
       </c>
       <c r="U66">
         <v>0.2067366166625341</v>
       </c>
       <c r="V66">
-        <v>0.05356747045306134</v>
+        <v>0.05274335552301426</v>
       </c>
       <c r="W66">
-        <v>0.1956622590578979</v>
+        <v>0.195832633790277</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.4285397636244908</v>
+        <v>0.421946844184114</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6989,22 +6989,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2014893562194791</v>
+        <v>0.2030987223861044</v>
       </c>
       <c r="C67">
-        <v>-4642.724126418625</v>
+        <v>-4933.640927048406</v>
       </c>
       <c r="D67">
-        <v>8239.383407859659</v>
+        <v>8157.352876988007</v>
       </c>
       <c r="E67">
-        <v>10002.48055846554</v>
+        <v>10211.36682822367</v>
       </c>
       <c r="F67">
-        <v>13577.60753427828</v>
+        <v>13786.49380403641</v>
       </c>
       <c r="G67">
         <v>695.5</v>
@@ -7025,37 +7025,37 @@
         <v>1184.4</v>
       </c>
       <c r="M67">
-        <v>2806.988644008424</v>
+        <v>2850.173084685477</v>
       </c>
       <c r="N67">
-        <v>-1622.588644008424</v>
+        <v>-1665.773084685477</v>
       </c>
       <c r="O67">
-        <v>-202.823580501053</v>
+        <v>-208.2216355856846</v>
       </c>
       <c r="P67">
-        <v>-1419.765063507371</v>
+        <v>-1457.551449099792</v>
       </c>
       <c r="Q67">
-        <v>-878.165063507371</v>
+        <v>-915.9514490997923</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2119946978737114</v>
+        <v>0.2168827772229383</v>
       </c>
       <c r="T67">
-        <v>3.239443999587116</v>
+        <v>3.334721764280855</v>
       </c>
       <c r="U67">
         <v>0.2067366166625341</v>
       </c>
       <c r="V67">
-        <v>0.05274335552301426</v>
+        <v>0.05194421377266555</v>
       </c>
       <c r="W67">
-        <v>0.195832633790277</v>
+        <v>0.1959978456519778</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.421946844184114</v>
+        <v>0.4155537101813244</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7071,22 +7071,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2030987223861044</v>
+        <v>0.2047080885527297</v>
       </c>
       <c r="C68">
-        <v>-4933.640927048406</v>
+        <v>-5222.940452526485</v>
       </c>
       <c r="D68">
-        <v>8157.352876988007</v>
+        <v>8076.939621268056</v>
       </c>
       <c r="E68">
-        <v>10211.36682822367</v>
+        <v>10420.25309798179</v>
       </c>
       <c r="F68">
-        <v>13786.49380403641</v>
+        <v>13995.38007379454</v>
       </c>
       <c r="G68">
         <v>695.5</v>
@@ -7107,37 +7107,37 @@
         <v>1184.4</v>
       </c>
       <c r="M68">
-        <v>2850.173084685477</v>
+        <v>2893.35752536253</v>
       </c>
       <c r="N68">
-        <v>-1665.773084685477</v>
+        <v>-1708.95752536253</v>
       </c>
       <c r="O68">
-        <v>-208.2216355856846</v>
+        <v>-213.6196906703162</v>
       </c>
       <c r="P68">
-        <v>-1457.551449099792</v>
+        <v>-1495.337834692214</v>
       </c>
       <c r="Q68">
-        <v>-915.9514490997923</v>
+        <v>-953.7378346922136</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2168827772229383</v>
+        <v>0.2220671038054515</v>
       </c>
       <c r="T68">
-        <v>3.334721764280855</v>
+        <v>3.435773938956032</v>
       </c>
       <c r="U68">
         <v>0.2067366166625341</v>
       </c>
       <c r="V68">
-        <v>0.05194421377266555</v>
+        <v>0.0511689269999392</v>
       </c>
       <c r="W68">
-        <v>0.1959978456519778</v>
+        <v>0.1961581258163145</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7145,7 +7145,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.4155537101813244</v>
+        <v>0.4093514159995135</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7153,22 +7153,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2047080885527297</v>
+        <v>0.206317454719355</v>
       </c>
       <c r="C69">
-        <v>-5222.940452526485</v>
+        <v>-5510.670064124677</v>
       </c>
       <c r="D69">
-        <v>8076.939621268056</v>
+        <v>7998.09627942799</v>
       </c>
       <c r="E69">
-        <v>10420.25309798179</v>
+        <v>10629.13936773992</v>
       </c>
       <c r="F69">
-        <v>13995.38007379454</v>
+        <v>14204.26634355267</v>
       </c>
       <c r="G69">
         <v>695.5</v>
@@ -7189,37 +7189,37 @@
         <v>1184.4</v>
       </c>
       <c r="M69">
-        <v>2893.35752536253</v>
+        <v>2936.541966039583</v>
       </c>
       <c r="N69">
-        <v>-1708.95752536253</v>
+        <v>-1752.141966039583</v>
       </c>
       <c r="O69">
-        <v>-213.6196906703162</v>
+        <v>-219.0177457549478</v>
       </c>
       <c r="P69">
-        <v>-1495.337834692214</v>
+        <v>-1533.124220284635</v>
       </c>
       <c r="Q69">
-        <v>-953.7378346922136</v>
+        <v>-991.5242202846349</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2220671038054515</v>
+        <v>0.2275754507993719</v>
       </c>
       <c r="T69">
-        <v>3.435773938956032</v>
+        <v>3.543141874548408</v>
       </c>
       <c r="U69">
         <v>0.2067366166625341</v>
       </c>
       <c r="V69">
-        <v>0.0511689269999392</v>
+        <v>0.05041644277935185</v>
       </c>
       <c r="W69">
-        <v>0.1961581258163145</v>
+        <v>0.1963136918581706</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7227,7 +7227,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.4093514159995135</v>
+        <v>0.4033315422348148</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7235,22 +7235,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.206317454719355</v>
+        <v>0.2079268208859804</v>
       </c>
       <c r="C70">
-        <v>-5510.670064124677</v>
+        <v>-5796.875291716917</v>
       </c>
       <c r="D70">
-        <v>7998.09627942799</v>
+        <v>7920.77732159388</v>
       </c>
       <c r="E70">
-        <v>10629.13936773992</v>
+        <v>10838.02563749805</v>
       </c>
       <c r="F70">
-        <v>14204.26634355267</v>
+        <v>14413.1526133108</v>
       </c>
       <c r="G70">
         <v>695.5</v>
@@ -7271,37 +7271,37 @@
         <v>1184.4</v>
       </c>
       <c r="M70">
-        <v>2936.541966039583</v>
+        <v>2979.726406716636</v>
       </c>
       <c r="N70">
-        <v>-1752.141966039583</v>
+        <v>-1795.326406716636</v>
       </c>
       <c r="O70">
-        <v>-219.0177457549478</v>
+        <v>-224.4158008395794</v>
       </c>
       <c r="P70">
-        <v>-1533.124220284635</v>
+        <v>-1570.910605877056</v>
       </c>
       <c r="Q70">
-        <v>-991.5242202846349</v>
+        <v>-1029.310605877056</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2275754507993719</v>
+        <v>0.2334391750187065</v>
       </c>
       <c r="T70">
-        <v>3.543141874548408</v>
+        <v>3.657436773727389</v>
       </c>
       <c r="U70">
         <v>0.2067366166625341</v>
       </c>
       <c r="V70">
-        <v>0.05041644277935185</v>
+        <v>0.04968576969559312</v>
       </c>
       <c r="W70">
-        <v>0.1963136918581706</v>
+        <v>0.1964647487393933</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7309,7 +7309,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.4033315422348148</v>
+        <v>0.397486157564745</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7317,22 +7317,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2079268208859804</v>
+        <v>0.2095361870526057</v>
       </c>
       <c r="C71">
-        <v>-5796.875291716917</v>
+        <v>-6081.599921453835</v>
       </c>
       <c r="D71">
-        <v>7920.77732159388</v>
+        <v>7844.938961615087</v>
       </c>
       <c r="E71">
-        <v>10838.02563749805</v>
+        <v>11046.91190725618</v>
       </c>
       <c r="F71">
-        <v>14413.1526133108</v>
+        <v>14622.03888306892</v>
       </c>
       <c r="G71">
         <v>695.5</v>
@@ -7353,37 +7353,37 @@
         <v>1184.4</v>
       </c>
       <c r="M71">
-        <v>2979.726406716636</v>
+        <v>3022.910847393688</v>
       </c>
       <c r="N71">
-        <v>-1795.326406716636</v>
+        <v>-1838.510847393688</v>
       </c>
       <c r="O71">
-        <v>-224.4158008395794</v>
+        <v>-229.813855924211</v>
       </c>
       <c r="P71">
-        <v>-1570.910605877056</v>
+        <v>-1608.696991469477</v>
       </c>
       <c r="Q71">
-        <v>-1029.310605877056</v>
+        <v>-1067.096991469477</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2334391750187065</v>
+        <v>0.2396938141859967</v>
       </c>
       <c r="T71">
-        <v>3.657436773727389</v>
+        <v>3.779351332851636</v>
       </c>
       <c r="U71">
         <v>0.2067366166625341</v>
       </c>
       <c r="V71">
-        <v>0.04968576969559312</v>
+        <v>0.04897597298565608</v>
       </c>
       <c r="W71">
-        <v>0.1964647487393933</v>
+        <v>0.1966114897097239</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.397486157564745</v>
+        <v>0.3918077838852487</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7399,22 +7399,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2095361870526057</v>
+        <v>0.2111455532192311</v>
       </c>
       <c r="C72">
-        <v>-6081.599921453835</v>
+        <v>-6364.886078448462</v>
       </c>
       <c r="D72">
-        <v>7844.938961615087</v>
+        <v>7770.539074378588</v>
       </c>
       <c r="E72">
-        <v>11046.91190725618</v>
+        <v>11255.79817701431</v>
       </c>
       <c r="F72">
-        <v>14622.03888306892</v>
+        <v>14830.92515282705</v>
       </c>
       <c r="G72">
         <v>695.5</v>
@@ -7435,37 +7435,37 @@
         <v>1184.4</v>
       </c>
       <c r="M72">
-        <v>3022.910847393688</v>
+        <v>3066.095288070741</v>
       </c>
       <c r="N72">
-        <v>-1838.510847393688</v>
+        <v>-1881.695288070741</v>
       </c>
       <c r="O72">
-        <v>-229.813855924211</v>
+        <v>-235.2119110088426</v>
       </c>
       <c r="P72">
-        <v>-1608.696991469477</v>
+        <v>-1646.483377061898</v>
       </c>
       <c r="Q72">
-        <v>-1067.096991469477</v>
+        <v>-1104.883377061898</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2396938141859967</v>
+        <v>0.2463798077786173</v>
       </c>
       <c r="T72">
-        <v>3.779351332851636</v>
+        <v>3.909673792605141</v>
       </c>
       <c r="U72">
         <v>0.2067366166625341</v>
       </c>
       <c r="V72">
-        <v>0.04897597298565608</v>
+        <v>0.04828617054923839</v>
       </c>
       <c r="W72">
-        <v>0.1966114897097239</v>
+        <v>0.1967540971315945</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7473,7 +7473,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3918077838852487</v>
+        <v>0.3862893643939072</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7481,22 +7481,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2111455532192311</v>
+        <v>0.2127549193858564</v>
       </c>
       <c r="C73">
-        <v>-6364.886078448459</v>
+        <v>-6646.774304801029</v>
       </c>
       <c r="D73">
-        <v>7770.539074378591</v>
+        <v>7697.537117784148</v>
       </c>
       <c r="E73">
-        <v>11255.7981770143</v>
+        <v>11464.68444677243</v>
       </c>
       <c r="F73">
-        <v>14830.92515282705</v>
+        <v>15039.81142258518</v>
       </c>
       <c r="G73">
         <v>695.5</v>
@@ -7517,37 +7517,37 @@
         <v>1184.4</v>
       </c>
       <c r="M73">
-        <v>3066.09528807074</v>
+        <v>3109.279728747793</v>
       </c>
       <c r="N73">
-        <v>-1881.69528807074</v>
+        <v>-1924.879728747793</v>
       </c>
       <c r="O73">
-        <v>-235.2119110088425</v>
+        <v>-240.6099660934742</v>
       </c>
       <c r="P73">
-        <v>-1646.483377061898</v>
+        <v>-1684.269762654319</v>
       </c>
       <c r="Q73">
-        <v>-1104.883377061898</v>
+        <v>-1142.669762654319</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2463798077786172</v>
+        <v>0.2535433723421393</v>
       </c>
       <c r="T73">
-        <v>3.909673792605139</v>
+        <v>4.049304999483894</v>
       </c>
       <c r="U73">
         <v>0.2067366166625341</v>
       </c>
       <c r="V73">
-        <v>0.0482861705492384</v>
+        <v>0.04761552929161009</v>
       </c>
       <c r="W73">
-        <v>0.1967540971315944</v>
+        <v>0.1968927432361909</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3862893643939072</v>
+        <v>0.3809242343328807</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7563,22 +7563,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2127549193858564</v>
+        <v>0.2143642855524817</v>
       </c>
       <c r="C74">
-        <v>-6646.774304801029</v>
+        <v>-6927.303633266642</v>
       </c>
       <c r="D74">
-        <v>7697.537117784148</v>
+        <v>7625.894059076661</v>
       </c>
       <c r="E74">
-        <v>11464.68444677243</v>
+        <v>11673.57071653056</v>
       </c>
       <c r="F74">
-        <v>15039.81142258518</v>
+        <v>15248.6976923433</v>
       </c>
       <c r="G74">
         <v>695.5</v>
@@ -7599,37 +7599,37 @@
         <v>1184.4</v>
       </c>
       <c r="M74">
-        <v>3109.279728747793</v>
+        <v>3152.464169424846</v>
       </c>
       <c r="N74">
-        <v>-1924.879728747793</v>
+        <v>-1968.064169424846</v>
       </c>
       <c r="O74">
-        <v>-240.6099660934742</v>
+        <v>-246.0080211781057</v>
       </c>
       <c r="P74">
-        <v>-1684.269762654319</v>
+        <v>-1722.05614824674</v>
       </c>
       <c r="Q74">
-        <v>-1142.669762654319</v>
+        <v>-1180.45614824674</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2535433723421393</v>
+        <v>0.261237571317774</v>
       </c>
       <c r="T74">
-        <v>4.049304999483894</v>
+        <v>4.199279258724038</v>
       </c>
       <c r="U74">
         <v>0.2067366166625341</v>
       </c>
       <c r="V74">
-        <v>0.04761552929161009</v>
+        <v>0.04696326176706749</v>
       </c>
       <c r="W74">
-        <v>0.1968927432361909</v>
+        <v>0.1970275908173736</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7637,7 +7637,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3809242343328807</v>
+        <v>0.3757060941365399</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7645,22 +7645,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2143642855524817</v>
+        <v>0.215973651719107</v>
       </c>
       <c r="C75">
-        <v>-6927.303633266642</v>
+        <v>-7206.511656846964</v>
       </c>
       <c r="D75">
-        <v>7625.894059076661</v>
+        <v>7555.572305254466</v>
       </c>
       <c r="E75">
-        <v>11673.57071653056</v>
+        <v>11882.45698628869</v>
       </c>
       <c r="F75">
-        <v>15248.6976923433</v>
+        <v>15457.58396210143</v>
       </c>
       <c r="G75">
         <v>695.5</v>
@@ -7681,37 +7681,37 @@
         <v>1184.4</v>
       </c>
       <c r="M75">
-        <v>3152.464169424846</v>
+        <v>3195.648610101899</v>
       </c>
       <c r="N75">
-        <v>-1968.064169424846</v>
+        <v>-2011.248610101899</v>
       </c>
       <c r="O75">
-        <v>-246.0080211781057</v>
+        <v>-251.4060762627373</v>
       </c>
       <c r="P75">
-        <v>-1722.05614824674</v>
+        <v>-1759.842533839161</v>
       </c>
       <c r="Q75">
-        <v>-1180.45614824674</v>
+        <v>-1218.242533839161</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.261237571317774</v>
+        <v>0.269523631753073</v>
       </c>
       <c r="T75">
-        <v>4.199279258724038</v>
+        <v>4.360789999444194</v>
       </c>
       <c r="U75">
         <v>0.2067366166625341</v>
       </c>
       <c r="V75">
-        <v>0.04696326176706749</v>
+        <v>0.04632862309453954</v>
       </c>
       <c r="W75">
-        <v>0.1970275908173736</v>
+        <v>0.1971587938693352</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7719,7 +7719,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3757060941365399</v>
+        <v>0.3706289847563163</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7727,22 +7727,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.215973651719107</v>
+        <v>0.2175830178857324</v>
       </c>
       <c r="C76">
-        <v>-7206.511656846964</v>
+        <v>-7484.434594566692</v>
       </c>
       <c r="D76">
-        <v>7555.572305254466</v>
+        <v>7486.535637292867</v>
       </c>
       <c r="E76">
-        <v>11882.45698628869</v>
+        <v>12091.34325604681</v>
       </c>
       <c r="F76">
-        <v>15457.58396210143</v>
+        <v>15666.47023185956</v>
       </c>
       <c r="G76">
         <v>695.5</v>
@@ -7763,37 +7763,37 @@
         <v>1184.4</v>
       </c>
       <c r="M76">
-        <v>3195.648610101899</v>
+        <v>3238.833050778951</v>
       </c>
       <c r="N76">
-        <v>-2011.248610101899</v>
+        <v>-2054.433050778951</v>
       </c>
       <c r="O76">
-        <v>-251.4060762627373</v>
+        <v>-256.8041313473689</v>
       </c>
       <c r="P76">
-        <v>-1759.842533839161</v>
+        <v>-1797.628919431583</v>
       </c>
       <c r="Q76">
-        <v>-1218.242533839161</v>
+        <v>-1256.028919431582</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.269523631753073</v>
+        <v>0.2784725770231959</v>
       </c>
       <c r="T76">
-        <v>4.360789999444194</v>
+        <v>4.535221599421962</v>
       </c>
       <c r="U76">
         <v>0.2067366166625341</v>
       </c>
       <c r="V76">
-        <v>0.04632862309453954</v>
+        <v>0.04571090811994568</v>
       </c>
       <c r="W76">
-        <v>0.1971587938693352</v>
+        <v>0.1972864981732446</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7801,7 +7801,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3706289847563163</v>
+        <v>0.3656872649595654</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7809,22 +7809,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2175830178857324</v>
+        <v>0.2191923840523578</v>
       </c>
       <c r="C77">
-        <v>-7484.434594566692</v>
+        <v>-7761.10735367661</v>
       </c>
       <c r="D77">
-        <v>7486.535637292867</v>
+        <v>7418.749147941077</v>
       </c>
       <c r="E77">
-        <v>12091.34325604681</v>
+        <v>12300.22952580494</v>
       </c>
       <c r="F77">
-        <v>15666.47023185956</v>
+        <v>15875.35650161769</v>
       </c>
       <c r="G77">
         <v>695.5</v>
@@ -7845,37 +7845,37 @@
         <v>1184.4</v>
       </c>
       <c r="M77">
-        <v>3238.833050778951</v>
+        <v>3282.017491456004</v>
       </c>
       <c r="N77">
-        <v>-2054.433050778951</v>
+        <v>-2097.617491456004</v>
       </c>
       <c r="O77">
-        <v>-256.8041313473689</v>
+        <v>-262.2021864320005</v>
       </c>
       <c r="P77">
-        <v>-1797.628919431583</v>
+        <v>-1835.415305024004</v>
       </c>
       <c r="Q77">
-        <v>-1256.028919431582</v>
+        <v>-1293.815305024004</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2784725770231959</v>
+        <v>0.2881672677324958</v>
       </c>
       <c r="T77">
-        <v>4.535221599421962</v>
+        <v>4.724189166064544</v>
       </c>
       <c r="U77">
         <v>0.2067366166625341</v>
       </c>
       <c r="V77">
-        <v>0.04571090811994568</v>
+        <v>0.04510944880257797</v>
       </c>
       <c r="W77">
-        <v>0.1972864981732446</v>
+        <v>0.1974108418375773</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7883,7 +7883,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3656872649595654</v>
+        <v>0.3608755904206238</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7891,22 +7891,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2191923840523578</v>
+        <v>0.2208017502189831</v>
       </c>
       <c r="C78">
-        <v>-7761.10735367661</v>
+        <v>-8036.563588507681</v>
       </c>
       <c r="D78">
-        <v>7418.749147941077</v>
+        <v>7352.179182868134</v>
       </c>
       <c r="E78">
-        <v>12300.22952580494</v>
+        <v>12509.11579556307</v>
       </c>
       <c r="F78">
-        <v>15875.35650161769</v>
+        <v>16084.24277137582</v>
       </c>
       <c r="G78">
         <v>695.5</v>
@@ -7927,37 +7927,37 @@
         <v>1184.4</v>
       </c>
       <c r="M78">
-        <v>3282.017491456004</v>
+        <v>3325.201932133057</v>
       </c>
       <c r="N78">
-        <v>-2097.617491456004</v>
+        <v>-2140.801932133057</v>
       </c>
       <c r="O78">
-        <v>-262.2021864320005</v>
+        <v>-267.6002415166321</v>
       </c>
       <c r="P78">
-        <v>-1835.415305024004</v>
+        <v>-1873.201690616424</v>
       </c>
       <c r="Q78">
-        <v>-1293.815305024004</v>
+        <v>-1331.601690616425</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2881672677324958</v>
+        <v>0.298704975025213</v>
       </c>
       <c r="T78">
-        <v>4.724189166064544</v>
+        <v>4.929588695023872</v>
       </c>
       <c r="U78">
         <v>0.2067366166625341</v>
       </c>
       <c r="V78">
-        <v>0.04510944880257797</v>
+        <v>0.0445236118051419</v>
       </c>
       <c r="W78">
-        <v>0.1974108418375773</v>
+        <v>0.197531955796343</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7965,7 +7965,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3608755904206238</v>
+        <v>0.3561888944411352</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7973,22 +7973,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2208017502189831</v>
+        <v>0.2224111163856085</v>
       </c>
       <c r="C79">
-        <v>-8036.563588507681</v>
+        <v>-8310.835756184657</v>
       </c>
       <c r="D79">
-        <v>7352.179182868134</v>
+        <v>7286.793284949285</v>
       </c>
       <c r="E79">
-        <v>12509.11579556307</v>
+        <v>12718.0020653212</v>
       </c>
       <c r="F79">
-        <v>16084.24277137582</v>
+        <v>16293.12904113394</v>
       </c>
       <c r="G79">
         <v>695.5</v>
@@ -8009,37 +8009,37 @@
         <v>1184.4</v>
       </c>
       <c r="M79">
-        <v>3325.201932133057</v>
+        <v>3368.386372810109</v>
       </c>
       <c r="N79">
-        <v>-2140.801932133057</v>
+        <v>-2183.986372810109</v>
       </c>
       <c r="O79">
-        <v>-267.6002415166321</v>
+        <v>-272.9982966012636</v>
       </c>
       <c r="P79">
-        <v>-1873.201690616424</v>
+        <v>-1910.988076208846</v>
       </c>
       <c r="Q79">
-        <v>-1331.601690616425</v>
+        <v>-1369.388076208846</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.298704975025213</v>
+        <v>0.3102006557081772</v>
       </c>
       <c r="T79">
-        <v>4.929588695023872</v>
+        <v>5.153660908434047</v>
       </c>
       <c r="U79">
         <v>0.2067366166625341</v>
       </c>
       <c r="V79">
-        <v>0.0445236118051419</v>
+        <v>0.04395279626917854</v>
       </c>
       <c r="W79">
-        <v>0.197531955796343</v>
+        <v>0.1976499642689865</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3561888944411352</v>
+        <v>0.3516223701534283</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8055,22 +8055,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2224111163856085</v>
+        <v>0.2240204825522338</v>
       </c>
       <c r="C80">
-        <v>-8310.835756184657</v>
+        <v>-8583.955169392995</v>
       </c>
       <c r="D80">
-        <v>7286.793284949285</v>
+        <v>7222.560141499076</v>
       </c>
       <c r="E80">
-        <v>12718.0020653212</v>
+        <v>12926.88833507933</v>
       </c>
       <c r="F80">
-        <v>16293.12904113394</v>
+        <v>16502.01531089207</v>
       </c>
       <c r="G80">
         <v>695.5</v>
@@ -8091,37 +8091,37 @@
         <v>1184.4</v>
       </c>
       <c r="M80">
-        <v>3368.386372810109</v>
+        <v>3411.570813487162</v>
       </c>
       <c r="N80">
-        <v>-2183.986372810109</v>
+        <v>-2227.170813487162</v>
       </c>
       <c r="O80">
-        <v>-272.9982966012636</v>
+        <v>-278.3963516858953</v>
       </c>
       <c r="P80">
-        <v>-1910.988076208846</v>
+        <v>-1948.774461801267</v>
       </c>
       <c r="Q80">
-        <v>-1369.388076208846</v>
+        <v>-1407.174461801267</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3102006557081772</v>
+        <v>0.3227911631228524</v>
       </c>
       <c r="T80">
-        <v>5.153660908434047</v>
+        <v>5.399073332645194</v>
       </c>
       <c r="U80">
         <v>0.2067366166625341</v>
       </c>
       <c r="V80">
-        <v>0.04395279626917854</v>
+        <v>0.0433964317594421</v>
       </c>
       <c r="W80">
-        <v>0.1976499642689865</v>
+        <v>0.1977649851853605</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8129,7 +8129,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3516223701534283</v>
+        <v>0.3471714540755367</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8137,22 +8137,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2240204825522338</v>
+        <v>0.2256298487188591</v>
       </c>
       <c r="C81">
-        <v>-8583.955169392995</v>
+        <v>-8855.952046379296</v>
       </c>
       <c r="D81">
-        <v>7222.560141499076</v>
+        <v>7159.4495342709</v>
       </c>
       <c r="E81">
-        <v>12926.88833507933</v>
+        <v>13135.77460483745</v>
       </c>
       <c r="F81">
-        <v>16502.01531089207</v>
+        <v>16710.9015806502</v>
       </c>
       <c r="G81">
         <v>695.5</v>
@@ -8173,37 +8173,37 @@
         <v>1184.4</v>
       </c>
       <c r="M81">
-        <v>3411.570813487162</v>
+        <v>3454.755254164214</v>
       </c>
       <c r="N81">
-        <v>-2227.170813487162</v>
+        <v>-2270.355254164214</v>
       </c>
       <c r="O81">
-        <v>-278.3963516858953</v>
+        <v>-283.7944067705268</v>
       </c>
       <c r="P81">
-        <v>-1948.774461801267</v>
+        <v>-1986.560847393687</v>
       </c>
       <c r="Q81">
-        <v>-1407.174461801267</v>
+        <v>-1444.960847393687</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3227911631228524</v>
+        <v>0.3366407212789951</v>
       </c>
       <c r="T81">
-        <v>5.399073332645194</v>
+        <v>5.669026999277454</v>
       </c>
       <c r="U81">
         <v>0.2067366166625341</v>
       </c>
       <c r="V81">
-        <v>0.0433964317594421</v>
+        <v>0.04285397636244908</v>
       </c>
       <c r="W81">
-        <v>0.1977649851853605</v>
+        <v>0.1978771305788252</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8211,7 +8211,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3471714540755367</v>
+        <v>0.3428318108995927</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8219,22 +8219,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2256298487188591</v>
+        <v>0.2272392148854845</v>
       </c>
       <c r="C82">
-        <v>-8855.952046379296</v>
+        <v>-9126.85555835308</v>
       </c>
       <c r="D82">
-        <v>7159.4495342709</v>
+        <v>7097.432292055243</v>
       </c>
       <c r="E82">
-        <v>13135.77460483745</v>
+        <v>13344.66087459558</v>
       </c>
       <c r="F82">
-        <v>16710.9015806502</v>
+        <v>16919.78785040832</v>
       </c>
       <c r="G82">
         <v>695.5</v>
@@ -8255,37 +8255,37 @@
         <v>1184.4</v>
       </c>
       <c r="M82">
-        <v>3454.755254164214</v>
+        <v>3497.939694841267</v>
       </c>
       <c r="N82">
-        <v>-2270.355254164214</v>
+        <v>-2313.539694841267</v>
       </c>
       <c r="O82">
-        <v>-283.7944067705268</v>
+        <v>-289.1924618551584</v>
       </c>
       <c r="P82">
-        <v>-1986.560847393687</v>
+        <v>-2024.347232986109</v>
       </c>
       <c r="Q82">
-        <v>-1444.960847393687</v>
+        <v>-1482.747232986109</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3366407212789951</v>
+        <v>0.3519481276621</v>
       </c>
       <c r="T82">
-        <v>5.669026999277454</v>
+        <v>5.967396841344688</v>
       </c>
       <c r="U82">
         <v>0.2067366166625341</v>
       </c>
       <c r="V82">
-        <v>0.04285397636244908</v>
+        <v>0.04232491492587563</v>
       </c>
       <c r="W82">
-        <v>0.1978771305788252</v>
+        <v>0.197986506950229</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8293,7 +8293,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3428318108995927</v>
+        <v>0.3385993194070051</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8301,22 +8301,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2272392148854845</v>
+        <v>0.2288485810521098</v>
       </c>
       <c r="C83">
-        <v>-9126.85555835308</v>
+        <v>-9396.693874446002</v>
       </c>
       <c r="D83">
-        <v>7097.432292055243</v>
+        <v>7036.480245720449</v>
       </c>
       <c r="E83">
-        <v>13344.66087459558</v>
+        <v>13553.54714435371</v>
       </c>
       <c r="F83">
-        <v>16919.78785040832</v>
+        <v>17128.67412016645</v>
       </c>
       <c r="G83">
         <v>695.5</v>
@@ -8337,37 +8337,37 @@
         <v>1184.4</v>
       </c>
       <c r="M83">
-        <v>3497.939694841267</v>
+        <v>3541.12413551832</v>
       </c>
       <c r="N83">
-        <v>-2313.539694841267</v>
+        <v>-2356.72413551832</v>
       </c>
       <c r="O83">
-        <v>-289.1924618551584</v>
+        <v>-294.59051693979</v>
       </c>
       <c r="P83">
-        <v>-2024.347232986109</v>
+        <v>-2062.13361857853</v>
       </c>
       <c r="Q83">
-        <v>-1482.747232986109</v>
+        <v>-1520.53361857853</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3519481276621</v>
+        <v>0.3689563569766612</v>
       </c>
       <c r="T83">
-        <v>5.967396841344688</v>
+        <v>6.29891888808606</v>
       </c>
       <c r="U83">
         <v>0.2067366166625341</v>
       </c>
       <c r="V83">
-        <v>0.04232491492587563</v>
+        <v>0.04180875742677959</v>
       </c>
       <c r="W83">
-        <v>0.197986506950229</v>
+        <v>0.1980932156052571</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3385993194070051</v>
+        <v>0.3344700594142367</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8383,22 +8383,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2288485810521098</v>
+        <v>0.2304579472187352</v>
       </c>
       <c r="C84">
-        <v>-9396.693874446002</v>
+        <v>-9665.494204374236</v>
       </c>
       <c r="D84">
-        <v>7036.480245720449</v>
+        <v>6976.566185550344</v>
       </c>
       <c r="E84">
-        <v>13553.54714435371</v>
+        <v>13762.43341411183</v>
       </c>
       <c r="F84">
-        <v>17128.67412016645</v>
+        <v>17337.56038992458</v>
       </c>
       <c r="G84">
         <v>695.5</v>
@@ -8419,37 +8419,37 @@
         <v>1184.4</v>
       </c>
       <c r="M84">
-        <v>3541.12413551832</v>
+        <v>3584.308576195373</v>
       </c>
       <c r="N84">
-        <v>-2356.72413551832</v>
+        <v>-2399.908576195373</v>
       </c>
       <c r="O84">
-        <v>-294.59051693979</v>
+        <v>-299.9885720244216</v>
       </c>
       <c r="P84">
-        <v>-2062.13361857853</v>
+        <v>-2099.920004170951</v>
       </c>
       <c r="Q84">
-        <v>-1520.53361857853</v>
+        <v>-1558.320004170952</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3689563569766612</v>
+        <v>0.3879655544458765</v>
       </c>
       <c r="T84">
-        <v>6.29891888808606</v>
+        <v>6.669443528561711</v>
       </c>
       <c r="U84">
         <v>0.2067366166625341</v>
       </c>
       <c r="V84">
-        <v>0.04180875742677959</v>
+        <v>0.04130503745778224</v>
       </c>
       <c r="W84">
-        <v>0.1980932156052571</v>
+        <v>0.198197352967393</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8457,7 +8457,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3344700594142367</v>
+        <v>0.330440299662258</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8465,22 +8465,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2304579472187352</v>
+        <v>0.2320673133853605</v>
       </c>
       <c r="C85">
-        <v>-9665.494204374236</v>
+        <v>-9933.282838939633</v>
       </c>
       <c r="D85">
-        <v>6976.566185550344</v>
+        <v>6917.663820743075</v>
       </c>
       <c r="E85">
-        <v>13762.43341411183</v>
+        <v>13971.31968386996</v>
       </c>
       <c r="F85">
-        <v>17337.56038992458</v>
+        <v>17546.44665968271</v>
       </c>
       <c r="G85">
         <v>695.5</v>
@@ -8501,37 +8501,37 @@
         <v>1184.4</v>
       </c>
       <c r="M85">
-        <v>3584.308576195373</v>
+        <v>3627.493016872426</v>
       </c>
       <c r="N85">
-        <v>-2399.908576195373</v>
+        <v>-2443.093016872426</v>
       </c>
       <c r="O85">
-        <v>-299.9885720244216</v>
+        <v>-305.3866271090532</v>
       </c>
       <c r="P85">
-        <v>-2099.920004170951</v>
+        <v>-2137.706389763372</v>
       </c>
       <c r="Q85">
-        <v>-1558.320004170952</v>
+        <v>-1596.106389763373</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3879655544458765</v>
+        <v>0.4093509015987439</v>
       </c>
       <c r="T85">
-        <v>6.669443528561711</v>
+        <v>7.08628374909682</v>
       </c>
       <c r="U85">
         <v>0.2067366166625341</v>
       </c>
       <c r="V85">
-        <v>0.04130503745778224</v>
+        <v>0.04081331082138007</v>
       </c>
       <c r="W85">
-        <v>0.198197352967393</v>
+        <v>0.1982990108685256</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8539,7 +8539,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.330440299662258</v>
+        <v>0.3265064865710405</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8547,22 +8547,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2320673133853605</v>
+        <v>0.2336766795519858</v>
       </c>
       <c r="C86">
-        <v>-9933.282838939629</v>
+        <v>-10200.08518849641</v>
       </c>
       <c r="D86">
-        <v>6917.663820743075</v>
+        <v>6859.747740944423</v>
       </c>
       <c r="E86">
-        <v>13971.31968386996</v>
+        <v>14180.20595362809</v>
       </c>
       <c r="F86">
-        <v>17546.4466596827</v>
+        <v>17755.33292944083</v>
       </c>
       <c r="G86">
         <v>695.5</v>
@@ -8583,37 +8583,37 @@
         <v>1184.4</v>
       </c>
       <c r="M86">
-        <v>3627.493016872425</v>
+        <v>3670.677457549478</v>
       </c>
       <c r="N86">
-        <v>-2443.093016872425</v>
+        <v>-2486.277457549478</v>
       </c>
       <c r="O86">
-        <v>-305.3866271090531</v>
+        <v>-310.7846821936847</v>
       </c>
       <c r="P86">
-        <v>-2137.706389763372</v>
+        <v>-2175.492775355793</v>
       </c>
       <c r="Q86">
-        <v>-1596.106389763372</v>
+        <v>-1633.892775355793</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4093509015987437</v>
+        <v>0.4335876283719933</v>
       </c>
       <c r="T86">
-        <v>7.086283749096815</v>
+        <v>7.558702665703269</v>
       </c>
       <c r="U86">
         <v>0.2067366166625341</v>
       </c>
       <c r="V86">
-        <v>0.04081331082138008</v>
+        <v>0.04033315422348149</v>
       </c>
       <c r="W86">
-        <v>0.1982990108685256</v>
+        <v>0.1983982768190433</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3265064865710406</v>
+        <v>0.3226652337878519</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8629,22 +8629,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2336766795519858</v>
+        <v>0.2352860457186112</v>
       </c>
       <c r="C87">
-        <v>-10200.08518849641</v>
+        <v>-10465.9258195016</v>
       </c>
       <c r="D87">
-        <v>6859.747740944423</v>
+        <v>6802.79337969736</v>
       </c>
       <c r="E87">
-        <v>14180.20595362809</v>
+        <v>14389.09222338621</v>
       </c>
       <c r="F87">
-        <v>17755.33292944083</v>
+        <v>17964.21919919896</v>
       </c>
       <c r="G87">
         <v>695.5</v>
@@ -8665,37 +8665,37 @@
         <v>1184.4</v>
       </c>
       <c r="M87">
-        <v>3670.677457549478</v>
+        <v>3713.861898226531</v>
       </c>
       <c r="N87">
-        <v>-2486.277457549478</v>
+        <v>-2529.461898226531</v>
       </c>
       <c r="O87">
-        <v>-310.7846821936847</v>
+        <v>-316.1827372783163</v>
       </c>
       <c r="P87">
-        <v>-2175.492775355793</v>
+        <v>-2213.279160948214</v>
       </c>
       <c r="Q87">
-        <v>-1633.892775355793</v>
+        <v>-1671.679160948214</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4335876283719933</v>
+        <v>0.4612867446842785</v>
       </c>
       <c r="T87">
-        <v>7.558702665703269</v>
+        <v>8.098609998967788</v>
       </c>
       <c r="U87">
         <v>0.2067366166625341</v>
       </c>
       <c r="V87">
-        <v>0.04033315422348149</v>
+        <v>0.03986416405809216</v>
       </c>
       <c r="W87">
-        <v>0.1983982768190433</v>
+        <v>0.1984952342590839</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8703,7 +8703,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3226652337878519</v>
+        <v>0.3189133124647373</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8711,22 +8711,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2352860457186112</v>
+        <v>0.2368954118852365</v>
       </c>
       <c r="C88">
-        <v>-10465.9258195016</v>
+        <v>-10730.82848925961</v>
       </c>
       <c r="D88">
-        <v>6802.79337969736</v>
+        <v>6746.776979697483</v>
       </c>
       <c r="E88">
-        <v>14389.09222338621</v>
+        <v>14597.97849314434</v>
       </c>
       <c r="F88">
-        <v>17964.21919919896</v>
+        <v>18173.10546895709</v>
       </c>
       <c r="G88">
         <v>695.5</v>
@@ -8747,37 +8747,37 @@
         <v>1184.4</v>
       </c>
       <c r="M88">
-        <v>3713.861898226531</v>
+        <v>3757.046338903584</v>
       </c>
       <c r="N88">
-        <v>-2529.461898226531</v>
+        <v>-2572.646338903583</v>
       </c>
       <c r="O88">
-        <v>-316.1827372783163</v>
+        <v>-321.5807923629479</v>
       </c>
       <c r="P88">
-        <v>-2213.279160948214</v>
+        <v>-2251.065546540635</v>
       </c>
       <c r="Q88">
-        <v>-1671.679160948214</v>
+        <v>-1709.465546540635</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4612867446842785</v>
+        <v>0.4932472635061461</v>
       </c>
       <c r="T88">
-        <v>8.098609998967788</v>
+        <v>8.721579998888387</v>
       </c>
       <c r="U88">
         <v>0.2067366166625341</v>
       </c>
       <c r="V88">
-        <v>0.03986416405809216</v>
+        <v>0.03940595527581525</v>
       </c>
       <c r="W88">
-        <v>0.1984952342590839</v>
+        <v>0.1985899627924569</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8785,7 +8785,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3189133124647373</v>
+        <v>0.3152476422065219</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8793,22 +8793,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2368954118852365</v>
+        <v>0.2385047780518618</v>
       </c>
       <c r="C89">
-        <v>-10730.82848925961</v>
+        <v>-10994.81617896431</v>
       </c>
       <c r="D89">
-        <v>6746.776979697483</v>
+        <v>6691.675559750909</v>
       </c>
       <c r="E89">
-        <v>14597.97849314434</v>
+        <v>14806.86476290247</v>
       </c>
       <c r="F89">
-        <v>18173.10546895709</v>
+        <v>18381.99173871522</v>
       </c>
       <c r="G89">
         <v>695.5</v>
@@ -8829,37 +8829,37 @@
         <v>1184.4</v>
       </c>
       <c r="M89">
-        <v>3757.046338903584</v>
+        <v>3800.230779580636</v>
       </c>
       <c r="N89">
-        <v>-2572.646338903583</v>
+        <v>-2615.830779580636</v>
       </c>
       <c r="O89">
-        <v>-321.5807923629479</v>
+        <v>-326.9788474475795</v>
       </c>
       <c r="P89">
-        <v>-2251.065546540635</v>
+        <v>-2288.851932133057</v>
       </c>
       <c r="Q89">
-        <v>-1709.465546540635</v>
+        <v>-1747.251932133057</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4932472635061461</v>
+        <v>0.5305345354649916</v>
       </c>
       <c r="T89">
-        <v>8.721579998888387</v>
+        <v>9.448378332129089</v>
       </c>
       <c r="U89">
         <v>0.2067366166625341</v>
       </c>
       <c r="V89">
-        <v>0.03940595527581525</v>
+        <v>0.03895816032949916</v>
       </c>
       <c r="W89">
-        <v>0.1985899627924569</v>
+        <v>0.1986825384046169</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8867,7 +8867,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3152476422065219</v>
+        <v>0.3116652826359932</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8875,22 +8875,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2385047780518618</v>
+        <v>0.2401141442184871</v>
       </c>
       <c r="C90">
-        <v>-10994.81617896431</v>
+        <v>-11257.91112513501</v>
       </c>
       <c r="D90">
-        <v>6691.675559750909</v>
+        <v>6637.466883338332</v>
       </c>
       <c r="E90">
-        <v>14806.86476290247</v>
+        <v>15015.7510326606</v>
       </c>
       <c r="F90">
-        <v>18381.99173871522</v>
+        <v>18590.87800847334</v>
       </c>
       <c r="G90">
         <v>695.5</v>
@@ -8911,37 +8911,37 @@
         <v>1184.4</v>
       </c>
       <c r="M90">
-        <v>3800.230779580636</v>
+        <v>3843.415220257689</v>
       </c>
       <c r="N90">
-        <v>-2615.830779580636</v>
+        <v>-2659.015220257689</v>
       </c>
       <c r="O90">
-        <v>-326.9788474475795</v>
+        <v>-332.3769025322111</v>
       </c>
       <c r="P90">
-        <v>-2288.851932133057</v>
+        <v>-2326.638317725478</v>
       </c>
       <c r="Q90">
-        <v>-1747.251932133057</v>
+        <v>-1785.038317725478</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5305345354649916</v>
+        <v>0.5746013114163544</v>
       </c>
       <c r="T90">
-        <v>9.448378332129089</v>
+        <v>10.30732181686809</v>
       </c>
       <c r="U90">
         <v>0.2067366166625341</v>
       </c>
       <c r="V90">
-        <v>0.03895816032949916</v>
+        <v>0.03852042819096546</v>
       </c>
       <c r="W90">
-        <v>0.1986825384046169</v>
+        <v>0.1987730336659418</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8949,7 +8949,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3116652826359932</v>
+        <v>0.3081634255277237</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8957,22 +8957,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2401141442184871</v>
+        <v>0.2417235103851125</v>
       </c>
       <c r="C91">
-        <v>-11257.91112513501</v>
+        <v>-11520.13484953685</v>
       </c>
       <c r="D91">
-        <v>6637.466883338332</v>
+        <v>6584.129428694617</v>
       </c>
       <c r="E91">
-        <v>15015.7510326606</v>
+        <v>15224.63730241873</v>
       </c>
       <c r="F91">
-        <v>18590.87800847334</v>
+        <v>18799.76427823147</v>
       </c>
       <c r="G91">
         <v>695.5</v>
@@ -8993,37 +8993,37 @@
         <v>1184.4</v>
       </c>
       <c r="M91">
-        <v>3843.415220257689</v>
+        <v>3886.599660934742</v>
       </c>
       <c r="N91">
-        <v>-2659.015220257689</v>
+        <v>-2702.199660934742</v>
       </c>
       <c r="O91">
-        <v>-332.3769025322111</v>
+        <v>-337.7749576168427</v>
       </c>
       <c r="P91">
-        <v>-2326.638317725478</v>
+        <v>-2364.424703317899</v>
       </c>
       <c r="Q91">
-        <v>-1785.038317725478</v>
+        <v>-1822.824703317899</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5746013114163544</v>
+        <v>0.62748144255799</v>
       </c>
       <c r="T91">
-        <v>10.30732181686809</v>
+        <v>11.33805399855491</v>
       </c>
       <c r="U91">
         <v>0.2067366166625341</v>
       </c>
       <c r="V91">
-        <v>0.03852042819096546</v>
+        <v>0.03809242343328807</v>
       </c>
       <c r="W91">
-        <v>0.1987730336659418</v>
+        <v>0.1988615179214595</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -9031,7 +9031,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3081634255277237</v>
+        <v>0.3047393874663046</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9039,22 +9039,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2417235103851125</v>
+        <v>0.2433328765517379</v>
       </c>
       <c r="C92">
-        <v>-11520.13484953685</v>
+        <v>-11781.50818766998</v>
       </c>
       <c r="D92">
-        <v>6584.129428694617</v>
+        <v>6531.642360319625</v>
       </c>
       <c r="E92">
-        <v>15224.63730241873</v>
+        <v>15433.52357217685</v>
       </c>
       <c r="F92">
-        <v>18799.76427823147</v>
+        <v>19008.6505479896</v>
       </c>
       <c r="G92">
         <v>695.5</v>
@@ -9075,37 +9075,37 @@
         <v>1184.4</v>
       </c>
       <c r="M92">
-        <v>3886.599660934742</v>
+        <v>3929.784101611795</v>
       </c>
       <c r="N92">
-        <v>-2702.199660934742</v>
+        <v>-2745.384101611794</v>
       </c>
       <c r="O92">
-        <v>-337.7749576168427</v>
+        <v>-343.1730127014743</v>
       </c>
       <c r="P92">
-        <v>-2364.424703317899</v>
+        <v>-2402.21108891032</v>
       </c>
       <c r="Q92">
-        <v>-1822.824703317899</v>
+        <v>-1860.61108891032</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.62748144255799</v>
+        <v>0.6921127139533223</v>
       </c>
       <c r="T92">
-        <v>11.33805399855491</v>
+        <v>12.59783777617212</v>
       </c>
       <c r="U92">
         <v>0.2067366166625341</v>
       </c>
       <c r="V92">
-        <v>0.03809242343328807</v>
+        <v>0.0376738253735816</v>
       </c>
       <c r="W92">
-        <v>0.1988615179214595</v>
+        <v>0.1989480574680647</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9113,7 +9113,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3047393874663046</v>
+        <v>0.3013906029886528</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9121,22 +9121,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2433328765517379</v>
+        <v>0.2449422427183632</v>
       </c>
       <c r="C93">
-        <v>-11781.50818766998</v>
+        <v>-12042.05131590688</v>
       </c>
       <c r="D93">
-        <v>6531.642360319625</v>
+        <v>6479.985501840846</v>
       </c>
       <c r="E93">
-        <v>15433.52357217685</v>
+        <v>15642.40984193498</v>
       </c>
       <c r="F93">
-        <v>19008.6505479896</v>
+        <v>19217.53681774773</v>
       </c>
       <c r="G93">
         <v>695.5</v>
@@ -9157,37 +9157,37 @@
         <v>1184.4</v>
       </c>
       <c r="M93">
-        <v>3929.784101611795</v>
+        <v>3972.968542288847</v>
       </c>
       <c r="N93">
-        <v>-2745.384101611794</v>
+        <v>-2788.568542288847</v>
       </c>
       <c r="O93">
-        <v>-343.1730127014743</v>
+        <v>-348.5710677861059</v>
       </c>
       <c r="P93">
-        <v>-2402.21108891032</v>
+        <v>-2439.997474502741</v>
       </c>
       <c r="Q93">
-        <v>-1860.61108891032</v>
+        <v>-1898.397474502741</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6921127139533223</v>
+        <v>0.7729018031974878</v>
       </c>
       <c r="T93">
-        <v>12.59783777617212</v>
+        <v>14.17256749819364</v>
       </c>
       <c r="U93">
         <v>0.2067366166625341</v>
       </c>
       <c r="V93">
-        <v>0.0376738253735816</v>
+        <v>0.03726432727169485</v>
       </c>
       <c r="W93">
-        <v>0.1989480574680647</v>
+        <v>0.1990327157201785</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3013906029886528</v>
+        <v>0.2981146181735588</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9203,22 +9203,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2449422427183632</v>
+        <v>0.2465516088849886</v>
       </c>
       <c r="C94">
-        <v>-12042.05131590688</v>
+        <v>-12301.7837773522</v>
       </c>
       <c r="D94">
-        <v>6479.985501840846</v>
+        <v>6429.139310153656</v>
       </c>
       <c r="E94">
-        <v>15642.40984193498</v>
+        <v>15851.29611169311</v>
       </c>
       <c r="F94">
-        <v>19217.53681774773</v>
+        <v>19426.42308750585</v>
       </c>
       <c r="G94">
         <v>695.5</v>
@@ -9239,37 +9239,37 @@
         <v>1184.4</v>
       </c>
       <c r="M94">
-        <v>3972.968542288847</v>
+        <v>4016.152982965899</v>
       </c>
       <c r="N94">
-        <v>-2788.568542288847</v>
+        <v>-2831.752982965899</v>
       </c>
       <c r="O94">
-        <v>-348.5710677861059</v>
+        <v>-353.9691228707374</v>
       </c>
       <c r="P94">
-        <v>-2439.997474502741</v>
+        <v>-2477.783860095162</v>
       </c>
       <c r="Q94">
-        <v>-1898.397474502741</v>
+        <v>-1936.183860095162</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7729018031974878</v>
+        <v>0.8767734893685577</v>
       </c>
       <c r="T94">
-        <v>14.17256749819364</v>
+        <v>16.19721999793559</v>
       </c>
       <c r="U94">
         <v>0.2067366166625341</v>
       </c>
       <c r="V94">
-        <v>0.03726432727169485</v>
+        <v>0.03686363558060136</v>
       </c>
       <c r="W94">
-        <v>0.1990327157201785</v>
+        <v>0.1991155533647199</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9277,7 +9277,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2981146181735588</v>
+        <v>0.2949090846448109</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9285,22 +9285,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2465516088849886</v>
+        <v>0.2481609750516139</v>
       </c>
       <c r="C95">
-        <v>-12301.7837773522</v>
+        <v>-12560.72450649437</v>
       </c>
       <c r="D95">
-        <v>6429.139310153656</v>
+        <v>6379.084850769614</v>
       </c>
       <c r="E95">
-        <v>15851.29611169311</v>
+        <v>16060.18238145124</v>
       </c>
       <c r="F95">
-        <v>19426.42308750585</v>
+        <v>19635.30935726398</v>
       </c>
       <c r="G95">
         <v>695.5</v>
@@ -9321,37 +9321,37 @@
         <v>1184.4</v>
       </c>
       <c r="M95">
-        <v>4016.152982965899</v>
+        <v>4059.337423642952</v>
       </c>
       <c r="N95">
-        <v>-2831.752982965899</v>
+        <v>-2874.937423642952</v>
       </c>
       <c r="O95">
-        <v>-353.9691228707374</v>
+        <v>-359.367177955369</v>
       </c>
       <c r="P95">
-        <v>-2477.783860095162</v>
+        <v>-2515.570245687583</v>
       </c>
       <c r="Q95">
-        <v>-1936.183860095162</v>
+        <v>-1973.970245687583</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8767734893685577</v>
+        <v>1.015269070929984</v>
       </c>
       <c r="T95">
-        <v>16.19721999793559</v>
+        <v>18.89675666425819</v>
       </c>
       <c r="U95">
         <v>0.2067366166625341</v>
       </c>
       <c r="V95">
-        <v>0.03686363558060136</v>
+        <v>0.03647146924463751</v>
       </c>
       <c r="W95">
-        <v>0.1991155533647199</v>
+        <v>0.1991966285061861</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9359,7 +9359,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2949090846448109</v>
+        <v>0.2917717539571001</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9367,22 +9367,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2481609750516139</v>
+        <v>0.2497703412182393</v>
       </c>
       <c r="C96">
-        <v>-12560.72450649437</v>
+        <v>-12818.89185271473</v>
       </c>
       <c r="D96">
-        <v>6379.084850769614</v>
+        <v>6329.803774307381</v>
       </c>
       <c r="E96">
-        <v>16060.18238145124</v>
+        <v>16269.06865120936</v>
       </c>
       <c r="F96">
-        <v>19635.30935726398</v>
+        <v>19844.19562702211</v>
       </c>
       <c r="G96">
         <v>695.5</v>
@@ -9403,37 +9403,37 @@
         <v>1184.4</v>
       </c>
       <c r="M96">
-        <v>4059.337423642952</v>
+        <v>4102.521864320005</v>
       </c>
       <c r="N96">
-        <v>-2874.937423642952</v>
+        <v>-2918.121864320005</v>
       </c>
       <c r="O96">
-        <v>-359.367177955369</v>
+        <v>-364.7652330400006</v>
       </c>
       <c r="P96">
-        <v>-2515.570245687583</v>
+        <v>-2553.356631280004</v>
       </c>
       <c r="Q96">
-        <v>-1973.970245687583</v>
+        <v>-2011.756631280005</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.015269070929984</v>
+        <v>1.209162885115982</v>
       </c>
       <c r="T96">
-        <v>18.89675666425819</v>
+        <v>22.67610799710984</v>
       </c>
       <c r="U96">
         <v>0.2067366166625341</v>
       </c>
       <c r="V96">
-        <v>0.03647146924463751</v>
+        <v>0.03608755904206238</v>
       </c>
       <c r="W96">
-        <v>0.1991966285061861</v>
+        <v>0.1992759968025687</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9441,7 +9441,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2917717539571001</v>
+        <v>0.2887004723364991</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9449,22 +9449,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2497703412182393</v>
+        <v>0.2513797073848646</v>
       </c>
       <c r="C97">
-        <v>-12818.89185271473</v>
+        <v>-13076.30360271522</v>
       </c>
       <c r="D97">
-        <v>6329.803774307381</v>
+        <v>6281.278294065016</v>
       </c>
       <c r="E97">
-        <v>16269.06865120936</v>
+        <v>16477.95492096749</v>
       </c>
       <c r="F97">
-        <v>19844.19562702211</v>
+        <v>20053.08189678024</v>
       </c>
       <c r="G97">
         <v>695.5</v>
@@ -9485,37 +9485,37 @@
         <v>1184.4</v>
       </c>
       <c r="M97">
-        <v>4102.521864320005</v>
+        <v>4145.706304997058</v>
       </c>
       <c r="N97">
-        <v>-2918.121864320005</v>
+        <v>-2961.306304997058</v>
       </c>
       <c r="O97">
-        <v>-364.7652330400006</v>
+        <v>-370.1632881246323</v>
       </c>
       <c r="P97">
-        <v>-2553.356631280004</v>
+        <v>-2591.143016872426</v>
       </c>
       <c r="Q97">
-        <v>-2011.756631280005</v>
+        <v>-2049.543016872426</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.209162885115982</v>
+        <v>1.500003606394978</v>
       </c>
       <c r="T97">
-        <v>22.67610799710984</v>
+        <v>28.34513499638732</v>
       </c>
       <c r="U97">
         <v>0.2067366166625341</v>
       </c>
       <c r="V97">
-        <v>0.03608755904206238</v>
+        <v>0.03571164696870756</v>
       </c>
       <c r="W97">
-        <v>0.1992759968025687</v>
+        <v>0.1993537115927767</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9523,7 +9523,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2887004723364991</v>
+        <v>0.2856931757496605</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9531,22 +9531,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2513797073848646</v>
+        <v>0.2529890735514899</v>
       </c>
       <c r="C98">
-        <v>-13076.30360271522</v>
+        <v>-13332.97700192233</v>
       </c>
       <c r="D98">
-        <v>6281.278294065016</v>
+        <v>6233.491164616028</v>
       </c>
       <c r="E98">
-        <v>16477.95492096749</v>
+        <v>16686.84119072562</v>
       </c>
       <c r="F98">
-        <v>20053.08189678023</v>
+        <v>20261.96816653836</v>
       </c>
       <c r="G98">
         <v>695.5</v>
@@ -9567,37 +9567,37 @@
         <v>1184.4</v>
       </c>
       <c r="M98">
-        <v>4145.706304997057</v>
+        <v>4188.89074567411</v>
       </c>
       <c r="N98">
-        <v>-2961.306304997057</v>
+        <v>-3004.49074567411</v>
       </c>
       <c r="O98">
-        <v>-370.1632881246322</v>
+        <v>-375.5613432092637</v>
       </c>
       <c r="P98">
-        <v>-2591.143016872425</v>
+        <v>-2628.929402464846</v>
       </c>
       <c r="Q98">
-        <v>-2049.543016872425</v>
+        <v>-2087.329402464846</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.500003606394974</v>
+        <v>1.984738141859965</v>
       </c>
       <c r="T98">
-        <v>28.34513499638724</v>
+        <v>37.79351332851632</v>
       </c>
       <c r="U98">
         <v>0.2067366166625341</v>
       </c>
       <c r="V98">
-        <v>0.03571164696870757</v>
+        <v>0.03534348565975182</v>
       </c>
       <c r="W98">
-        <v>0.1993537115927767</v>
+        <v>0.1994298240161762</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9605,7 +9605,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2856931757496606</v>
+        <v>0.2827478852780145</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9613,22 +9613,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2529890735514899</v>
+        <v>0.2545984397181152</v>
       </c>
       <c r="C99">
-        <v>-13332.97700192233</v>
+        <v>-13588.92877492142</v>
       </c>
       <c r="D99">
-        <v>6233.491164616028</v>
+        <v>6186.425661375071</v>
       </c>
       <c r="E99">
-        <v>16686.84119072562</v>
+        <v>16895.72746048374</v>
       </c>
       <c r="F99">
-        <v>20261.96816653836</v>
+        <v>20470.85443629649</v>
       </c>
       <c r="G99">
         <v>695.5</v>
@@ -9649,37 +9649,37 @@
         <v>1184.4</v>
       </c>
       <c r="M99">
-        <v>4188.89074567411</v>
+        <v>4232.075186351163</v>
       </c>
       <c r="N99">
-        <v>-3004.49074567411</v>
+        <v>-3047.675186351163</v>
       </c>
       <c r="O99">
-        <v>-375.5613432092637</v>
+        <v>-380.9593982938954</v>
       </c>
       <c r="P99">
-        <v>-2628.929402464846</v>
+        <v>-2666.715788057268</v>
       </c>
       <c r="Q99">
-        <v>-2087.329402464846</v>
+        <v>-2125.115788057268</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.984738141859965</v>
+        <v>2.954207212789947</v>
       </c>
       <c r="T99">
-        <v>37.79351332851632</v>
+        <v>56.69026999277447</v>
       </c>
       <c r="U99">
         <v>0.2067366166625341</v>
       </c>
       <c r="V99">
-        <v>0.03534348565975182</v>
+        <v>0.0349828378468972</v>
       </c>
       <c r="W99">
-        <v>0.1994298240161762</v>
+        <v>0.1995043831248125</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9687,7 +9687,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2827478852780145</v>
+        <v>0.2798627027751777</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9695,22 +9695,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2545984397181152</v>
+        <v>0.2562078058847406</v>
       </c>
       <c r="C100">
-        <v>-13588.92877492142</v>
+        <v>-13844.17514497218</v>
       </c>
       <c r="D100">
-        <v>6186.425661375071</v>
+        <v>6140.065561082441</v>
       </c>
       <c r="E100">
-        <v>16895.72746048374</v>
+        <v>17104.61373024187</v>
       </c>
       <c r="F100">
-        <v>20470.85443629649</v>
+        <v>20679.74070605462</v>
       </c>
       <c r="G100">
         <v>695.5</v>
@@ -9731,37 +9731,37 @@
         <v>1184.4</v>
       </c>
       <c r="M100">
-        <v>4232.075186351163</v>
+        <v>4275.259627028216</v>
       </c>
       <c r="N100">
-        <v>-3047.675186351163</v>
+        <v>-3090.859627028216</v>
       </c>
       <c r="O100">
-        <v>-380.9593982938954</v>
+        <v>-386.3574533785269</v>
       </c>
       <c r="P100">
-        <v>-2666.715788057268</v>
+        <v>-2704.502173649689</v>
       </c>
       <c r="Q100">
-        <v>-2125.115788057268</v>
+        <v>-2162.902173649689</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.954207212789947</v>
+        <v>5.862614425579895</v>
       </c>
       <c r="T100">
-        <v>56.69026999277447</v>
+        <v>113.3805399855489</v>
       </c>
       <c r="U100">
         <v>0.2067366166625341</v>
       </c>
       <c r="V100">
-        <v>0.0349828378468972</v>
+        <v>0.0346294758484437</v>
       </c>
       <c r="W100">
-        <v>0.1995043831248125</v>
+        <v>0.1995774359888299</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9769,91 +9769,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2798627027751777</v>
+        <v>0.2770358067875496</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2562078058847406</v>
-      </c>
-      <c r="C101">
-        <v>-13844.17514497218</v>
-      </c>
-      <c r="D101">
-        <v>6140.065561082441</v>
-      </c>
-      <c r="E101">
-        <v>17104.61373024187</v>
-      </c>
-      <c r="F101">
-        <v>20679.74070605462</v>
-      </c>
-      <c r="G101">
-        <v>695.5</v>
-      </c>
-      <c r="H101">
-        <v>17313.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1726</v>
-      </c>
-      <c r="K101">
-        <v>541.6</v>
-      </c>
-      <c r="L101">
-        <v>1184.4</v>
-      </c>
-      <c r="M101">
-        <v>4275.259627028216</v>
-      </c>
-      <c r="N101">
-        <v>-3090.859627028216</v>
-      </c>
-      <c r="O101">
-        <v>-386.3574533785269</v>
-      </c>
-      <c r="P101">
-        <v>-2704.502173649689</v>
-      </c>
-      <c r="Q101">
-        <v>-2162.902173649689</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.862614425579895</v>
-      </c>
-      <c r="T101">
-        <v>113.3805399855489</v>
-      </c>
-      <c r="U101">
-        <v>0.2067366166625341</v>
-      </c>
-      <c r="V101">
-        <v>0.0346294758484437</v>
-      </c>
-      <c r="W101">
-        <v>0.1995774359888299</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2770358067875496</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
